--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q548"/>
+  <dimension ref="A1:Q550"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -23081,33 +23081,153 @@
       </c>
     </row>
     <row r="548">
-      <c r="A548" s="60" t="inlineStr">
+      <c r="A548" t="n">
+        <v>542</v>
+      </c>
+      <c r="B548" s="128" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C548">
+        <f>IF(B548="","",TEXT(B548,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>Concrete/Gitti</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>Gitti/Concrete 41.48 MT @ ₹2,300/MT</t>
+        </is>
+      </c>
+      <c r="H548" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="I548" t="n">
+        <v>41.48</v>
+      </c>
+      <c r="J548" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="K548" t="n">
+        <v>2300</v>
+      </c>
+      <c r="L548">
+        <f>I548*K548</f>
+        <v/>
+      </c>
+      <c r="N548">
+        <f>M548*L548</f>
+        <v/>
+      </c>
+      <c r="O548">
+        <f>IF(L548="","",IF(M548="",L548,L548*(1-M548)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="n">
+        <v>543</v>
+      </c>
+      <c r="B549" s="128" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C549">
+        <f>IF(B549="","",TEXT(B549,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>Labour for gitti/concrete loading</t>
+        </is>
+      </c>
+      <c r="H549" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="I549" t="n">
+        <v>1</v>
+      </c>
+      <c r="J549" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K549" t="n">
+        <v>200</v>
+      </c>
+      <c r="L549">
+        <f>I549*K549</f>
+        <v/>
+      </c>
+      <c r="N549">
+        <f>M549*L549</f>
+        <v/>
+      </c>
+      <c r="O549">
+        <f>IF(L549="","",IF(M549="",L549,L549*(1-M549)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B548" s="60" t="n"/>
-      <c r="C548" s="60" t="n"/>
-      <c r="D548" s="60" t="n"/>
-      <c r="E548" s="60" t="n"/>
-      <c r="F548" s="60" t="n"/>
-      <c r="G548" s="60" t="n"/>
-      <c r="H548" s="60" t="n"/>
-      <c r="I548" s="60" t="n"/>
-      <c r="J548" s="60" t="n"/>
-      <c r="K548" s="60" t="n"/>
-      <c r="L548" s="61">
-        <f>SUM(L5:L547)</f>
-        <v/>
-      </c>
-      <c r="M548" s="60" t="n"/>
-      <c r="N548" s="60" t="n"/>
-      <c r="O548" s="61">
+      <c r="B550" s="60" t="n"/>
+      <c r="C550" s="60" t="n"/>
+      <c r="D550" s="60" t="n"/>
+      <c r="E550" s="60" t="n"/>
+      <c r="F550" s="60" t="n"/>
+      <c r="G550" s="60" t="n"/>
+      <c r="H550" s="60" t="n"/>
+      <c r="I550" s="60" t="n"/>
+      <c r="J550" s="60" t="n"/>
+      <c r="K550" s="60" t="n"/>
+      <c r="L550" s="61">
+        <f>SUM(L5:L549)</f>
+        <v/>
+      </c>
+      <c r="M550" s="60" t="n"/>
+      <c r="N550" s="60" t="n"/>
+      <c r="O550" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P548" s="60" t="n"/>
-      <c r="Q548" s="60" t="n"/>
+      <c r="P550" s="60" t="n"/>
+      <c r="Q550" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -37197,32 +37317,92 @@
       <c r="M49" s="47" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="99">
-      <c r="A50" s="43" t="n"/>
-      <c r="B50" s="53" t="n"/>
-      <c r="C50" s="55" t="n"/>
-      <c r="D50" s="55" t="n"/>
-      <c r="E50" s="55" t="n"/>
-      <c r="F50" s="55" t="n"/>
-      <c r="G50" s="63" t="n"/>
-      <c r="H50" s="55" t="n"/>
+      <c r="A50" s="43" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="53" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C50" s="55" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D50" s="55" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="E50" s="55" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F50" s="55" t="inlineStr">
+        <is>
+          <t>Gitti/Concrete 41.48 MT + labour</t>
+        </is>
+      </c>
+      <c r="G50" s="63" t="n">
+        <v>5000</v>
+      </c>
+      <c r="H50" s="55" t="inlineStr">
+        <is>
+          <t>GPay</t>
+        </is>
+      </c>
       <c r="I50" s="55" t="n"/>
       <c r="J50" s="55" t="n"/>
-      <c r="K50" s="55" t="n"/>
+      <c r="K50" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L50" s="58" t="n"/>
       <c r="M50" s="55" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="99">
-      <c r="A51" s="41" t="n"/>
-      <c r="B51" s="45" t="n"/>
-      <c r="C51" s="47" t="n"/>
-      <c r="D51" s="47" t="n"/>
-      <c r="E51" s="47" t="n"/>
-      <c r="F51" s="47" t="n"/>
-      <c r="G51" s="62" t="n"/>
-      <c r="H51" s="47" t="n"/>
+      <c r="A51" s="41" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="45" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C51" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D51" s="47" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="E51" s="47" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F51" s="47" t="inlineStr">
+        <is>
+          <t>Gitti/Concrete 41.48 MT + labour</t>
+        </is>
+      </c>
+      <c r="G51" s="62" t="n">
+        <v>90600</v>
+      </c>
+      <c r="H51" s="47" t="inlineStr">
+        <is>
+          <t>Bank</t>
+        </is>
+      </c>
       <c r="I51" s="47" t="n"/>
       <c r="J51" s="47" t="n"/>
-      <c r="K51" s="47" t="n"/>
+      <c r="K51" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L51" s="50" t="n"/>
       <c r="M51" s="47" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -37407,17 +37407,47 @@
       <c r="M51" s="47" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="99">
-      <c r="A52" s="43" t="n"/>
-      <c r="B52" s="53" t="n"/>
-      <c r="C52" s="55" t="n"/>
-      <c r="D52" s="55" t="n"/>
-      <c r="E52" s="55" t="n"/>
-      <c r="F52" s="55" t="n"/>
-      <c r="G52" s="63" t="n"/>
-      <c r="H52" s="55" t="n"/>
+      <c r="A52" s="43" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="53" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C52" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D52" s="55" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="E52" s="55" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F52" s="55" t="inlineStr">
+        <is>
+          <t>Gitti/Concrete final settlement balance</t>
+        </is>
+      </c>
+      <c r="G52" s="63" t="n">
+        <v>4</v>
+      </c>
+      <c r="H52" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I52" s="55" t="n"/>
       <c r="J52" s="55" t="n"/>
-      <c r="K52" s="55" t="n"/>
+      <c r="K52" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L52" s="58" t="n"/>
       <c r="M52" s="55" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q550"/>
+  <dimension ref="A1:Q551"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -23201,33 +23201,93 @@
       </c>
     </row>
     <row r="550">
-      <c r="A550" s="60" t="inlineStr">
+      <c r="A550" t="n">
+        <v>544</v>
+      </c>
+      <c r="B550" s="128" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C550">
+        <f>IF(B550="","",TEXT(B550,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>Engineer Supervision</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>Engineer supervision and site coordination</t>
+        </is>
+      </c>
+      <c r="H550" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I550" t="n">
+        <v>1</v>
+      </c>
+      <c r="J550" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K550" t="n">
+        <v>37700</v>
+      </c>
+      <c r="L550">
+        <f>I550*K550</f>
+        <v/>
+      </c>
+      <c r="N550">
+        <f>M550*L550</f>
+        <v/>
+      </c>
+      <c r="O550">
+        <f>IF(L550="","",IF(M550="",L550,L550*(1-M550)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B550" s="60" t="n"/>
-      <c r="C550" s="60" t="n"/>
-      <c r="D550" s="60" t="n"/>
-      <c r="E550" s="60" t="n"/>
-      <c r="F550" s="60" t="n"/>
-      <c r="G550" s="60" t="n"/>
-      <c r="H550" s="60" t="n"/>
-      <c r="I550" s="60" t="n"/>
-      <c r="J550" s="60" t="n"/>
-      <c r="K550" s="60" t="n"/>
-      <c r="L550" s="61">
-        <f>SUM(L5:L549)</f>
-        <v/>
-      </c>
-      <c r="M550" s="60" t="n"/>
-      <c r="N550" s="60" t="n"/>
-      <c r="O550" s="61">
+      <c r="B551" s="60" t="n"/>
+      <c r="C551" s="60" t="n"/>
+      <c r="D551" s="60" t="n"/>
+      <c r="E551" s="60" t="n"/>
+      <c r="F551" s="60" t="n"/>
+      <c r="G551" s="60" t="n"/>
+      <c r="H551" s="60" t="n"/>
+      <c r="I551" s="60" t="n"/>
+      <c r="J551" s="60" t="n"/>
+      <c r="K551" s="60" t="n"/>
+      <c r="L551" s="61">
+        <f>SUM(L5:L550)</f>
+        <v/>
+      </c>
+      <c r="M551" s="60" t="n"/>
+      <c r="N551" s="60" t="n"/>
+      <c r="O551" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P550" s="60" t="n"/>
-      <c r="Q550" s="60" t="n"/>
+      <c r="P551" s="60" t="n"/>
+      <c r="Q551" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -37452,17 +37512,47 @@
       <c r="M52" s="55" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="99">
-      <c r="A53" s="41" t="n"/>
-      <c r="B53" s="45" t="n"/>
-      <c r="C53" s="47" t="n"/>
-      <c r="D53" s="47" t="n"/>
-      <c r="E53" s="47" t="n"/>
-      <c r="F53" s="47" t="n"/>
-      <c r="G53" s="62" t="n"/>
-      <c r="H53" s="47" t="n"/>
+      <c r="A53" s="41" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="45" t="n">
+        <v>46224</v>
+      </c>
+      <c r="C53" s="47" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D53" s="47" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E53" s="47" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F53" s="47" t="inlineStr">
+        <is>
+          <t>Engineer supervision and coordination</t>
+        </is>
+      </c>
+      <c r="G53" s="62" t="n">
+        <v>37700</v>
+      </c>
+      <c r="H53" s="47" t="inlineStr">
+        <is>
+          <t>GPay</t>
+        </is>
+      </c>
       <c r="I53" s="47" t="n"/>
       <c r="J53" s="47" t="n"/>
-      <c r="K53" s="47" t="n"/>
+      <c r="K53" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L53" s="50" t="n"/>
       <c r="M53" s="47" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q551"/>
+  <dimension ref="A1:Q553"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -23261,33 +23261,153 @@
       </c>
     </row>
     <row r="551">
-      <c r="A551" s="60" t="inlineStr">
+      <c r="A551" t="n">
+        <v>545</v>
+      </c>
+      <c r="B551" s="128" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C551">
+        <f>IF(B551="","",TEXT(B551,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>Ultratech Premium Cement 20 bags @ ₹330</t>
+        </is>
+      </c>
+      <c r="H551" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I551" t="n">
+        <v>20</v>
+      </c>
+      <c r="J551" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K551" t="n">
+        <v>330</v>
+      </c>
+      <c r="L551">
+        <f>I551*K551</f>
+        <v/>
+      </c>
+      <c r="N551">
+        <f>M551*L551</f>
+        <v/>
+      </c>
+      <c r="O551">
+        <f>IF(L551="","",IF(M551="",L551,L551*(1-M551)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="n">
+        <v>546</v>
+      </c>
+      <c r="B552" s="128" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C552">
+        <f>IF(B552="","",TEXT(B552,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>Labour for cement handling/loading</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I552" t="n">
+        <v>1</v>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K552" t="n">
+        <v>400</v>
+      </c>
+      <c r="L552">
+        <f>I552*K552</f>
+        <v/>
+      </c>
+      <c r="N552">
+        <f>M552*L552</f>
+        <v/>
+      </c>
+      <c r="O552">
+        <f>IF(L552="","",IF(M552="",L552,L552*(1-M552)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B551" s="60" t="n"/>
-      <c r="C551" s="60" t="n"/>
-      <c r="D551" s="60" t="n"/>
-      <c r="E551" s="60" t="n"/>
-      <c r="F551" s="60" t="n"/>
-      <c r="G551" s="60" t="n"/>
-      <c r="H551" s="60" t="n"/>
-      <c r="I551" s="60" t="n"/>
-      <c r="J551" s="60" t="n"/>
-      <c r="K551" s="60" t="n"/>
-      <c r="L551" s="61">
-        <f>SUM(L5:L550)</f>
-        <v/>
-      </c>
-      <c r="M551" s="60" t="n"/>
-      <c r="N551" s="60" t="n"/>
-      <c r="O551" s="61">
+      <c r="B553" s="60" t="n"/>
+      <c r="C553" s="60" t="n"/>
+      <c r="D553" s="60" t="n"/>
+      <c r="E553" s="60" t="n"/>
+      <c r="F553" s="60" t="n"/>
+      <c r="G553" s="60" t="n"/>
+      <c r="H553" s="60" t="n"/>
+      <c r="I553" s="60" t="n"/>
+      <c r="J553" s="60" t="n"/>
+      <c r="K553" s="60" t="n"/>
+      <c r="L553" s="61">
+        <f>SUM(L5:L552)</f>
+        <v/>
+      </c>
+      <c r="M553" s="60" t="n"/>
+      <c r="N553" s="60" t="n"/>
+      <c r="O553" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P551" s="60" t="n"/>
-      <c r="Q551" s="60" t="n"/>
+      <c r="P553" s="60" t="n"/>
+      <c r="Q553" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -37557,17 +37677,47 @@
       <c r="M53" s="47" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="99">
-      <c r="A54" s="43" t="n"/>
-      <c r="B54" s="53" t="n"/>
-      <c r="C54" s="55" t="n"/>
-      <c r="D54" s="55" t="n"/>
-      <c r="E54" s="55" t="n"/>
-      <c r="F54" s="55" t="n"/>
-      <c r="G54" s="63" t="n"/>
-      <c r="H54" s="55" t="n"/>
+      <c r="A54" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="53" t="n">
+        <v>46225</v>
+      </c>
+      <c r="C54" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D54" s="55" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E54" s="55" t="inlineStr">
+        <is>
+          <t>Building Materials + Labour</t>
+        </is>
+      </c>
+      <c r="F54" s="55" t="inlineStr">
+        <is>
+          <t>Cement 20 bags + labour</t>
+        </is>
+      </c>
+      <c r="G54" s="63" t="n">
+        <v>7000</v>
+      </c>
+      <c r="H54" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I54" s="55" t="n"/>
       <c r="J54" s="55" t="n"/>
-      <c r="K54" s="55" t="n"/>
+      <c r="K54" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L54" s="58" t="n"/>
       <c r="M54" s="55" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q553"/>
+  <dimension ref="A1:Q554"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -23381,33 +23381,93 @@
       </c>
     </row>
     <row r="553">
-      <c r="A553" s="60" t="inlineStr">
+      <c r="A553" t="n">
+        <v>547</v>
+      </c>
+      <c r="B553" s="128" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C553">
+        <f>IF(B553="","",TEXT(B553,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>Engineer Supervision</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>Payment to Santosh — aara mil (received)</t>
+        </is>
+      </c>
+      <c r="H553" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I553" t="n">
+        <v>1</v>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K553" t="n">
+        <v>4000</v>
+      </c>
+      <c r="L553">
+        <f>I553*K553</f>
+        <v/>
+      </c>
+      <c r="N553">
+        <f>M553*L553</f>
+        <v/>
+      </c>
+      <c r="O553">
+        <f>IF(L553="","",IF(M553="",L553,L553*(1-M553)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B553" s="60" t="n"/>
-      <c r="C553" s="60" t="n"/>
-      <c r="D553" s="60" t="n"/>
-      <c r="E553" s="60" t="n"/>
-      <c r="F553" s="60" t="n"/>
-      <c r="G553" s="60" t="n"/>
-      <c r="H553" s="60" t="n"/>
-      <c r="I553" s="60" t="n"/>
-      <c r="J553" s="60" t="n"/>
-      <c r="K553" s="60" t="n"/>
-      <c r="L553" s="61">
-        <f>SUM(L5:L552)</f>
-        <v/>
-      </c>
-      <c r="M553" s="60" t="n"/>
-      <c r="N553" s="60" t="n"/>
-      <c r="O553" s="61">
+      <c r="B554" s="60" t="n"/>
+      <c r="C554" s="60" t="n"/>
+      <c r="D554" s="60" t="n"/>
+      <c r="E554" s="60" t="n"/>
+      <c r="F554" s="60" t="n"/>
+      <c r="G554" s="60" t="n"/>
+      <c r="H554" s="60" t="n"/>
+      <c r="I554" s="60" t="n"/>
+      <c r="J554" s="60" t="n"/>
+      <c r="K554" s="60" t="n"/>
+      <c r="L554" s="61">
+        <f>SUM(L5:L553)</f>
+        <v/>
+      </c>
+      <c r="M554" s="60" t="n"/>
+      <c r="N554" s="60" t="n"/>
+      <c r="O554" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P553" s="60" t="n"/>
-      <c r="Q553" s="60" t="n"/>
+      <c r="P554" s="60" t="n"/>
+      <c r="Q554" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -37722,17 +37782,47 @@
       <c r="M54" s="55" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="99">
-      <c r="A55" s="41" t="n"/>
-      <c r="B55" s="45" t="n"/>
-      <c r="C55" s="47" t="n"/>
-      <c r="D55" s="47" t="n"/>
-      <c r="E55" s="47" t="n"/>
-      <c r="F55" s="47" t="n"/>
-      <c r="G55" s="62" t="n"/>
-      <c r="H55" s="47" t="n"/>
+      <c r="A55" s="41" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="45" t="n">
+        <v>46234</v>
+      </c>
+      <c r="C55" s="47" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D55" s="47" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E55" s="47" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F55" s="47" t="inlineStr">
+        <is>
+          <t>Santosh aara mil — payment received</t>
+        </is>
+      </c>
+      <c r="G55" s="62" t="n">
+        <v>4000</v>
+      </c>
+      <c r="H55" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I55" s="47" t="n"/>
       <c r="J55" s="47" t="n"/>
-      <c r="K55" s="47" t="n"/>
+      <c r="K55" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L55" s="50" t="n"/>
       <c r="M55" s="47" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -37827,17 +37827,47 @@
       <c r="M55" s="47" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="99">
-      <c r="A56" s="43" t="n"/>
-      <c r="B56" s="53" t="n"/>
-      <c r="C56" s="55" t="n"/>
-      <c r="D56" s="55" t="n"/>
-      <c r="E56" s="55" t="n"/>
-      <c r="F56" s="55" t="n"/>
-      <c r="G56" s="63" t="n"/>
-      <c r="H56" s="55" t="n"/>
+      <c r="A56" s="43" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="53" t="n">
+        <v>46236</v>
+      </c>
+      <c r="C56" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D56" s="55" t="inlineStr">
+        <is>
+          <t>Mukesh Yadav</t>
+        </is>
+      </c>
+      <c r="E56" s="55" t="inlineStr">
+        <is>
+          <t>Land Development + Labour</t>
+        </is>
+      </c>
+      <c r="F56" s="55" t="inlineStr">
+        <is>
+          <t>JCB + Mitti + Sand movement — final settlement</t>
+        </is>
+      </c>
+      <c r="G56" s="63" t="n">
+        <v>32950</v>
+      </c>
+      <c r="H56" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I56" s="55" t="n"/>
       <c r="J56" s="55" t="n"/>
-      <c r="K56" s="55" t="n"/>
+      <c r="K56" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L56" s="58" t="n"/>
       <c r="M56" s="55" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q554"/>
+  <dimension ref="A1:Q559"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -23441,33 +23441,333 @@
       </c>
     </row>
     <row r="554">
-      <c r="A554" s="60" t="inlineStr">
+      <c r="A554" t="n">
+        <v>548</v>
+      </c>
+      <c r="B554" s="128" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C554">
+        <f>IF(B554="","",TEXT(B554,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>Ultratech Super cement 25 bags @ ₹350</t>
+        </is>
+      </c>
+      <c r="H554" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I554" t="n">
+        <v>25</v>
+      </c>
+      <c r="J554" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K554" t="n">
+        <v>350</v>
+      </c>
+      <c r="L554">
+        <f>I554*K554</f>
+        <v/>
+      </c>
+      <c r="N554">
+        <f>M554*L554</f>
+        <v/>
+      </c>
+      <c r="O554">
+        <f>IF(L554="","",IF(M554="",L554,L554*(1-M554)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="n">
+        <v>549</v>
+      </c>
+      <c r="B555" s="128" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C555">
+        <f>IF(B555="","",TEXT(B555,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>10mm Tata Tiscon Rod 50 pcs @ ₹590 (4% disc)</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I555" t="n">
+        <v>50</v>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K555" t="n">
+        <v>566.4</v>
+      </c>
+      <c r="L555">
+        <f>I555*K555</f>
+        <v/>
+      </c>
+      <c r="N555">
+        <f>M555*L555</f>
+        <v/>
+      </c>
+      <c r="O555">
+        <f>IF(L555="","",IF(M555="",L555,L555*(1-M555)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="n">
+        <v>550</v>
+      </c>
+      <c r="B556" s="128" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C556">
+        <f>IF(B556="","",TEXT(B556,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>6mm Tata Tiscon Rod 40 pcs @ ₹228</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I556" t="n">
+        <v>40</v>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K556" t="n">
+        <v>228</v>
+      </c>
+      <c r="L556">
+        <f>I556*K556</f>
+        <v/>
+      </c>
+      <c r="N556">
+        <f>M556*L556</f>
+        <v/>
+      </c>
+      <c r="O556">
+        <f>IF(L556="","",IF(M556="",L556,L556*(1-M556)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="n">
+        <v>551</v>
+      </c>
+      <c r="B557" s="128" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C557">
+        <f>IF(B557="","",TEXT(B557,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Tata soft wire 10 Kg @ ₹110</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I557" t="n">
+        <v>10</v>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K557" t="n">
+        <v>110</v>
+      </c>
+      <c r="L557">
+        <f>I557*K557</f>
+        <v/>
+      </c>
+      <c r="N557">
+        <f>M557*L557</f>
+        <v/>
+      </c>
+      <c r="O557">
+        <f>IF(L557="","",IF(M557="",L557,L557*(1-M557)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="n">
+        <v>552</v>
+      </c>
+      <c r="B558" s="128" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C558">
+        <f>IF(B558="","",TEXT(B558,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Labour for loading/handling</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I558" t="n">
+        <v>1</v>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K558" t="n">
+        <v>450</v>
+      </c>
+      <c r="L558">
+        <f>I558*K558</f>
+        <v/>
+      </c>
+      <c r="N558">
+        <f>M558*L558</f>
+        <v/>
+      </c>
+      <c r="O558">
+        <f>IF(L558="","",IF(M558="",L558,L558*(1-M558)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B554" s="60" t="n"/>
-      <c r="C554" s="60" t="n"/>
-      <c r="D554" s="60" t="n"/>
-      <c r="E554" s="60" t="n"/>
-      <c r="F554" s="60" t="n"/>
-      <c r="G554" s="60" t="n"/>
-      <c r="H554" s="60" t="n"/>
-      <c r="I554" s="60" t="n"/>
-      <c r="J554" s="60" t="n"/>
-      <c r="K554" s="60" t="n"/>
-      <c r="L554" s="61">
-        <f>SUM(L5:L553)</f>
-        <v/>
-      </c>
-      <c r="M554" s="60" t="n"/>
-      <c r="N554" s="60" t="n"/>
-      <c r="O554" s="61">
+      <c r="B559" s="60" t="n"/>
+      <c r="C559" s="60" t="n"/>
+      <c r="D559" s="60" t="n"/>
+      <c r="E559" s="60" t="n"/>
+      <c r="F559" s="60" t="n"/>
+      <c r="G559" s="60" t="n"/>
+      <c r="H559" s="60" t="n"/>
+      <c r="I559" s="60" t="n"/>
+      <c r="J559" s="60" t="n"/>
+      <c r="K559" s="60" t="n"/>
+      <c r="L559" s="61">
+        <f>SUM(L5:L558)</f>
+        <v/>
+      </c>
+      <c r="M559" s="60" t="n"/>
+      <c r="N559" s="60" t="n"/>
+      <c r="O559" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P554" s="60" t="n"/>
-      <c r="Q554" s="60" t="n"/>
+      <c r="P559" s="60" t="n"/>
+      <c r="Q559" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -37872,17 +38172,47 @@
       <c r="M56" s="55" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="99">
-      <c r="A57" s="41" t="n"/>
-      <c r="B57" s="45" t="n"/>
-      <c r="C57" s="47" t="n"/>
-      <c r="D57" s="47" t="n"/>
-      <c r="E57" s="47" t="n"/>
-      <c r="F57" s="47" t="n"/>
-      <c r="G57" s="62" t="n"/>
-      <c r="H57" s="47" t="n"/>
+      <c r="A57" s="41" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="45" t="n">
+        <v>46241</v>
+      </c>
+      <c r="C57" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D57" s="47" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E57" s="47" t="inlineStr">
+        <is>
+          <t>Building Materials + Steel + Labour</t>
+        </is>
+      </c>
+      <c r="F57" s="47" t="inlineStr">
+        <is>
+          <t>Cement + Tata Tiscon rods + wire + labour</t>
+        </is>
+      </c>
+      <c r="G57" s="62" t="n">
+        <v>47740</v>
+      </c>
+      <c r="H57" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I57" s="47" t="n"/>
       <c r="J57" s="47" t="n"/>
-      <c r="K57" s="47" t="n"/>
+      <c r="K57" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L57" s="50" t="n"/>
       <c r="M57" s="47" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q559"/>
+  <dimension ref="A1:Q564"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -23741,33 +23741,333 @@
       </c>
     </row>
     <row r="559">
-      <c r="A559" s="60" t="inlineStr">
+      <c r="A559" t="n">
+        <v>553</v>
+      </c>
+      <c r="B559" s="128" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C559">
+        <f>IF(B559="","",TEXT(B559,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Darbhanga labour payment</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I559" t="n">
+        <v>1</v>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="K559" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L559">
+        <f>I559*K559</f>
+        <v/>
+      </c>
+      <c r="N559">
+        <f>M559*L559</f>
+        <v/>
+      </c>
+      <c r="O559">
+        <f>IF(L559="","",IF(M559="",L559,L559*(1-M559)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="n">
+        <v>554</v>
+      </c>
+      <c r="B560" s="128" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C560">
+        <f>IF(B560="","",TEXT(B560,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>Fabrication</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Chotu lohabala</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I560" t="n">
+        <v>1</v>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="K560" t="n">
+        <v>5000</v>
+      </c>
+      <c r="L560">
+        <f>I560*K560</f>
+        <v/>
+      </c>
+      <c r="N560">
+        <f>M560*L560</f>
+        <v/>
+      </c>
+      <c r="O560">
+        <f>IF(L560="","",IF(M560="",L560,L560*(1-M560)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="n">
+        <v>555</v>
+      </c>
+      <c r="B561" s="128" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C561">
+        <f>IF(B561="","",TEXT(B561,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>Fabrication</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Grilling</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I561" t="n">
+        <v>1</v>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K561" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L561">
+        <f>I561*K561</f>
+        <v/>
+      </c>
+      <c r="N561">
+        <f>M561*L561</f>
+        <v/>
+      </c>
+      <c r="O561">
+        <f>IF(L561="","",IF(M561="",L561,L561*(1-M561)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="n">
+        <v>556</v>
+      </c>
+      <c r="B562" s="128" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C562">
+        <f>IF(B562="","",TEXT(B562,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>Plywood/Shuttering</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>4mm ply</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I562" t="n">
+        <v>1</v>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="K562" t="n">
+        <v>700</v>
+      </c>
+      <c r="L562">
+        <f>I562*K562</f>
+        <v/>
+      </c>
+      <c r="N562">
+        <f>M562*L562</f>
+        <v/>
+      </c>
+      <c r="O562">
+        <f>IF(L562="","",IF(M562="",L562,L562*(1-M562)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="n">
+        <v>557</v>
+      </c>
+      <c r="B563" s="128" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C563">
+        <f>IF(B563="","",TEXT(B563,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Bayju</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I563" t="n">
+        <v>1</v>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="K563" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L563">
+        <f>I563*K563</f>
+        <v/>
+      </c>
+      <c r="N563">
+        <f>M563*L563</f>
+        <v/>
+      </c>
+      <c r="O563">
+        <f>IF(L563="","",IF(M563="",L563,L563*(1-M563)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B559" s="60" t="n"/>
-      <c r="C559" s="60" t="n"/>
-      <c r="D559" s="60" t="n"/>
-      <c r="E559" s="60" t="n"/>
-      <c r="F559" s="60" t="n"/>
-      <c r="G559" s="60" t="n"/>
-      <c r="H559" s="60" t="n"/>
-      <c r="I559" s="60" t="n"/>
-      <c r="J559" s="60" t="n"/>
-      <c r="K559" s="60" t="n"/>
-      <c r="L559" s="61">
-        <f>SUM(L5:L558)</f>
-        <v/>
-      </c>
-      <c r="M559" s="60" t="n"/>
-      <c r="N559" s="60" t="n"/>
-      <c r="O559" s="61">
+      <c r="B564" s="60" t="n"/>
+      <c r="C564" s="60" t="n"/>
+      <c r="D564" s="60" t="n"/>
+      <c r="E564" s="60" t="n"/>
+      <c r="F564" s="60" t="n"/>
+      <c r="G564" s="60" t="n"/>
+      <c r="H564" s="60" t="n"/>
+      <c r="I564" s="60" t="n"/>
+      <c r="J564" s="60" t="n"/>
+      <c r="K564" s="60" t="n"/>
+      <c r="L564" s="61">
+        <f>SUM(L5:L563)</f>
+        <v/>
+      </c>
+      <c r="M564" s="60" t="n"/>
+      <c r="N564" s="60" t="n"/>
+      <c r="O564" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P559" s="60" t="n"/>
-      <c r="Q559" s="60" t="n"/>
+      <c r="P564" s="60" t="n"/>
+      <c r="Q564" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -35716,7 +36016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M504"/>
+  <dimension ref="A1:M505"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -38217,17 +38517,47 @@
       <c r="M57" s="47" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="99">
-      <c r="A58" s="43" t="n"/>
-      <c r="B58" s="53" t="n"/>
-      <c r="C58" s="55" t="n"/>
-      <c r="D58" s="55" t="n"/>
-      <c r="E58" s="55" t="n"/>
-      <c r="F58" s="55" t="n"/>
-      <c r="G58" s="63" t="n"/>
-      <c r="H58" s="55" t="n"/>
+      <c r="A58" s="43" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="53" t="n">
+        <v>46243</v>
+      </c>
+      <c r="C58" s="55" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D58" s="55" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E58" s="55" t="inlineStr">
+        <is>
+          <t>Labour + Steel/Iron + Building Materials</t>
+        </is>
+      </c>
+      <c r="F58" s="55" t="inlineStr">
+        <is>
+          <t>Darbhanga labour, chotu lohabala, grilling, 4mm ply, Bayju</t>
+        </is>
+      </c>
+      <c r="G58" s="63" t="n">
+        <v>37900</v>
+      </c>
+      <c r="H58" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I58" s="55" t="n"/>
       <c r="J58" s="55" t="n"/>
-      <c r="K58" s="55" t="n"/>
+      <c r="K58" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L58" s="58" t="n"/>
       <c r="M58" s="55" t="n"/>
     </row>
@@ -46945,6 +47275,14 @@
         <v/>
       </c>
       <c r="M504" s="55" t="n"/>
+    </row>
+    <row r="505">
+      <c r="B505" s="128" t="n"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:M504"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q564"/>
+  <dimension ref="A1:Q565"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -24041,33 +24041,93 @@
       </c>
     </row>
     <row r="564">
-      <c r="A564" s="60" t="inlineStr">
+      <c r="A564" t="n">
+        <v>558</v>
+      </c>
+      <c r="B564" s="128" t="n">
+        <v>46256</v>
+      </c>
+      <c r="C564">
+        <f>IF(B564="","",TEXT(B564,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>Bricks</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Brick delivery — tractor 21-27 (10,500 bricks @ ₹8.5)</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>Brick Company</t>
+        </is>
+      </c>
+      <c r="I564" t="n">
+        <v>10500</v>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K564" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L564">
+        <f>I564*K564</f>
+        <v/>
+      </c>
+      <c r="N564">
+        <f>M564*L564</f>
+        <v/>
+      </c>
+      <c r="O564">
+        <f>IF(L564="","",IF(M564="",L564,L564*(1-M564)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B564" s="60" t="n"/>
-      <c r="C564" s="60" t="n"/>
-      <c r="D564" s="60" t="n"/>
-      <c r="E564" s="60" t="n"/>
-      <c r="F564" s="60" t="n"/>
-      <c r="G564" s="60" t="n"/>
-      <c r="H564" s="60" t="n"/>
-      <c r="I564" s="60" t="n"/>
-      <c r="J564" s="60" t="n"/>
-      <c r="K564" s="60" t="n"/>
-      <c r="L564" s="61">
-        <f>SUM(L5:L563)</f>
-        <v/>
-      </c>
-      <c r="M564" s="60" t="n"/>
-      <c r="N564" s="60" t="n"/>
-      <c r="O564" s="61">
+      <c r="B565" s="60" t="n"/>
+      <c r="C565" s="60" t="n"/>
+      <c r="D565" s="60" t="n"/>
+      <c r="E565" s="60" t="n"/>
+      <c r="F565" s="60" t="n"/>
+      <c r="G565" s="60" t="n"/>
+      <c r="H565" s="60" t="n"/>
+      <c r="I565" s="60" t="n"/>
+      <c r="J565" s="60" t="n"/>
+      <c r="K565" s="60" t="n"/>
+      <c r="L565" s="61">
+        <f>SUM(L5:L564)</f>
+        <v/>
+      </c>
+      <c r="M565" s="60" t="n"/>
+      <c r="N565" s="60" t="n"/>
+      <c r="O565" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P564" s="60" t="n"/>
-      <c r="Q564" s="60" t="n"/>
+      <c r="P565" s="60" t="n"/>
+      <c r="Q565" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6453,7 +6453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q565"/>
+  <dimension ref="A1:Q568"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -24101,33 +24101,213 @@
       </c>
     </row>
     <row r="565">
-      <c r="A565" s="60" t="inlineStr">
+      <c r="A565" t="n">
+        <v>559</v>
+      </c>
+      <c r="B565" s="128" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C565">
+        <f>IF(B565="","",TEXT(B565,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Ultratech Super cement 30 bags @ ₹340</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I565" t="n">
+        <v>30</v>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K565" t="n">
+        <v>340</v>
+      </c>
+      <c r="L565">
+        <f>I565*K565</f>
+        <v/>
+      </c>
+      <c r="N565">
+        <f>M565*L565</f>
+        <v/>
+      </c>
+      <c r="O565">
+        <f>IF(L565="","",IF(M565="",L565,L565*(1-M565)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="n">
+        <v>560</v>
+      </c>
+      <c r="B566" s="128" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C566">
+        <f>IF(B566="","",TEXT(B566,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Ultratech Plain cement 20 bags @ ₹320</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I566" t="n">
+        <v>20</v>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K566" t="n">
+        <v>320</v>
+      </c>
+      <c r="L566">
+        <f>I566*K566</f>
+        <v/>
+      </c>
+      <c r="N566">
+        <f>M566*L566</f>
+        <v/>
+      </c>
+      <c r="O566">
+        <f>IF(L566="","",IF(M566="",L566,L566*(1-M566)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="n">
+        <v>561</v>
+      </c>
+      <c r="B567" s="128" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C567">
+        <f>IF(B567="","",TEXT(B567,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I567" t="n">
+        <v>1</v>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>Service</t>
+        </is>
+      </c>
+      <c r="K567" t="n">
+        <v>500</v>
+      </c>
+      <c r="L567">
+        <f>I567*K567</f>
+        <v/>
+      </c>
+      <c r="N567">
+        <f>M567*L567</f>
+        <v/>
+      </c>
+      <c r="O567">
+        <f>IF(L567="","",IF(M567="",L567,L567*(1-M567)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B565" s="60" t="n"/>
-      <c r="C565" s="60" t="n"/>
-      <c r="D565" s="60" t="n"/>
-      <c r="E565" s="60" t="n"/>
-      <c r="F565" s="60" t="n"/>
-      <c r="G565" s="60" t="n"/>
-      <c r="H565" s="60" t="n"/>
-      <c r="I565" s="60" t="n"/>
-      <c r="J565" s="60" t="n"/>
-      <c r="K565" s="60" t="n"/>
-      <c r="L565" s="61">
-        <f>SUM(L5:L564)</f>
-        <v/>
-      </c>
-      <c r="M565" s="60" t="n"/>
-      <c r="N565" s="60" t="n"/>
-      <c r="O565" s="61">
+      <c r="B568" s="60" t="n"/>
+      <c r="C568" s="60" t="n"/>
+      <c r="D568" s="60" t="n"/>
+      <c r="E568" s="60" t="n"/>
+      <c r="F568" s="60" t="n"/>
+      <c r="G568" s="60" t="n"/>
+      <c r="H568" s="60" t="n"/>
+      <c r="I568" s="60" t="n"/>
+      <c r="J568" s="60" t="n"/>
+      <c r="K568" s="60" t="n"/>
+      <c r="L568" s="61">
+        <f>SUM(L5:L567)</f>
+        <v/>
+      </c>
+      <c r="M568" s="60" t="n"/>
+      <c r="N568" s="60" t="n"/>
+      <c r="O568" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P565" s="60" t="n"/>
-      <c r="Q565" s="60" t="n"/>
+      <c r="P568" s="60" t="n"/>
+      <c r="Q568" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -38622,17 +38802,47 @@
       <c r="M58" s="55" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="99">
-      <c r="A59" s="41" t="n"/>
-      <c r="B59" s="45" t="n"/>
-      <c r="C59" s="47" t="n"/>
-      <c r="D59" s="47" t="n"/>
-      <c r="E59" s="47" t="n"/>
-      <c r="F59" s="47" t="n"/>
-      <c r="G59" s="62" t="n"/>
-      <c r="H59" s="47" t="n"/>
+      <c r="A59" s="41" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="45" t="n">
+        <v>46258</v>
+      </c>
+      <c r="C59" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D59" s="47" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E59" s="47" t="inlineStr">
+        <is>
+          <t>Building Materials + Labour</t>
+        </is>
+      </c>
+      <c r="F59" s="47" t="inlineStr">
+        <is>
+          <t>Ultratech Super + Plain cement, labour</t>
+        </is>
+      </c>
+      <c r="G59" s="62" t="n">
+        <v>17100</v>
+      </c>
+      <c r="H59" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I59" s="47" t="n"/>
       <c r="J59" s="47" t="n"/>
-      <c r="K59" s="47" t="n"/>
+      <c r="K59" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L59" s="50" t="n"/>
       <c r="M59" s="47" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -16,6 +16,7 @@
     <sheet name="Labour Tracker" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Monthly Summary" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Vendor Summary" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Unit Funding" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'All Transactions'!$A$4:$Q$504</definedName>
@@ -2938,6 +2939,91 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" style="99" min="1" max="1"/>
+    <col width="8" customWidth="1" style="99" min="2" max="2"/>
+    <col width="16" customWidth="1" style="99" min="3" max="3"/>
+    <col width="40" customWidth="1" style="99" min="4" max="4"/>
+    <col width="60" customWidth="1" style="99" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>UNIT FUNDING — B-Unit / C-Unit cost split &amp; external funder commitments</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>All spend is split 50/50 between B-Unit and C-Unit unless a transaction is explicitly tagged to one unit.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Funder</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Commitment ₹</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Family-funded threshold ₹ (kicks in after this much unit spend)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Deepu</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Avinash funds first ₹10L of C-Unit spend; Deepu funds the next ₹15L of C-Unit spend beyond that</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6453,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q568"/>
+  <dimension ref="A1:R568"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -6472,6 +6558,7 @@
     <col width="14" customWidth="1" style="99" min="15" max="15"/>
     <col width="18" customWidth="1" style="99" min="16" max="16"/>
     <col width="14" customWidth="1" style="99" min="17" max="17"/>
+    <col width="30" customWidth="1" style="99" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="17.25" customHeight="1" s="99">
@@ -6572,6 +6659,11 @@
       <c r="Q4" s="40" t="inlineStr">
         <is>
           <t>Payment Mode</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Building Unit (B/C, blank=joint 50/50)</t>
         </is>
       </c>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R568"/>
+  <dimension ref="A1:R569"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -24373,33 +24373,93 @@
       </c>
     </row>
     <row r="568">
-      <c r="A568" s="60" t="inlineStr">
+      <c r="A568" t="n">
+        <v>562</v>
+      </c>
+      <c r="B568" s="128" t="n">
+        <v>46257</v>
+      </c>
+      <c r="C568">
+        <f>IF(B568="","",TEXT(B568,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>Bricks</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Brick delivery — tractor 28-29 (3,000 bricks @ ₹8.5)</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>Brick Company</t>
+        </is>
+      </c>
+      <c r="I568" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K568" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L568">
+        <f>I568*K568</f>
+        <v/>
+      </c>
+      <c r="N568">
+        <f>M568*L568</f>
+        <v/>
+      </c>
+      <c r="O568">
+        <f>IF(L568="","",IF(M568="",L568,L568*(1-M568)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B568" s="60" t="n"/>
-      <c r="C568" s="60" t="n"/>
-      <c r="D568" s="60" t="n"/>
-      <c r="E568" s="60" t="n"/>
-      <c r="F568" s="60" t="n"/>
-      <c r="G568" s="60" t="n"/>
-      <c r="H568" s="60" t="n"/>
-      <c r="I568" s="60" t="n"/>
-      <c r="J568" s="60" t="n"/>
-      <c r="K568" s="60" t="n"/>
-      <c r="L568" s="61">
-        <f>SUM(L5:L567)</f>
-        <v/>
-      </c>
-      <c r="M568" s="60" t="n"/>
-      <c r="N568" s="60" t="n"/>
-      <c r="O568" s="61">
+      <c r="B569" s="60" t="n"/>
+      <c r="C569" s="60" t="n"/>
+      <c r="D569" s="60" t="n"/>
+      <c r="E569" s="60" t="n"/>
+      <c r="F569" s="60" t="n"/>
+      <c r="G569" s="60" t="n"/>
+      <c r="H569" s="60" t="n"/>
+      <c r="I569" s="60" t="n"/>
+      <c r="J569" s="60" t="n"/>
+      <c r="K569" s="60" t="n"/>
+      <c r="L569" s="61">
+        <f>SUM(L5:L568)</f>
+        <v/>
+      </c>
+      <c r="M569" s="60" t="n"/>
+      <c r="N569" s="60" t="n"/>
+      <c r="O569" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P568" s="60" t="n"/>
-      <c r="Q568" s="60" t="n"/>
+      <c r="P569" s="60" t="n"/>
+      <c r="Q569" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -23380,7 +23380,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>Ultratech Premium Cement 20 bags @ ₹330</t>
+          <t>Ultratech Super Cement 20 bags @ ₹330</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6832,7 +6832,7 @@
       </c>
       <c r="F7" s="47" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Super</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="G7" s="47" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="F34" s="55" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Super</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="G34" s="55" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="F44" s="55" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Super</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="G44" s="55" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="F57" s="55" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Super</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="G57" s="55" t="inlineStr">
@@ -10732,7 +10732,7 @@
       </c>
       <c r="F63" s="55" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Super</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="G63" s="55" t="inlineStr">

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -21287,15 +21287,15 @@
         </is>
       </c>
       <c r="I517" t="n">
-        <v>1</v>
+        <v>944</v>
       </c>
       <c r="J517" t="inlineStr">
         <is>
-          <t>Lumpsum</t>
+          <t>CFT</t>
         </is>
       </c>
       <c r="K517" t="n">
-        <v>56500</v>
+        <v>59.85169491525424</v>
       </c>
       <c r="L517">
         <f>IF(OR(I517="",K517=""),"",I517*K517)</f>
@@ -21343,15 +21343,15 @@
         </is>
       </c>
       <c r="I518" t="n">
-        <v>1</v>
+        <v>936</v>
       </c>
       <c r="J518" t="inlineStr">
         <is>
-          <t>Lumpsum</t>
+          <t>CFT</t>
         </is>
       </c>
       <c r="K518" t="n">
-        <v>56000</v>
+        <v>59.82905982905983</v>
       </c>
       <c r="L518">
         <f>IF(OR(I518="",K518=""),"",I518*K518)</f>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R569"/>
+  <dimension ref="A1:R572"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -24433,33 +24433,213 @@
       </c>
     </row>
     <row r="569">
-      <c r="A569" s="60" t="inlineStr">
+      <c r="A569" t="n">
+        <v>563</v>
+      </c>
+      <c r="B569" s="128" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C569">
+        <f>IF(B569="","",TEXT(B569,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Ultratech Super cement 12 bags @ ₹340</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I569" t="n">
+        <v>12</v>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K569" t="n">
+        <v>340</v>
+      </c>
+      <c r="L569">
+        <f>I569*K569</f>
+        <v/>
+      </c>
+      <c r="N569">
+        <f>M569*L569</f>
+        <v/>
+      </c>
+      <c r="O569">
+        <f>IF(L569="","",IF(M569="",L569,L569*(1-M569)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="n">
+        <v>564</v>
+      </c>
+      <c r="B570" s="128" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C570">
+        <f>IF(B570="","",TEXT(B570,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Ultratech Plain cement 24 bags @ ₹320</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I570" t="n">
+        <v>24</v>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K570" t="n">
+        <v>320</v>
+      </c>
+      <c r="L570">
+        <f>I570*K570</f>
+        <v/>
+      </c>
+      <c r="N570">
+        <f>M570*L570</f>
+        <v/>
+      </c>
+      <c r="O570">
+        <f>IF(L570="","",IF(M570="",L570,L570*(1-M570)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="n">
+        <v>565</v>
+      </c>
+      <c r="B571" s="128" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C571">
+        <f>IF(B571="","",TEXT(B571,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>Material Transport</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Cement transportation</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I571" t="n">
+        <v>1</v>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>Trip</t>
+        </is>
+      </c>
+      <c r="K571" t="n">
+        <v>450</v>
+      </c>
+      <c r="L571">
+        <f>I571*K571</f>
+        <v/>
+      </c>
+      <c r="N571">
+        <f>M571*L571</f>
+        <v/>
+      </c>
+      <c r="O571">
+        <f>IF(L571="","",IF(M571="",L571,L571*(1-M571)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B569" s="60" t="n"/>
-      <c r="C569" s="60" t="n"/>
-      <c r="D569" s="60" t="n"/>
-      <c r="E569" s="60" t="n"/>
-      <c r="F569" s="60" t="n"/>
-      <c r="G569" s="60" t="n"/>
-      <c r="H569" s="60" t="n"/>
-      <c r="I569" s="60" t="n"/>
-      <c r="J569" s="60" t="n"/>
-      <c r="K569" s="60" t="n"/>
-      <c r="L569" s="61">
-        <f>SUM(L5:L568)</f>
-        <v/>
-      </c>
-      <c r="M569" s="60" t="n"/>
-      <c r="N569" s="60" t="n"/>
-      <c r="O569" s="61">
+      <c r="B572" s="60" t="n"/>
+      <c r="C572" s="60" t="n"/>
+      <c r="D572" s="60" t="n"/>
+      <c r="E572" s="60" t="n"/>
+      <c r="F572" s="60" t="n"/>
+      <c r="G572" s="60" t="n"/>
+      <c r="H572" s="60" t="n"/>
+      <c r="I572" s="60" t="n"/>
+      <c r="J572" s="60" t="n"/>
+      <c r="K572" s="60" t="n"/>
+      <c r="L572" s="61">
+        <f>SUM(L5:L571)</f>
+        <v/>
+      </c>
+      <c r="M572" s="60" t="n"/>
+      <c r="N572" s="60" t="n"/>
+      <c r="O572" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P569" s="60" t="n"/>
-      <c r="Q569" s="60" t="n"/>
+      <c r="P572" s="60" t="n"/>
+      <c r="Q572" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -38999,17 +39179,47 @@
       <c r="M59" s="47" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="99">
-      <c r="A60" s="43" t="n"/>
-      <c r="B60" s="53" t="n"/>
-      <c r="C60" s="55" t="n"/>
-      <c r="D60" s="55" t="n"/>
-      <c r="E60" s="55" t="n"/>
-      <c r="F60" s="55" t="n"/>
-      <c r="G60" s="63" t="n"/>
-      <c r="H60" s="55" t="n"/>
+      <c r="A60" s="43" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="53" t="n">
+        <v>46270</v>
+      </c>
+      <c r="C60" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D60" s="55" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E60" s="55" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F60" s="55" t="inlineStr">
+        <is>
+          <t>Ultratech Super+Plain cement, transport</t>
+        </is>
+      </c>
+      <c r="G60" s="63" t="n">
+        <v>12210</v>
+      </c>
+      <c r="H60" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I60" s="55" t="n"/>
       <c r="J60" s="55" t="n"/>
-      <c r="K60" s="55" t="n"/>
+      <c r="K60" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L60" s="58" t="n"/>
       <c r="M60" s="55" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -39224,17 +39224,47 @@
       <c r="M60" s="55" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="99">
-      <c r="A61" s="41" t="n"/>
-      <c r="B61" s="45" t="n"/>
-      <c r="C61" s="47" t="n"/>
-      <c r="D61" s="47" t="n"/>
-      <c r="E61" s="47" t="n"/>
-      <c r="F61" s="47" t="n"/>
-      <c r="G61" s="62" t="n"/>
-      <c r="H61" s="47" t="n"/>
+      <c r="A61" s="41" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="45" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C61" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D61" s="47" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E61" s="47" t="inlineStr">
+        <is>
+          <t>Advance</t>
+        </is>
+      </c>
+      <c r="F61" s="47" t="inlineStr">
+        <is>
+          <t>Advance for upcoming work — to be adjusted against future bills</t>
+        </is>
+      </c>
+      <c r="G61" s="62" t="n">
+        <v>100000</v>
+      </c>
+      <c r="H61" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I61" s="47" t="n"/>
       <c r="J61" s="47" t="n"/>
-      <c r="K61" s="47" t="n"/>
+      <c r="K61" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L61" s="50" t="n"/>
       <c r="M61" s="47" t="n"/>
     </row>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -1466,7 +1466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -2466,7 +2466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" style="99" min="1" max="1"/>
     <col width="12" customWidth="1" style="99" min="2" max="2"/>
@@ -2946,7 +2946,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
     <col width="8" customWidth="1" style="99" min="2" max="2"/>
@@ -3032,7 +3032,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="2" customWidth="1" style="99" min="1" max="1"/>
     <col width="18" customWidth="1" style="99" min="2" max="2"/>
@@ -5053,7 +5053,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -6539,8 +6539,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R572"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <dimension ref="A1:R573"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -24613,33 +24613,93 @@
       </c>
     </row>
     <row r="572">
-      <c r="A572" s="60" t="inlineStr">
+      <c r="A572" t="n">
+        <v>566</v>
+      </c>
+      <c r="B572" s="128" t="n">
+        <v>46277</v>
+      </c>
+      <c r="C572">
+        <f>IF(B572="","",TEXT(B572,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>Engineer Supervision</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Construction work done — general site supervision &amp; labour (Sep)</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I572" t="n">
+        <v>1</v>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K572" t="n">
+        <v>100000</v>
+      </c>
+      <c r="L572">
+        <f>I572*K572</f>
+        <v/>
+      </c>
+      <c r="N572">
+        <f>M572*L572</f>
+        <v/>
+      </c>
+      <c r="O572">
+        <f>IF(L572="","",IF(M572="",L572,L572*(1-M572)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B572" s="60" t="n"/>
-      <c r="C572" s="60" t="n"/>
-      <c r="D572" s="60" t="n"/>
-      <c r="E572" s="60" t="n"/>
-      <c r="F572" s="60" t="n"/>
-      <c r="G572" s="60" t="n"/>
-      <c r="H572" s="60" t="n"/>
-      <c r="I572" s="60" t="n"/>
-      <c r="J572" s="60" t="n"/>
-      <c r="K572" s="60" t="n"/>
-      <c r="L572" s="61">
-        <f>SUM(L5:L571)</f>
-        <v/>
-      </c>
-      <c r="M572" s="60" t="n"/>
-      <c r="N572" s="60" t="n"/>
-      <c r="O572" s="61">
+      <c r="B573" s="60" t="n"/>
+      <c r="C573" s="60" t="n"/>
+      <c r="D573" s="60" t="n"/>
+      <c r="E573" s="60" t="n"/>
+      <c r="F573" s="60" t="n"/>
+      <c r="G573" s="60" t="n"/>
+      <c r="H573" s="60" t="n"/>
+      <c r="I573" s="60" t="n"/>
+      <c r="J573" s="60" t="n"/>
+      <c r="K573" s="60" t="n"/>
+      <c r="L573" s="61">
+        <f>SUM(L5:L572)</f>
+        <v/>
+      </c>
+      <c r="M573" s="60" t="n"/>
+      <c r="N573" s="60" t="n"/>
+      <c r="O573" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P572" s="60" t="n"/>
-      <c r="Q572" s="60" t="n"/>
+      <c r="P573" s="60" t="n"/>
+      <c r="Q573" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -24682,7 +24742,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O504"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -36589,7 +36649,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M505"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -39242,12 +39302,12 @@
       </c>
       <c r="E61" s="47" t="inlineStr">
         <is>
-          <t>Advance</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F61" s="47" t="inlineStr">
         <is>
-          <t>Advance for upcoming work — to be adjusted against future bills</t>
+          <t>Construction work done — general site supervision &amp; labour (Sep)</t>
         </is>
       </c>
       <c r="G61" s="62" t="n">
@@ -47987,7 +48047,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -49331,7 +49391,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J504"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="3"/>
@@ -58005,7 +58065,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
     <col width="18" customWidth="1" style="99" min="2" max="2"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -1466,7 +1466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="3" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -2466,7 +2466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="26" customWidth="1" style="99" min="1" max="1"/>
     <col width="12" customWidth="1" style="99" min="2" max="2"/>
@@ -2946,7 +2946,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
     <col width="8" customWidth="1" style="99" min="2" max="2"/>
@@ -3032,7 +3032,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="2" customWidth="1" style="99" min="1" max="1"/>
     <col width="18" customWidth="1" style="99" min="2" max="2"/>
@@ -5053,7 +5053,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -6539,8 +6539,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R606"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <dimension ref="A1:R607"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -30487,33 +30487,93 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" s="60" t="inlineStr">
+      <c r="A606" t="n">
+        <v>614</v>
+      </c>
+      <c r="B606" s="128" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C606">
+        <f>IF(B606="","",TEXT(B606,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>Sand Truck — 944 CFT @ ₹60.59/CFT</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Sand Truck Wala</t>
+        </is>
+      </c>
+      <c r="I606" t="n">
+        <v>944</v>
+      </c>
+      <c r="J606" t="inlineStr">
+        <is>
+          <t>CFT</t>
+        </is>
+      </c>
+      <c r="K606" t="n">
+        <v>60.59322033898305</v>
+      </c>
+      <c r="L606">
+        <f>IF(OR(I606="",K606=""),"",I606*K606)</f>
+        <v/>
+      </c>
+      <c r="N606">
+        <f>M606*L606</f>
+        <v/>
+      </c>
+      <c r="O606">
+        <f>IF(L606="","",IF(M606="",L606,L606*(1-M606)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B606" s="60" t="n"/>
-      <c r="C606" s="60" t="n"/>
-      <c r="D606" s="60" t="n"/>
-      <c r="E606" s="60" t="n"/>
-      <c r="F606" s="60" t="n"/>
-      <c r="G606" s="60" t="n"/>
-      <c r="H606" s="60" t="n"/>
-      <c r="I606" s="60" t="n"/>
-      <c r="J606" s="60" t="n"/>
-      <c r="K606" s="60" t="n"/>
-      <c r="L606" s="61">
-        <f>SUM(L5:L605)</f>
-        <v/>
-      </c>
-      <c r="M606" s="60" t="n"/>
-      <c r="N606" s="60" t="n"/>
-      <c r="O606" s="61">
+      <c r="B607" s="60" t="n"/>
+      <c r="C607" s="60" t="n"/>
+      <c r="D607" s="60" t="n"/>
+      <c r="E607" s="60" t="n"/>
+      <c r="F607" s="60" t="n"/>
+      <c r="G607" s="60" t="n"/>
+      <c r="H607" s="60" t="n"/>
+      <c r="I607" s="60" t="n"/>
+      <c r="J607" s="60" t="n"/>
+      <c r="K607" s="60" t="n"/>
+      <c r="L607" s="61">
+        <f>SUM(L5:L606)</f>
+        <v/>
+      </c>
+      <c r="M607" s="60" t="n"/>
+      <c r="N607" s="60" t="n"/>
+      <c r="O607" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P606" s="60" t="n"/>
-      <c r="Q606" s="60" t="n"/>
+      <c r="P607" s="60" t="n"/>
+      <c r="Q607" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -30556,7 +30616,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O504"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -42463,7 +42523,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M495"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -46832,16 +46892,44 @@
       <c r="A99" s="41" t="n">
         <v>105</v>
       </c>
-      <c r="B99" s="45" t="n"/>
-      <c r="C99" s="47" t="n"/>
-      <c r="D99" s="47" t="n"/>
-      <c r="E99" s="47" t="n"/>
-      <c r="F99" s="47" t="n"/>
-      <c r="G99" s="62" t="n"/>
-      <c r="H99" s="47" t="n"/>
+      <c r="B99" s="45" t="n">
+        <v>46287</v>
+      </c>
+      <c r="C99" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D99" s="47" t="inlineStr">
+        <is>
+          <t>Sand Truck Wala</t>
+        </is>
+      </c>
+      <c r="E99" s="47" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F99" s="47" t="inlineStr">
+        <is>
+          <t>Sand Truck — 944 CFT</t>
+        </is>
+      </c>
+      <c r="G99" s="62" t="n">
+        <v>57200</v>
+      </c>
+      <c r="H99" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I99" s="47" t="n"/>
       <c r="J99" s="47" t="n"/>
-      <c r="K99" s="47" t="n"/>
+      <c r="K99" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L99" s="50">
         <f>IF(G109="","",IF(L108="",G109,L108+G109))</f>
         <v/>
@@ -54806,7 +54894,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -56150,7 +56238,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J504"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="3"/>
@@ -64824,7 +64912,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
     <col width="18" customWidth="1" style="99" min="2" max="2"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -1466,7 +1466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D110"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -2466,7 +2466,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="99" min="1" max="1"/>
     <col width="12" customWidth="1" style="99" min="2" max="2"/>
@@ -2946,7 +2946,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
     <col width="8" customWidth="1" style="99" min="2" max="2"/>
@@ -3032,7 +3032,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N64"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" style="99" min="1" max="1"/>
     <col width="18" customWidth="1" style="99" min="2" max="2"/>
@@ -5053,7 +5053,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N48"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -6539,8 +6539,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R607"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <dimension ref="A1:R609"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -30547,33 +30547,153 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" s="60" t="inlineStr">
+      <c r="A607" t="n">
+        <v>615</v>
+      </c>
+      <c r="B607" s="128" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C607">
+        <f>IF(B607="","",TEXT(B607,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F607" t="inlineStr">
+        <is>
+          <t>Engineer Supervision</t>
+        </is>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>Construction work done — general site supervision &amp; labour (Papa, 28-Sep)</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I607" t="n">
+        <v>1</v>
+      </c>
+      <c r="J607" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K607" t="n">
+        <v>50000</v>
+      </c>
+      <c r="L607">
+        <f>IF(OR(I607="",K607=""),"",I607*K607)</f>
+        <v/>
+      </c>
+      <c r="N607">
+        <f>M607*L607</f>
+        <v/>
+      </c>
+      <c r="O607">
+        <f>IF(L607="","",IF(M607="",L607,L607*(1-M607)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="n">
+        <v>616</v>
+      </c>
+      <c r="B608" s="128" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C608">
+        <f>IF(B608="","",TEXT(B608,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F608" t="inlineStr">
+        <is>
+          <t>Concrete/Gitti</t>
+        </is>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>Gitti delivery (qty not recorded)</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="I608" t="n">
+        <v>1</v>
+      </c>
+      <c r="J608" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K608" t="n">
+        <v>79500</v>
+      </c>
+      <c r="L608">
+        <f>IF(OR(I608="",K608=""),"",I608*K608)</f>
+        <v/>
+      </c>
+      <c r="N608">
+        <f>M608*L608</f>
+        <v/>
+      </c>
+      <c r="O608">
+        <f>IF(L608="","",IF(M608="",L608,L608*(1-M608)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B607" s="60" t="n"/>
-      <c r="C607" s="60" t="n"/>
-      <c r="D607" s="60" t="n"/>
-      <c r="E607" s="60" t="n"/>
-      <c r="F607" s="60" t="n"/>
-      <c r="G607" s="60" t="n"/>
-      <c r="H607" s="60" t="n"/>
-      <c r="I607" s="60" t="n"/>
-      <c r="J607" s="60" t="n"/>
-      <c r="K607" s="60" t="n"/>
-      <c r="L607" s="61">
-        <f>SUM(L5:L606)</f>
-        <v/>
-      </c>
-      <c r="M607" s="60" t="n"/>
-      <c r="N607" s="60" t="n"/>
-      <c r="O607" s="61">
+      <c r="B609" s="60" t="n"/>
+      <c r="C609" s="60" t="n"/>
+      <c r="D609" s="60" t="n"/>
+      <c r="E609" s="60" t="n"/>
+      <c r="F609" s="60" t="n"/>
+      <c r="G609" s="60" t="n"/>
+      <c r="H609" s="60" t="n"/>
+      <c r="I609" s="60" t="n"/>
+      <c r="J609" s="60" t="n"/>
+      <c r="K609" s="60" t="n"/>
+      <c r="L609" s="61">
+        <f>SUM(L5:L608)</f>
+        <v/>
+      </c>
+      <c r="M609" s="60" t="n"/>
+      <c r="N609" s="60" t="n"/>
+      <c r="O609" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P607" s="60" t="n"/>
-      <c r="Q607" s="60" t="n"/>
+      <c r="P609" s="60" t="n"/>
+      <c r="Q609" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -30616,7 +30736,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:O504"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -42523,7 +42643,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:M495"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="2"/>
@@ -46940,16 +47060,44 @@
       <c r="A100" s="43" t="n">
         <v>106</v>
       </c>
-      <c r="B100" s="53" t="n"/>
-      <c r="C100" s="55" t="n"/>
-      <c r="D100" s="55" t="n"/>
-      <c r="E100" s="55" t="n"/>
-      <c r="F100" s="55" t="n"/>
-      <c r="G100" s="63" t="n"/>
-      <c r="H100" s="55" t="n"/>
+      <c r="B100" s="53" t="n">
+        <v>46293</v>
+      </c>
+      <c r="C100" s="55" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D100" s="55" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E100" s="55" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F100" s="55" t="inlineStr">
+        <is>
+          <t>Construction work done — general (Papa, 28-Sep)</t>
+        </is>
+      </c>
+      <c r="G100" s="63" t="n">
+        <v>50000</v>
+      </c>
+      <c r="H100" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I100" s="55" t="n"/>
       <c r="J100" s="55" t="n"/>
-      <c r="K100" s="55" t="n"/>
+      <c r="K100" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L100" s="58">
         <f>IF(G110="","",IF(L109="",G110,L109+G110))</f>
         <v/>
@@ -46960,16 +47108,44 @@
       <c r="A101" s="41" t="n">
         <v>107</v>
       </c>
-      <c r="B101" s="45" t="n"/>
-      <c r="C101" s="47" t="n"/>
-      <c r="D101" s="47" t="n"/>
-      <c r="E101" s="47" t="n"/>
-      <c r="F101" s="47" t="n"/>
-      <c r="G101" s="62" t="n"/>
-      <c r="H101" s="47" t="n"/>
+      <c r="B101" s="45" t="n">
+        <v>46296</v>
+      </c>
+      <c r="C101" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D101" s="47" t="inlineStr">
+        <is>
+          <t>Concrete Supplier</t>
+        </is>
+      </c>
+      <c r="E101" s="47" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F101" s="47" t="inlineStr">
+        <is>
+          <t>Gitti delivery</t>
+        </is>
+      </c>
+      <c r="G101" s="62" t="n">
+        <v>79500</v>
+      </c>
+      <c r="H101" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I101" s="47" t="n"/>
       <c r="J101" s="47" t="n"/>
-      <c r="K101" s="47" t="n"/>
+      <c r="K101" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L101" s="50">
         <f>IF(G111="","",IF(L110="",G111,L110+G111))</f>
         <v/>
@@ -54894,7 +55070,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:I35"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
     <col width="28" customWidth="1" style="99" min="2" max="2"/>
@@ -56238,7 +56414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:J504"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
     <col width="14" customWidth="1" style="99" min="2" max="3"/>
@@ -64912,7 +65088,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:K29"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" outlineLevelCol="0"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
     <col width="18" customWidth="1" style="99" min="2" max="2"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R609"/>
+  <dimension ref="A1:R630"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -30667,33 +30667,1293 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" s="60" t="inlineStr">
+      <c r="A609" t="n">
+        <v>617</v>
+      </c>
+      <c r="B609" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C609">
+        <f>IF(B609="","",TEXT(B609,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F609" t="inlineStr">
+        <is>
+          <t>Tiscon 16mm</t>
+        </is>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>Tiscon 16mm rod 6 pcs</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I609" t="n">
+        <v>6</v>
+      </c>
+      <c r="J609" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K609" t="n">
+        <v>1459.166666666667</v>
+      </c>
+      <c r="L609">
+        <f>IF(OR(I609="",K609=""),"",I609*K609)</f>
+        <v/>
+      </c>
+      <c r="N609">
+        <f>M609*L609</f>
+        <v/>
+      </c>
+      <c r="O609">
+        <f>IF(L609="","",IF(M609="",L609,L609*(1-M609)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="n">
+        <v>618</v>
+      </c>
+      <c r="B610" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C610">
+        <f>IF(B610="","",TEXT(B610,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F610" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm</t>
+        </is>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm rod 50 pcs</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I610" t="n">
+        <v>50</v>
+      </c>
+      <c r="J610" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K610" t="n">
+        <v>819.84</v>
+      </c>
+      <c r="L610">
+        <f>IF(OR(I610="",K610=""),"",I610*K610)</f>
+        <v/>
+      </c>
+      <c r="N610">
+        <f>M610*L610</f>
+        <v/>
+      </c>
+      <c r="O610">
+        <f>IF(L610="","",IF(M610="",L610,L610*(1-M610)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="n">
+        <v>619</v>
+      </c>
+      <c r="B611" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C611">
+        <f>IF(B611="","",TEXT(B611,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm</t>
+        </is>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm rod 260 pcs</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I611" t="n">
+        <v>260</v>
+      </c>
+      <c r="J611" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K611" t="n">
+        <v>580.8</v>
+      </c>
+      <c r="L611">
+        <f>IF(OR(I611="",K611=""),"",I611*K611)</f>
+        <v/>
+      </c>
+      <c r="N611">
+        <f>M611*L611</f>
+        <v/>
+      </c>
+      <c r="O611">
+        <f>IF(L611="","",IF(M611="",L611,L611*(1-M611)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="n">
+        <v>620</v>
+      </c>
+      <c r="B612" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C612">
+        <f>IF(B612="","",TEXT(B612,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F612" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm</t>
+        </is>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm rod 202 pcs</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I612" t="n">
+        <v>202</v>
+      </c>
+      <c r="J612" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K612" t="n">
+        <v>380.1584158415841</v>
+      </c>
+      <c r="L612">
+        <f>IF(OR(I612="",K612=""),"",I612*K612)</f>
+        <v/>
+      </c>
+      <c r="N612">
+        <f>M612*L612</f>
+        <v/>
+      </c>
+      <c r="O612">
+        <f>IF(L612="","",IF(M612="",L612,L612*(1-M612)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="n">
+        <v>621</v>
+      </c>
+      <c r="B613" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C613">
+        <f>IF(B613="","",TEXT(B613,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F613" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm</t>
+        </is>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm rod 50 pcs</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I613" t="n">
+        <v>50</v>
+      </c>
+      <c r="J613" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K613" t="n">
+        <v>233</v>
+      </c>
+      <c r="L613">
+        <f>IF(OR(I613="",K613=""),"",I613*K613)</f>
+        <v/>
+      </c>
+      <c r="N613">
+        <f>M613*L613</f>
+        <v/>
+      </c>
+      <c r="O613">
+        <f>IF(L613="","",IF(M613="",L613,L613*(1-M613)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="n">
+        <v>622</v>
+      </c>
+      <c r="B614" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C614">
+        <f>IF(B614="","",TEXT(B614,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F614" t="inlineStr">
+        <is>
+          <t>Binding Wire</t>
+        </is>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>Binding wire</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I614" t="n">
+        <v>1</v>
+      </c>
+      <c r="J614" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K614" t="n">
+        <v>1700</v>
+      </c>
+      <c r="L614">
+        <f>IF(OR(I614="",K614=""),"",I614*K614)</f>
+        <v/>
+      </c>
+      <c r="N614">
+        <f>M614*L614</f>
+        <v/>
+      </c>
+      <c r="O614">
+        <f>IF(L614="","",IF(M614="",L614,L614*(1-M614)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="n">
+        <v>623</v>
+      </c>
+      <c r="B615" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C615">
+        <f>IF(B615="","",TEXT(B615,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F615" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>Wire</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I615" t="n">
+        <v>1</v>
+      </c>
+      <c r="J615" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K615" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L615">
+        <f>IF(OR(I615="",K615=""),"",I615*K615)</f>
+        <v/>
+      </c>
+      <c r="N615">
+        <f>M615*L615</f>
+        <v/>
+      </c>
+      <c r="O615">
+        <f>IF(L615="","",IF(M615="",L615,L615*(1-M615)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="n">
+        <v>624</v>
+      </c>
+      <c r="B616" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C616">
+        <f>IF(B616="","",TEXT(B616,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F616" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I616" t="n">
+        <v>1</v>
+      </c>
+      <c r="J616" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K616" t="n">
+        <v>900</v>
+      </c>
+      <c r="L616">
+        <f>IF(OR(I616="",K616=""),"",I616*K616)</f>
+        <v/>
+      </c>
+      <c r="N616">
+        <f>M616*L616</f>
+        <v/>
+      </c>
+      <c r="O616">
+        <f>IF(L616="","",IF(M616="",L616,L616*(1-M616)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="n">
+        <v>625</v>
+      </c>
+      <c r="B617" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C617">
+        <f>IF(B617="","",TEXT(B617,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F617" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm</t>
+        </is>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm rod 60 pcs</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I617" t="n">
+        <v>60</v>
+      </c>
+      <c r="J617" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K617" t="n">
+        <v>391.6833333333333</v>
+      </c>
+      <c r="L617">
+        <f>IF(OR(I617="",K617=""),"",I617*K617)</f>
+        <v/>
+      </c>
+      <c r="N617">
+        <f>M617*L617</f>
+        <v/>
+      </c>
+      <c r="O617">
+        <f>IF(L617="","",IF(M617="",L617,L617*(1-M617)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="n">
+        <v>626</v>
+      </c>
+      <c r="B618" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C618">
+        <f>IF(B618="","",TEXT(B618,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I618" t="n">
+        <v>1</v>
+      </c>
+      <c r="J618" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K618" t="n">
+        <v>350</v>
+      </c>
+      <c r="L618">
+        <f>IF(OR(I618="",K618=""),"",I618*K618)</f>
+        <v/>
+      </c>
+      <c r="N618">
+        <f>M618*L618</f>
+        <v/>
+      </c>
+      <c r="O618">
+        <f>IF(L618="","",IF(M618="",L618,L618*(1-M618)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="n">
+        <v>627</v>
+      </c>
+      <c r="B619" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C619">
+        <f>IF(B619="","",TEXT(B619,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F619" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm</t>
+        </is>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm rod 24 pcs</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I619" t="n">
+        <v>24</v>
+      </c>
+      <c r="J619" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K619" t="n">
+        <v>240</v>
+      </c>
+      <c r="L619">
+        <f>IF(OR(I619="",K619=""),"",I619*K619)</f>
+        <v/>
+      </c>
+      <c r="N619">
+        <f>M619*L619</f>
+        <v/>
+      </c>
+      <c r="O619">
+        <f>IF(L619="","",IF(M619="",L619,L619*(1-M619)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="n">
+        <v>628</v>
+      </c>
+      <c r="B620" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C620">
+        <f>IF(B620="","",TEXT(B620,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F620" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I620" t="n">
+        <v>1</v>
+      </c>
+      <c r="J620" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K620" t="n">
+        <v>340</v>
+      </c>
+      <c r="L620">
+        <f>IF(OR(I620="",K620=""),"",I620*K620)</f>
+        <v/>
+      </c>
+      <c r="N620">
+        <f>M620*L620</f>
+        <v/>
+      </c>
+      <c r="O620">
+        <f>IF(L620="","",IF(M620="",L620,L620*(1-M620)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="n">
+        <v>629</v>
+      </c>
+      <c r="B621" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C621">
+        <f>IF(B621="","",TEXT(B621,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F621" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm</t>
+        </is>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>Tiscon 6mm rod 48 pcs</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I621" t="n">
+        <v>48</v>
+      </c>
+      <c r="J621" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K621" t="n">
+        <v>240</v>
+      </c>
+      <c r="L621">
+        <f>IF(OR(I621="",K621=""),"",I621*K621)</f>
+        <v/>
+      </c>
+      <c r="N621">
+        <f>M621*L621</f>
+        <v/>
+      </c>
+      <c r="O621">
+        <f>IF(L621="","",IF(M621="",L621,L621*(1-M621)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="n">
+        <v>630</v>
+      </c>
+      <c r="B622" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C622">
+        <f>IF(B622="","",TEXT(B622,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm</t>
+        </is>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm rod 6 pcs</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I622" t="n">
+        <v>6</v>
+      </c>
+      <c r="J622" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K622" t="n">
+        <v>866</v>
+      </c>
+      <c r="L622">
+        <f>IF(OR(I622="",K622=""),"",I622*K622)</f>
+        <v/>
+      </c>
+      <c r="N622">
+        <f>M622*L622</f>
+        <v/>
+      </c>
+      <c r="O622">
+        <f>IF(L622="","",IF(M622="",L622,L622*(1-M622)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="n">
+        <v>631</v>
+      </c>
+      <c r="B623" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C623">
+        <f>IF(B623="","",TEXT(B623,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I623" t="n">
+        <v>1</v>
+      </c>
+      <c r="J623" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K623" t="n">
+        <v>350</v>
+      </c>
+      <c r="L623">
+        <f>IF(OR(I623="",K623=""),"",I623*K623)</f>
+        <v/>
+      </c>
+      <c r="N623">
+        <f>M623*L623</f>
+        <v/>
+      </c>
+      <c r="O623">
+        <f>IF(L623="","",IF(M623="",L623,L623*(1-M623)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="n">
+        <v>632</v>
+      </c>
+      <c r="B624" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C624">
+        <f>IF(B624="","",TEXT(B624,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F624" t="inlineStr">
+        <is>
+          <t>Misc Expense</t>
+        </is>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I624" t="n">
+        <v>1</v>
+      </c>
+      <c r="J624" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K624" t="n">
+        <v>1170</v>
+      </c>
+      <c r="L624">
+        <f>IF(OR(I624="",K624=""),"",I624*K624)</f>
+        <v/>
+      </c>
+      <c r="N624">
+        <f>M624*L624</f>
+        <v/>
+      </c>
+      <c r="O624">
+        <f>IF(L624="","",IF(M624="",L624,L624*(1-M624)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="n">
+        <v>633</v>
+      </c>
+      <c r="B625" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C625">
+        <f>IF(B625="","",TEXT(B625,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F625" t="inlineStr">
+        <is>
+          <t>Rings</t>
+        </is>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>Rings (stirrups)</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I625" t="n">
+        <v>1</v>
+      </c>
+      <c r="J625" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K625" t="n">
+        <v>4040</v>
+      </c>
+      <c r="L625">
+        <f>IF(OR(I625="",K625=""),"",I625*K625)</f>
+        <v/>
+      </c>
+      <c r="N625">
+        <f>M625*L625</f>
+        <v/>
+      </c>
+      <c r="O625">
+        <f>IF(L625="","",IF(M625="",L625,L625*(1-M625)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="n">
+        <v>634</v>
+      </c>
+      <c r="B626" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C626">
+        <f>IF(B626="","",TEXT(B626,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F626" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>Ultratech Weatherplus cement 300 bags @ ₹370</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I626" t="n">
+        <v>300</v>
+      </c>
+      <c r="J626" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K626" t="n">
+        <v>370</v>
+      </c>
+      <c r="L626">
+        <f>IF(OR(I626="",K626=""),"",I626*K626)</f>
+        <v/>
+      </c>
+      <c r="N626">
+        <f>M626*L626</f>
+        <v/>
+      </c>
+      <c r="O626">
+        <f>IF(L626="","",IF(M626="",L626,L626*(1-M626)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="n">
+        <v>635</v>
+      </c>
+      <c r="B627" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C627">
+        <f>IF(B627="","",TEXT(B627,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F627" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I627" t="n">
+        <v>1</v>
+      </c>
+      <c r="J627" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K627" t="n">
+        <v>900</v>
+      </c>
+      <c r="L627">
+        <f>IF(OR(I627="",K627=""),"",I627*K627)</f>
+        <v/>
+      </c>
+      <c r="N627">
+        <f>M627*L627</f>
+        <v/>
+      </c>
+      <c r="O627">
+        <f>IF(L627="","",IF(M627="",L627,L627*(1-M627)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="n">
+        <v>636</v>
+      </c>
+      <c r="B628" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C628">
+        <f>IF(B628="","",TEXT(B628,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F628" t="inlineStr">
+        <is>
+          <t>Misc Expense</t>
+        </is>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>Misc</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I628" t="n">
+        <v>1</v>
+      </c>
+      <c r="J628" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K628" t="n">
+        <v>1200</v>
+      </c>
+      <c r="L628">
+        <f>IF(OR(I628="",K628=""),"",I628*K628)</f>
+        <v/>
+      </c>
+      <c r="N628">
+        <f>M628*L628</f>
+        <v/>
+      </c>
+      <c r="O628">
+        <f>IF(L628="","",IF(M628="",L628,L628*(1-M628)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="n">
+        <v>637</v>
+      </c>
+      <c r="B629" s="128" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C629">
+        <f>IF(B629="","",TEXT(B629,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F629" t="inlineStr">
+        <is>
+          <t>Dr Fixit</t>
+        </is>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>Dr Fixit 40 litres</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I629" t="n">
+        <v>40</v>
+      </c>
+      <c r="J629" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="K629" t="n">
+        <v>140</v>
+      </c>
+      <c r="L629">
+        <f>IF(OR(I629="",K629=""),"",I629*K629)</f>
+        <v/>
+      </c>
+      <c r="N629">
+        <f>M629*L629</f>
+        <v/>
+      </c>
+      <c r="O629">
+        <f>IF(L629="","",IF(M629="",L629,L629*(1-M629)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B609" s="60" t="n"/>
-      <c r="C609" s="60" t="n"/>
-      <c r="D609" s="60" t="n"/>
-      <c r="E609" s="60" t="n"/>
-      <c r="F609" s="60" t="n"/>
-      <c r="G609" s="60" t="n"/>
-      <c r="H609" s="60" t="n"/>
-      <c r="I609" s="60" t="n"/>
-      <c r="J609" s="60" t="n"/>
-      <c r="K609" s="60" t="n"/>
-      <c r="L609" s="61">
-        <f>SUM(L5:L608)</f>
-        <v/>
-      </c>
-      <c r="M609" s="60" t="n"/>
-      <c r="N609" s="60" t="n"/>
-      <c r="O609" s="61">
+      <c r="B630" s="60" t="n"/>
+      <c r="C630" s="60" t="n"/>
+      <c r="D630" s="60" t="n"/>
+      <c r="E630" s="60" t="n"/>
+      <c r="F630" s="60" t="n"/>
+      <c r="G630" s="60" t="n"/>
+      <c r="H630" s="60" t="n"/>
+      <c r="I630" s="60" t="n"/>
+      <c r="J630" s="60" t="n"/>
+      <c r="K630" s="60" t="n"/>
+      <c r="L630" s="61">
+        <f>SUM(L5:L629)</f>
+        <v/>
+      </c>
+      <c r="M630" s="60" t="n"/>
+      <c r="N630" s="60" t="n"/>
+      <c r="O630" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P609" s="60" t="n"/>
-      <c r="Q609" s="60" t="n"/>
+      <c r="P630" s="60" t="n"/>
+      <c r="Q630" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -47156,16 +48416,44 @@
       <c r="A102" s="43" t="n">
         <v>108</v>
       </c>
-      <c r="B102" s="53" t="n"/>
-      <c r="C102" s="55" t="n"/>
-      <c r="D102" s="55" t="n"/>
-      <c r="E102" s="55" t="n"/>
-      <c r="F102" s="55" t="n"/>
-      <c r="G102" s="63" t="n"/>
-      <c r="H102" s="55" t="n"/>
+      <c r="B102" s="53" t="n">
+        <v>46300</v>
+      </c>
+      <c r="C102" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D102" s="55" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E102" s="55" t="inlineStr">
+        <is>
+          <t>Steel / Iron + Cement + Building Materials</t>
+        </is>
+      </c>
+      <c r="F102" s="55" t="inlineStr">
+        <is>
+          <t>Part payment against 5-Oct bill (₹4,66,024)</t>
+        </is>
+      </c>
+      <c r="G102" s="63" t="n">
+        <v>450000</v>
+      </c>
+      <c r="H102" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I102" s="55" t="n"/>
       <c r="J102" s="55" t="n"/>
-      <c r="K102" s="55" t="n"/>
+      <c r="K102" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L102" s="58">
         <f>IF(G112="","",IF(L111="",G112,L111+G112))</f>
         <v/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R630"/>
+  <dimension ref="A1:R633"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -31927,33 +31927,213 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" s="60" t="inlineStr">
+      <c r="A630" t="n">
+        <v>638</v>
+      </c>
+      <c r="B630" s="128" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C630">
+        <f>IF(B630="","",TEXT(B630,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F630" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm</t>
+        </is>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm rod 2 pcs @ ₹902 (4% disc → ₹865.92)</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I630" t="n">
+        <v>2</v>
+      </c>
+      <c r="J630" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K630" t="n">
+        <v>865.92</v>
+      </c>
+      <c r="L630">
+        <f>IF(OR(I630="",K630=""),"",I630*K630)</f>
+        <v/>
+      </c>
+      <c r="N630">
+        <f>M630*L630</f>
+        <v/>
+      </c>
+      <c r="O630">
+        <f>IF(L630="","",IF(M630="",L630,L630*(1-M630)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="n">
+        <v>639</v>
+      </c>
+      <c r="B631" s="128" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C631">
+        <f>IF(B631="","",TEXT(B631,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F631" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm</t>
+        </is>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm rod 96 pcs @ ₹642 (4% disc → ₹616.32)</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I631" t="n">
+        <v>96</v>
+      </c>
+      <c r="J631" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K631" t="n">
+        <v>616.3200000000001</v>
+      </c>
+      <c r="L631">
+        <f>IF(OR(I631="",K631=""),"",I631*K631)</f>
+        <v/>
+      </c>
+      <c r="N631">
+        <f>M631*L631</f>
+        <v/>
+      </c>
+      <c r="O631">
+        <f>IF(L631="","",IF(M631="",L631,L631*(1-M631)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="n">
+        <v>640</v>
+      </c>
+      <c r="B632" s="128" t="n">
+        <v>46301</v>
+      </c>
+      <c r="C632">
+        <f>IF(B632="","",TEXT(B632,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F632" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I632" t="n">
+        <v>1</v>
+      </c>
+      <c r="J632" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K632" t="n">
+        <v>430</v>
+      </c>
+      <c r="L632">
+        <f>IF(OR(I632="",K632=""),"",I632*K632)</f>
+        <v/>
+      </c>
+      <c r="N632">
+        <f>M632*L632</f>
+        <v/>
+      </c>
+      <c r="O632">
+        <f>IF(L632="","",IF(M632="",L632,L632*(1-M632)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B630" s="60" t="n"/>
-      <c r="C630" s="60" t="n"/>
-      <c r="D630" s="60" t="n"/>
-      <c r="E630" s="60" t="n"/>
-      <c r="F630" s="60" t="n"/>
-      <c r="G630" s="60" t="n"/>
-      <c r="H630" s="60" t="n"/>
-      <c r="I630" s="60" t="n"/>
-      <c r="J630" s="60" t="n"/>
-      <c r="K630" s="60" t="n"/>
-      <c r="L630" s="61">
-        <f>SUM(L5:L629)</f>
-        <v/>
-      </c>
-      <c r="M630" s="60" t="n"/>
-      <c r="N630" s="60" t="n"/>
-      <c r="O630" s="61">
+      <c r="B633" s="60" t="n"/>
+      <c r="C633" s="60" t="n"/>
+      <c r="D633" s="60" t="n"/>
+      <c r="E633" s="60" t="n"/>
+      <c r="F633" s="60" t="n"/>
+      <c r="G633" s="60" t="n"/>
+      <c r="H633" s="60" t="n"/>
+      <c r="I633" s="60" t="n"/>
+      <c r="J633" s="60" t="n"/>
+      <c r="K633" s="60" t="n"/>
+      <c r="L633" s="61">
+        <f>SUM(L5:L632)</f>
+        <v/>
+      </c>
+      <c r="M633" s="60" t="n"/>
+      <c r="N633" s="60" t="n"/>
+      <c r="O633" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P630" s="60" t="n"/>
-      <c r="Q630" s="60" t="n"/>
+      <c r="P633" s="60" t="n"/>
+      <c r="Q633" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R633"/>
+  <dimension ref="A1:R643"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -32107,33 +32107,683 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" s="60" t="inlineStr">
+      <c r="A633" t="n">
+        <v>641</v>
+      </c>
+      <c r="B633" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C633">
+        <f>IF(B633="","",TEXT(B633,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F633" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>5 inch 7 feet wood × 6 pcs (gate frame, C unit)</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I633" t="n">
+        <v>4.375</v>
+      </c>
+      <c r="J633" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K633" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L633">
+        <f>IF(OR(I633="",K633=""),"",I633*K633)</f>
+        <v/>
+      </c>
+      <c r="N633">
+        <f>M633*L633</f>
+        <v/>
+      </c>
+      <c r="O633">
+        <f>IF(L633="","",IF(M633="",L633,L633*(1-M633)))</f>
+        <v/>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="n">
+        <v>642</v>
+      </c>
+      <c r="B634" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C634">
+        <f>IF(B634="","",TEXT(B634,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>4 inch 7 feet wood × 10 pcs (gate frame, C unit)</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I634" t="n">
+        <v>5.833333333333333</v>
+      </c>
+      <c r="J634" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K634" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L634">
+        <f>IF(OR(I634="",K634=""),"",I634*K634)</f>
+        <v/>
+      </c>
+      <c r="N634">
+        <f>M634*L634</f>
+        <v/>
+      </c>
+      <c r="O634">
+        <f>IF(L634="","",IF(M634="",L634,L634*(1-M634)))</f>
+        <v/>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="n">
+        <v>643</v>
+      </c>
+      <c r="B635" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C635">
+        <f>IF(B635="","",TEXT(B635,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F635" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>5 inch 3.5 feet wood × 3 pcs (gate frame, C unit)</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I635" t="n">
+        <v>1.09375</v>
+      </c>
+      <c r="J635" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K635" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L635">
+        <f>IF(OR(I635="",K635=""),"",I635*K635)</f>
+        <v/>
+      </c>
+      <c r="N635">
+        <f>M635*L635</f>
+        <v/>
+      </c>
+      <c r="O635">
+        <f>IF(L635="","",IF(M635="",L635,L635*(1-M635)))</f>
+        <v/>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="n">
+        <v>644</v>
+      </c>
+      <c r="B636" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C636">
+        <f>IF(B636="","",TEXT(B636,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F636" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>4 inch 3.5 feet wood × 5 pcs (gate frame, C unit)</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I636" t="n">
+        <v>1.458333333333333</v>
+      </c>
+      <c r="J636" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K636" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L636">
+        <f>IF(OR(I636="",K636=""),"",I636*K636)</f>
+        <v/>
+      </c>
+      <c r="N636">
+        <f>M636*L636</f>
+        <v/>
+      </c>
+      <c r="O636">
+        <f>IF(L636="","",IF(M636="",L636,L636*(1-M636)))</f>
+        <v/>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="n">
+        <v>645</v>
+      </c>
+      <c r="B637" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C637">
+        <f>IF(B637="","",TEXT(B637,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F637" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>Labour (gate frame wood, C unit)</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I637" t="n">
+        <v>1</v>
+      </c>
+      <c r="J637" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K637" t="n">
+        <v>400</v>
+      </c>
+      <c r="L637">
+        <f>IF(OR(I637="",K637=""),"",I637*K637)</f>
+        <v/>
+      </c>
+      <c r="N637">
+        <f>M637*L637</f>
+        <v/>
+      </c>
+      <c r="O637">
+        <f>IF(L637="","",IF(M637="",L637,L637*(1-M637)))</f>
+        <v/>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="n">
+        <v>646</v>
+      </c>
+      <c r="B638" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C638">
+        <f>IF(B638="","",TEXT(B638,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F638" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>5 inch 7 feet wood × 4 pcs (gate frame, B unit)</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I638" t="n">
+        <v>2.916666666666667</v>
+      </c>
+      <c r="J638" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K638" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L638">
+        <f>IF(OR(I638="",K638=""),"",I638*K638)</f>
+        <v/>
+      </c>
+      <c r="N638">
+        <f>M638*L638</f>
+        <v/>
+      </c>
+      <c r="O638">
+        <f>IF(L638="","",IF(M638="",L638,L638*(1-M638)))</f>
+        <v/>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="n">
+        <v>647</v>
+      </c>
+      <c r="B639" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C639">
+        <f>IF(B639="","",TEXT(B639,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F639" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>4 inch 7 feet wood × 6 pcs (gate frame, B unit)</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I639" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J639" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K639" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L639">
+        <f>IF(OR(I639="",K639=""),"",I639*K639)</f>
+        <v/>
+      </c>
+      <c r="N639">
+        <f>M639*L639</f>
+        <v/>
+      </c>
+      <c r="O639">
+        <f>IF(L639="","",IF(M639="",L639,L639*(1-M639)))</f>
+        <v/>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="n">
+        <v>648</v>
+      </c>
+      <c r="B640" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C640">
+        <f>IF(B640="","",TEXT(B640,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F640" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>5 inch 3.5 feet wood × 2 pcs (gate frame, B unit)</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I640" t="n">
+        <v>0.7291666666666666</v>
+      </c>
+      <c r="J640" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K640" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L640">
+        <f>IF(OR(I640="",K640=""),"",I640*K640)</f>
+        <v/>
+      </c>
+      <c r="N640">
+        <f>M640*L640</f>
+        <v/>
+      </c>
+      <c r="O640">
+        <f>IF(L640="","",IF(M640="",L640,L640*(1-M640)))</f>
+        <v/>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="n">
+        <v>649</v>
+      </c>
+      <c r="B641" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C641">
+        <f>IF(B641="","",TEXT(B641,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F641" t="inlineStr">
+        <is>
+          <t>Wood</t>
+        </is>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>4 inch 3.5 feet wood × 3 pcs (gate frame, B unit)</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I641" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="J641" t="inlineStr">
+        <is>
+          <t>cft</t>
+        </is>
+      </c>
+      <c r="K641" t="n">
+        <v>3300</v>
+      </c>
+      <c r="L641">
+        <f>IF(OR(I641="",K641=""),"",I641*K641)</f>
+        <v/>
+      </c>
+      <c r="N641">
+        <f>M641*L641</f>
+        <v/>
+      </c>
+      <c r="O641">
+        <f>IF(L641="","",IF(M641="",L641,L641*(1-M641)))</f>
+        <v/>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="n">
+        <v>650</v>
+      </c>
+      <c r="B642" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C642">
+        <f>IF(B642="","",TEXT(B642,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>Labour (gate frame wood, B unit)</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="I642" t="n">
+        <v>1</v>
+      </c>
+      <c r="J642" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K642" t="n">
+        <v>400</v>
+      </c>
+      <c r="L642">
+        <f>IF(OR(I642="",K642=""),"",I642*K642)</f>
+        <v/>
+      </c>
+      <c r="N642">
+        <f>M642*L642</f>
+        <v/>
+      </c>
+      <c r="O642">
+        <f>IF(L642="","",IF(M642="",L642,L642*(1-M642)))</f>
+        <v/>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B633" s="60" t="n"/>
-      <c r="C633" s="60" t="n"/>
-      <c r="D633" s="60" t="n"/>
-      <c r="E633" s="60" t="n"/>
-      <c r="F633" s="60" t="n"/>
-      <c r="G633" s="60" t="n"/>
-      <c r="H633" s="60" t="n"/>
-      <c r="I633" s="60" t="n"/>
-      <c r="J633" s="60" t="n"/>
-      <c r="K633" s="60" t="n"/>
-      <c r="L633" s="61">
-        <f>SUM(L5:L632)</f>
-        <v/>
-      </c>
-      <c r="M633" s="60" t="n"/>
-      <c r="N633" s="60" t="n"/>
-      <c r="O633" s="61">
+      <c r="B643" s="60" t="n"/>
+      <c r="C643" s="60" t="n"/>
+      <c r="D643" s="60" t="n"/>
+      <c r="E643" s="60" t="n"/>
+      <c r="F643" s="60" t="n"/>
+      <c r="G643" s="60" t="n"/>
+      <c r="H643" s="60" t="n"/>
+      <c r="I643" s="60" t="n"/>
+      <c r="J643" s="60" t="n"/>
+      <c r="K643" s="60" t="n"/>
+      <c r="L643" s="61">
+        <f>SUM(L5:L642)</f>
+        <v/>
+      </c>
+      <c r="M643" s="60" t="n"/>
+      <c r="N643" s="60" t="n"/>
+      <c r="O643" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P633" s="60" t="n"/>
-      <c r="Q633" s="60" t="n"/>
+      <c r="P643" s="60" t="n"/>
+      <c r="Q643" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -48644,16 +49294,44 @@
       <c r="A103" s="41" t="n">
         <v>109</v>
       </c>
-      <c r="B103" s="45" t="n"/>
-      <c r="C103" s="47" t="n"/>
-      <c r="D103" s="47" t="n"/>
-      <c r="E103" s="47" t="n"/>
-      <c r="F103" s="47" t="n"/>
-      <c r="G103" s="62" t="n"/>
-      <c r="H103" s="47" t="n"/>
+      <c r="B103" s="45" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C103" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D103" s="47" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="E103" s="47" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F103" s="47" t="inlineStr">
+        <is>
+          <t>Wood for gate frames — C unit ₹42,509 + B unit ₹26,869</t>
+        </is>
+      </c>
+      <c r="G103" s="62" t="n">
+        <v>69378</v>
+      </c>
+      <c r="H103" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I103" s="47" t="n"/>
       <c r="J103" s="47" t="n"/>
-      <c r="K103" s="47" t="n"/>
+      <c r="K103" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L103" s="50">
         <f>IF(G113="","",IF(L112="",G113,L112+G113))</f>
         <v/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -49342,16 +49342,44 @@
       <c r="A104" s="43" t="n">
         <v>110</v>
       </c>
-      <c r="B104" s="53" t="n"/>
-      <c r="C104" s="55" t="n"/>
-      <c r="D104" s="55" t="n"/>
-      <c r="E104" s="55" t="n"/>
-      <c r="F104" s="55" t="n"/>
-      <c r="G104" s="63" t="n"/>
-      <c r="H104" s="55" t="n"/>
+      <c r="B104" s="53" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C104" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D104" s="55" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E104" s="55" t="inlineStr">
+        <is>
+          <t>Steel / Iron + Cement + Building Materials</t>
+        </is>
+      </c>
+      <c r="F104" s="55" t="inlineStr">
+        <is>
+          <t>Part payment against Oct bills</t>
+        </is>
+      </c>
+      <c r="G104" s="63" t="n">
+        <v>70000</v>
+      </c>
+      <c r="H104" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I104" s="55" t="n"/>
       <c r="J104" s="55" t="n"/>
-      <c r="K104" s="55" t="n"/>
+      <c r="K104" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L104" s="58">
         <f>IF(G114="","",IF(L113="",G114,L113+G114))</f>
         <v/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R643"/>
+  <dimension ref="A1:R646"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -32757,33 +32757,213 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" s="60" t="inlineStr">
+      <c r="A643" t="n">
+        <v>651</v>
+      </c>
+      <c r="B643" s="128" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C643">
+        <f>IF(B643="","",TEXT(B643,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F643" t="inlineStr">
+        <is>
+          <t>Engineer Supervision</t>
+        </is>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>Construction work done — general site supervision &amp; labour (Papa, 7-Oct)</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I643" t="n">
+        <v>1</v>
+      </c>
+      <c r="J643" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K643" t="n">
+        <v>25000</v>
+      </c>
+      <c r="L643">
+        <f>IF(OR(I643="",K643=""),"",I643*K643)</f>
+        <v/>
+      </c>
+      <c r="N643">
+        <f>M643*L643</f>
+        <v/>
+      </c>
+      <c r="O643">
+        <f>IF(L643="","",IF(M643="",L643,L643*(1-M643)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="n">
+        <v>652</v>
+      </c>
+      <c r="B644" s="128" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C644">
+        <f>IF(B644="","",TEXT(B644,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F644" t="inlineStr">
+        <is>
+          <t>Engineer Supervision</t>
+        </is>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>Construction work done — general site supervision &amp; labour (Papa, 8-Oct)</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I644" t="n">
+        <v>1</v>
+      </c>
+      <c r="J644" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K644" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L644">
+        <f>IF(OR(I644="",K644=""),"",I644*K644)</f>
+        <v/>
+      </c>
+      <c r="N644">
+        <f>M644*L644</f>
+        <v/>
+      </c>
+      <c r="O644">
+        <f>IF(L644="","",IF(M644="",L644,L644*(1-M644)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="n">
+        <v>653</v>
+      </c>
+      <c r="B645" s="128" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C645">
+        <f>IF(B645="","",TEXT(B645,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="F645" t="inlineStr">
+        <is>
+          <t>Electrical Items</t>
+        </is>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>Electrical items — Mittal Electric, Darbhanga</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Mittal Electric</t>
+        </is>
+      </c>
+      <c r="I645" t="n">
+        <v>1</v>
+      </c>
+      <c r="J645" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K645" t="n">
+        <v>21065</v>
+      </c>
+      <c r="L645">
+        <f>IF(OR(I645="",K645=""),"",I645*K645)</f>
+        <v/>
+      </c>
+      <c r="N645">
+        <f>M645*L645</f>
+        <v/>
+      </c>
+      <c r="O645">
+        <f>IF(L645="","",IF(M645="",L645,L645*(1-M645)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B643" s="60" t="n"/>
-      <c r="C643" s="60" t="n"/>
-      <c r="D643" s="60" t="n"/>
-      <c r="E643" s="60" t="n"/>
-      <c r="F643" s="60" t="n"/>
-      <c r="G643" s="60" t="n"/>
-      <c r="H643" s="60" t="n"/>
-      <c r="I643" s="60" t="n"/>
-      <c r="J643" s="60" t="n"/>
-      <c r="K643" s="60" t="n"/>
-      <c r="L643" s="61">
-        <f>SUM(L5:L642)</f>
-        <v/>
-      </c>
-      <c r="M643" s="60" t="n"/>
-      <c r="N643" s="60" t="n"/>
-      <c r="O643" s="61">
+      <c r="B646" s="60" t="n"/>
+      <c r="C646" s="60" t="n"/>
+      <c r="D646" s="60" t="n"/>
+      <c r="E646" s="60" t="n"/>
+      <c r="F646" s="60" t="n"/>
+      <c r="G646" s="60" t="n"/>
+      <c r="H646" s="60" t="n"/>
+      <c r="I646" s="60" t="n"/>
+      <c r="J646" s="60" t="n"/>
+      <c r="K646" s="60" t="n"/>
+      <c r="L646" s="61">
+        <f>SUM(L5:L645)</f>
+        <v/>
+      </c>
+      <c r="M646" s="60" t="n"/>
+      <c r="N646" s="60" t="n"/>
+      <c r="O646" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P643" s="60" t="n"/>
-      <c r="Q643" s="60" t="n"/>
+      <c r="P646" s="60" t="n"/>
+      <c r="Q646" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -49390,16 +49570,44 @@
       <c r="A105" s="41" t="n">
         <v>111</v>
       </c>
-      <c r="B105" s="45" t="n"/>
-      <c r="C105" s="47" t="n"/>
-      <c r="D105" s="47" t="n"/>
-      <c r="E105" s="47" t="n"/>
-      <c r="F105" s="47" t="n"/>
-      <c r="G105" s="62" t="n"/>
-      <c r="H105" s="47" t="n"/>
+      <c r="B105" s="45" t="n">
+        <v>46302</v>
+      </c>
+      <c r="C105" s="47" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D105" s="47" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E105" s="47" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F105" s="47" t="inlineStr">
+        <is>
+          <t>Construction work done — general (Papa, 7-Oct)</t>
+        </is>
+      </c>
+      <c r="G105" s="62" t="n">
+        <v>25000</v>
+      </c>
+      <c r="H105" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I105" s="47" t="n"/>
       <c r="J105" s="47" t="n"/>
-      <c r="K105" s="47" t="n"/>
+      <c r="K105" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L105" s="50">
         <f>IF(G115="","",IF(L114="",G115,L114+G115))</f>
         <v/>
@@ -49410,16 +49618,44 @@
       <c r="A106" s="43" t="n">
         <v>112</v>
       </c>
-      <c r="B106" s="53" t="n"/>
-      <c r="C106" s="55" t="n"/>
-      <c r="D106" s="55" t="n"/>
-      <c r="E106" s="55" t="n"/>
-      <c r="F106" s="55" t="n"/>
-      <c r="G106" s="63" t="n"/>
-      <c r="H106" s="55" t="n"/>
+      <c r="B106" s="53" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C106" s="55" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D106" s="55" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E106" s="55" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F106" s="55" t="inlineStr">
+        <is>
+          <t>Construction work done — general (Papa, 8-Oct)</t>
+        </is>
+      </c>
+      <c r="G106" s="63" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H106" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I106" s="55" t="n"/>
       <c r="J106" s="55" t="n"/>
-      <c r="K106" s="55" t="n"/>
+      <c r="K106" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L106" s="58">
         <f>IF(G116="","",IF(L115="",G116,L115+G116))</f>
         <v/>
@@ -49430,16 +49666,44 @@
       <c r="A107" s="41" t="n">
         <v>113</v>
       </c>
-      <c r="B107" s="45" t="n"/>
-      <c r="C107" s="47" t="n"/>
-      <c r="D107" s="47" t="n"/>
-      <c r="E107" s="47" t="n"/>
-      <c r="F107" s="47" t="n"/>
-      <c r="G107" s="62" t="n"/>
-      <c r="H107" s="47" t="n"/>
+      <c r="B107" s="45" t="n">
+        <v>46303</v>
+      </c>
+      <c r="C107" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D107" s="47" t="inlineStr">
+        <is>
+          <t>Mittal Electric</t>
+        </is>
+      </c>
+      <c r="E107" s="47" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="F107" s="47" t="inlineStr">
+        <is>
+          <t>Electrical items — Mittal Electric, Darbhanga</t>
+        </is>
+      </c>
+      <c r="G107" s="62" t="n">
+        <v>21065</v>
+      </c>
+      <c r="H107" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I107" s="47" t="n"/>
       <c r="J107" s="47" t="n"/>
-      <c r="K107" s="47" t="n"/>
+      <c r="K107" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L107" s="50">
         <f>IF(G117="","",IF(L116="",G117,L116+G117))</f>
         <v/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -6539,7 +6539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R646"/>
+  <dimension ref="A1:R648"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -32937,33 +32937,153 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" s="60" t="inlineStr">
+      <c r="A646" t="n">
+        <v>654</v>
+      </c>
+      <c r="B646" s="128" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C646">
+        <f>IF(B646="","",TEXT(B646,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F646" t="inlineStr">
+        <is>
+          <t>Sand</t>
+        </is>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>Sand delivery — 40 MT @ ₹1,400/MT</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Sand Truck Wala</t>
+        </is>
+      </c>
+      <c r="I646" t="n">
+        <v>40</v>
+      </c>
+      <c r="J646" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="K646" t="n">
+        <v>1400</v>
+      </c>
+      <c r="L646">
+        <f>IF(OR(I646="",K646=""),"",I646*K646)</f>
+        <v/>
+      </c>
+      <c r="N646">
+        <f>M646*L646</f>
+        <v/>
+      </c>
+      <c r="O646">
+        <f>IF(L646="","",IF(M646="",L646,L646*(1-M646)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="n">
+        <v>655</v>
+      </c>
+      <c r="B647" s="128" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C647">
+        <f>IF(B647="","",TEXT(B647,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F647" t="inlineStr">
+        <is>
+          <t>Fuel</t>
+        </is>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>Diesel 10 litres @ ₹100/L</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
+      <c r="I647" t="n">
+        <v>10</v>
+      </c>
+      <c r="J647" t="inlineStr">
+        <is>
+          <t>Litres</t>
+        </is>
+      </c>
+      <c r="K647" t="n">
+        <v>100</v>
+      </c>
+      <c r="L647">
+        <f>IF(OR(I647="",K647=""),"",I647*K647)</f>
+        <v/>
+      </c>
+      <c r="N647">
+        <f>M647*L647</f>
+        <v/>
+      </c>
+      <c r="O647">
+        <f>IF(L647="","",IF(M647="",L647,L647*(1-M647)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B646" s="60" t="n"/>
-      <c r="C646" s="60" t="n"/>
-      <c r="D646" s="60" t="n"/>
-      <c r="E646" s="60" t="n"/>
-      <c r="F646" s="60" t="n"/>
-      <c r="G646" s="60" t="n"/>
-      <c r="H646" s="60" t="n"/>
-      <c r="I646" s="60" t="n"/>
-      <c r="J646" s="60" t="n"/>
-      <c r="K646" s="60" t="n"/>
-      <c r="L646" s="61">
-        <f>SUM(L5:L645)</f>
-        <v/>
-      </c>
-      <c r="M646" s="60" t="n"/>
-      <c r="N646" s="60" t="n"/>
-      <c r="O646" s="61">
+      <c r="B648" s="60" t="n"/>
+      <c r="C648" s="60" t="n"/>
+      <c r="D648" s="60" t="n"/>
+      <c r="E648" s="60" t="n"/>
+      <c r="F648" s="60" t="n"/>
+      <c r="G648" s="60" t="n"/>
+      <c r="H648" s="60" t="n"/>
+      <c r="I648" s="60" t="n"/>
+      <c r="J648" s="60" t="n"/>
+      <c r="K648" s="60" t="n"/>
+      <c r="L648" s="61">
+        <f>SUM(L5:L647)</f>
+        <v/>
+      </c>
+      <c r="M648" s="60" t="n"/>
+      <c r="N648" s="60" t="n"/>
+      <c r="O648" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P646" s="60" t="n"/>
-      <c r="Q646" s="60" t="n"/>
+      <c r="P648" s="60" t="n"/>
+      <c r="Q648" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -49714,16 +49834,44 @@
       <c r="A108" s="43" t="n">
         <v>114</v>
       </c>
-      <c r="B108" s="53" t="n"/>
-      <c r="C108" s="55" t="n"/>
-      <c r="D108" s="55" t="n"/>
-      <c r="E108" s="55" t="n"/>
-      <c r="F108" s="55" t="n"/>
-      <c r="G108" s="63" t="n"/>
-      <c r="H108" s="55" t="n"/>
+      <c r="B108" s="53" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C108" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D108" s="55" t="inlineStr">
+        <is>
+          <t>Sand Truck Wala</t>
+        </is>
+      </c>
+      <c r="E108" s="55" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F108" s="55" t="inlineStr">
+        <is>
+          <t>Sand delivery — 40 MT</t>
+        </is>
+      </c>
+      <c r="G108" s="63" t="n">
+        <v>56000</v>
+      </c>
+      <c r="H108" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I108" s="55" t="n"/>
       <c r="J108" s="55" t="n"/>
-      <c r="K108" s="55" t="n"/>
+      <c r="K108" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L108" s="58">
         <f>IF(G118="","",IF(L117="",G118,L117+G118))</f>
         <v/>
@@ -49734,16 +49882,44 @@
       <c r="A109" s="41" t="n">
         <v>115</v>
       </c>
-      <c r="B109" s="45" t="n"/>
-      <c r="C109" s="47" t="n"/>
-      <c r="D109" s="47" t="n"/>
-      <c r="E109" s="47" t="n"/>
-      <c r="F109" s="47" t="n"/>
-      <c r="G109" s="62" t="n"/>
-      <c r="H109" s="47" t="n"/>
+      <c r="B109" s="45" t="n">
+        <v>46304</v>
+      </c>
+      <c r="C109" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D109" s="47" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
+      <c r="E109" s="47" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F109" s="47" t="inlineStr">
+        <is>
+          <t>Diesel 10 litres</t>
+        </is>
+      </c>
+      <c r="G109" s="62" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H109" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I109" s="47" t="n"/>
       <c r="J109" s="47" t="n"/>
-      <c r="K109" s="47" t="n"/>
+      <c r="K109" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L109" s="50">
         <f>IF(G119="","",IF(L118="",G119,L118+G119))</f>
         <v/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -2547,81 +2547,93 @@
       <c r="I4" s="82" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="99">
-      <c r="A5" s="74" t="inlineStr">
+      <c r="A5" s="77" t="inlineStr">
         <is>
           <t>Pappu Hardware</t>
         </is>
       </c>
-      <c r="B5" s="84" t="n"/>
-      <c r="C5" s="84" t="n">
-        <v>451130</v>
-      </c>
-      <c r="D5" s="84" t="n">
-        <v>449830</v>
-      </c>
-      <c r="E5" s="96">
+      <c r="B5" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A5)</f>
+        <v/>
+      </c>
+      <c r="C5" s="87">
+        <f>SUMIF('All Transactions'!H:H,A5,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D5" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A5,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E5" s="97">
         <f>C5-D5</f>
         <v/>
       </c>
-      <c r="F5" s="85" t="inlineStr">
-        <is>
-          <t>⚠️ DUE</t>
-        </is>
-      </c>
-      <c r="G5" s="86" t="n"/>
-      <c r="H5" s="74" t="n"/>
+      <c r="F5" s="89">
+        <f>IF(E5&gt;0,"⚠️ DUE",IF(E5&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G5" s="90" t="n"/>
+      <c r="H5" s="77" t="n"/>
       <c r="I5" s="82" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="99">
       <c r="A6" s="77" t="inlineStr">
         <is>
-          <t>Brick Company</t>
-        </is>
-      </c>
-      <c r="B6" s="87" t="n"/>
-      <c r="C6" s="87" t="n">
-        <v>153000</v>
-      </c>
-      <c r="D6" s="87" t="n">
-        <v>369000</v>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="B6" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A6)</f>
+        <v/>
+      </c>
+      <c r="C6" s="87">
+        <f>SUMIF('All Transactions'!H:H,A6,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D6" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A6,'Payment Tracker'!G:G)</f>
+        <v/>
       </c>
       <c r="E6" s="97">
         <f>C6-D6</f>
         <v/>
       </c>
-      <c r="F6" s="89" t="inlineStr">
-        <is>
-          <t>🔵 ADV</t>
-        </is>
+      <c r="F6" s="89">
+        <f>IF(E6&gt;0,"⚠️ DUE",IF(E6&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
       </c>
       <c r="G6" s="90" t="n"/>
       <c r="H6" s="77" t="n"/>
       <c r="I6" s="82" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="99">
-      <c r="A7" s="74" t="inlineStr">
-        <is>
-          <t>Econ Builder</t>
-        </is>
-      </c>
-      <c r="B7" s="84" t="n"/>
-      <c r="C7" s="84" t="n">
-        <v>226000</v>
-      </c>
-      <c r="D7" s="84" t="n">
-        <v>226000</v>
-      </c>
-      <c r="E7" s="96">
+      <c r="A7" s="77" t="inlineStr">
+        <is>
+          <t>Brick Company</t>
+        </is>
+      </c>
+      <c r="B7" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A7)</f>
+        <v/>
+      </c>
+      <c r="C7" s="87">
+        <f>SUMIF('All Transactions'!H:H,A7,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D7" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A7,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E7" s="97">
         <f>C7-D7</f>
         <v/>
       </c>
-      <c r="F7" s="85" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
-      </c>
-      <c r="G7" s="86" t="n"/>
-      <c r="H7" s="74" t="n"/>
+      <c r="F7" s="89">
+        <f>IF(E7&gt;0,"⚠️ DUE",IF(E7&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G7" s="90" t="n"/>
+      <c r="H7" s="77" t="n"/>
       <c r="I7" s="82" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="99">
@@ -2630,50 +2642,58 @@
           <t>Concrete Supplier</t>
         </is>
       </c>
-      <c r="B8" s="87" t="n"/>
-      <c r="C8" s="87" t="n">
-        <v>161982</v>
-      </c>
-      <c r="D8" s="87" t="n">
-        <v>161982</v>
+      <c r="B8" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A8)</f>
+        <v/>
+      </c>
+      <c r="C8" s="87">
+        <f>SUMIF('All Transactions'!H:H,A8,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D8" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A8,'Payment Tracker'!G:G)</f>
+        <v/>
       </c>
       <c r="E8" s="97">
         <f>C8-D8</f>
         <v/>
       </c>
-      <c r="F8" s="89" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
+      <c r="F8" s="89">
+        <f>IF(E8&gt;0,"⚠️ DUE",IF(E8&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
       </c>
       <c r="G8" s="90" t="n"/>
       <c r="H8" s="77" t="n"/>
       <c r="I8" s="82" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="99">
-      <c r="A9" s="74" t="inlineStr">
+      <c r="A9" s="77" t="inlineStr">
         <is>
           <t>Sand Truck Wala</t>
         </is>
       </c>
-      <c r="B9" s="84" t="n"/>
-      <c r="C9" s="84" t="n">
-        <v>110000</v>
-      </c>
-      <c r="D9" s="84" t="n">
-        <v>110000</v>
-      </c>
-      <c r="E9" s="96">
+      <c r="B9" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A9)</f>
+        <v/>
+      </c>
+      <c r="C9" s="87">
+        <f>SUMIF('All Transactions'!H:H,A9,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D9" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A9,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E9" s="97">
         <f>C9-D9</f>
         <v/>
       </c>
-      <c r="F9" s="85" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
-      </c>
-      <c r="G9" s="86" t="n"/>
-      <c r="H9" s="74" t="n"/>
+      <c r="F9" s="89">
+        <f>IF(E9&gt;0,"⚠️ DUE",IF(E9&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G9" s="90" t="n"/>
+      <c r="H9" s="77" t="n"/>
       <c r="I9" s="82" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="99">
@@ -2682,174 +2702,235 @@
           <t>Mukesh Yadav</t>
         </is>
       </c>
-      <c r="B10" s="87" t="n"/>
-      <c r="C10" s="87" t="n">
-        <v>63200</v>
-      </c>
-      <c r="D10" s="87" t="n">
-        <v>63200</v>
+      <c r="B10" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A10)</f>
+        <v/>
+      </c>
+      <c r="C10" s="87">
+        <f>SUMIF('All Transactions'!H:H,A10,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D10" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A10,'Payment Tracker'!G:G)</f>
+        <v/>
       </c>
       <c r="E10" s="97">
         <f>C10-D10</f>
         <v/>
       </c>
-      <c r="F10" s="89" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
+      <c r="F10" s="89">
+        <f>IF(E10&gt;0,"⚠️ DUE",IF(E10&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
       </c>
       <c r="G10" s="90" t="n"/>
       <c r="H10" s="77" t="n"/>
       <c r="I10" s="82" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="99">
-      <c r="A11" s="74" t="inlineStr">
+      <c r="A11" s="77" t="inlineStr">
         <is>
           <t>Daily Labour</t>
         </is>
       </c>
-      <c r="B11" s="84" t="n"/>
-      <c r="C11" s="84" t="n">
-        <v>33075</v>
-      </c>
-      <c r="D11" s="84" t="n">
-        <v>33075</v>
-      </c>
-      <c r="E11" s="96">
+      <c r="B11" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A11)</f>
+        <v/>
+      </c>
+      <c r="C11" s="87">
+        <f>SUMIF('All Transactions'!H:H,A11,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D11" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A11,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E11" s="97">
         <f>C11-D11</f>
         <v/>
       </c>
-      <c r="F11" s="85" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
-      </c>
-      <c r="G11" s="86" t="n"/>
-      <c r="H11" s="74" t="n"/>
+      <c r="F11" s="89">
+        <f>IF(E11&gt;0,"⚠️ DUE",IF(E11&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G11" s="90" t="n"/>
+      <c r="H11" s="77" t="n"/>
       <c r="I11" s="82" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="99">
       <c r="A12" s="77" t="inlineStr">
         <is>
-          <t>Naveen Hardware</t>
-        </is>
-      </c>
-      <c r="B12" s="87" t="n"/>
-      <c r="C12" s="87" t="n">
-        <v>18650</v>
-      </c>
-      <c r="D12" s="87" t="n">
-        <v>18650</v>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
+      <c r="B12" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A12)</f>
+        <v/>
+      </c>
+      <c r="C12" s="87">
+        <f>SUMIF('All Transactions'!H:H,A12,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D12" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A12,'Payment Tracker'!G:G)</f>
+        <v/>
       </c>
       <c r="E12" s="97">
         <f>C12-D12</f>
         <v/>
       </c>
-      <c r="F12" s="89" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
+      <c r="F12" s="89">
+        <f>IF(E12&gt;0,"⚠️ DUE",IF(E12&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
       </c>
       <c r="G12" s="90" t="n"/>
       <c r="H12" s="77" t="n"/>
       <c r="I12" s="82" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="99">
-      <c r="A13" s="74" t="inlineStr">
+      <c r="A13" s="77" t="inlineStr">
         <is>
           <t>Local Purchase</t>
         </is>
       </c>
-      <c r="B13" s="84" t="n"/>
-      <c r="C13" s="84" t="n">
-        <v>5060</v>
-      </c>
-      <c r="D13" s="84" t="n">
-        <v>5060</v>
-      </c>
-      <c r="E13" s="96">
+      <c r="B13" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A13)</f>
+        <v/>
+      </c>
+      <c r="C13" s="87">
+        <f>SUMIF('All Transactions'!H:H,A13,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D13" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A13,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E13" s="97">
         <f>C13-D13</f>
         <v/>
       </c>
-      <c r="F13" s="85" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
-      </c>
-      <c r="G13" s="86" t="n"/>
-      <c r="H13" s="74" t="n"/>
+      <c r="F13" s="89">
+        <f>IF(E13&gt;0,"⚠️ DUE",IF(E13&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G13" s="90" t="n"/>
+      <c r="H13" s="77" t="n"/>
       <c r="I13" s="82" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="99">
       <c r="A14" s="77" t="inlineStr">
         <is>
-          <t>Sonbhai-Coordinator</t>
-        </is>
-      </c>
-      <c r="B14" s="87" t="n"/>
-      <c r="C14" s="87" t="n">
-        <v>1500</v>
-      </c>
-      <c r="D14" s="87" t="n">
-        <v>1500</v>
+          <t>Mittal Electric</t>
+        </is>
+      </c>
+      <c r="B14" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A14)</f>
+        <v/>
+      </c>
+      <c r="C14" s="87">
+        <f>SUMIF('All Transactions'!H:H,A14,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D14" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A14,'Payment Tracker'!G:G)</f>
+        <v/>
       </c>
       <c r="E14" s="97">
         <f>C14-D14</f>
         <v/>
       </c>
-      <c r="F14" s="89" t="inlineStr">
-        <is>
-          <t>✅ PAID</t>
-        </is>
+      <c r="F14" s="89">
+        <f>IF(E14&gt;0,"⚠️ DUE",IF(E14&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
       </c>
       <c r="G14" s="90" t="n"/>
       <c r="H14" s="77" t="n"/>
       <c r="I14" s="82" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="99">
-      <c r="A15" s="74" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B15" s="84" t="n"/>
-      <c r="C15" s="84">
-        <f>SUM(C5:C14)</f>
-        <v/>
-      </c>
-      <c r="D15" s="84">
-        <f>SUM(D5:D14)</f>
-        <v/>
-      </c>
-      <c r="E15" s="96">
+      <c r="A15" s="77" t="inlineStr">
+        <is>
+          <t>Naveen Hardware</t>
+        </is>
+      </c>
+      <c r="B15" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A15)</f>
+        <v/>
+      </c>
+      <c r="C15" s="87">
+        <f>SUMIF('All Transactions'!H:H,A15,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D15" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A15,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E15" s="97">
         <f>C15-D15</f>
         <v/>
       </c>
-      <c r="F15" s="85" t="n"/>
-      <c r="G15" s="86" t="n"/>
-      <c r="H15" s="74" t="n"/>
+      <c r="F15" s="89">
+        <f>IF(E15&gt;0,"⚠️ DUE",IF(E15&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G15" s="90" t="n"/>
+      <c r="H15" s="77" t="n"/>
       <c r="I15" s="82" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="99">
-      <c r="A16" s="77" t="n"/>
-      <c r="B16" s="87" t="n"/>
-      <c r="C16" s="78" t="n"/>
-      <c r="D16" s="78" t="n"/>
-      <c r="E16" s="88" t="n"/>
-      <c r="F16" s="89" t="n"/>
+      <c r="A16" s="77" t="inlineStr">
+        <is>
+          <t>Sonbhai-Coordinator</t>
+        </is>
+      </c>
+      <c r="B16" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A16)</f>
+        <v/>
+      </c>
+      <c r="C16" s="87">
+        <f>SUMIF('All Transactions'!H:H,A16,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D16" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A16,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E16" s="97">
+        <f>C16-D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="89">
+        <f>IF(E16&gt;0,"⚠️ DUE",IF(E16&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
       <c r="G16" s="90" t="n"/>
       <c r="H16" s="77" t="n"/>
       <c r="I16" s="82" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="99">
-      <c r="A17" s="80" t="n"/>
-      <c r="B17" s="91" t="n"/>
-      <c r="C17" s="81" t="n"/>
-      <c r="D17" s="81" t="n"/>
-      <c r="E17" s="81" t="n"/>
-      <c r="F17" s="80" t="n"/>
-      <c r="G17" s="80" t="n"/>
-      <c r="H17" s="80" t="n"/>
+      <c r="A17" s="74" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B17" s="84">
+        <f>SUM(B5:B16)</f>
+        <v/>
+      </c>
+      <c r="C17" s="84">
+        <f>SUM(C5:C16)</f>
+        <v/>
+      </c>
+      <c r="D17" s="84">
+        <f>SUM(D5:D16)</f>
+        <v/>
+      </c>
+      <c r="E17" s="96">
+        <f>C17-D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="85" t="n"/>
+      <c r="G17" s="86" t="n"/>
+      <c r="H17" s="74" t="n"/>
       <c r="I17" s="82" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="99">
@@ -3141,23 +3222,26 @@
     <row r="7" ht="33.75" customHeight="1" s="99">
       <c r="A7" s="6" t="n"/>
       <c r="B7" s="112">
-        <f>SUM('Payment Tracker'!G5:G100)</f>
+        <f>SUM('Payment Tracker'!G5:G500)</f>
         <v/>
       </c>
       <c r="C7" s="113" t="n"/>
       <c r="D7" s="6" t="n"/>
-      <c r="E7" s="122" t="n">
-        <v>1223597</v>
+      <c r="E7" s="122">
+        <f>'Material Summary'!H35</f>
+        <v/>
       </c>
       <c r="F7" s="113" t="n"/>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="120" t="n">
-        <v>216000</v>
+      <c r="H7" s="120">
+        <f>-SUMIF('Vendor Summary'!E5:E16,"&lt;0")</f>
+        <v/>
       </c>
       <c r="I7" s="113" t="n"/>
       <c r="J7" s="6" t="n"/>
-      <c r="K7" s="121" t="n">
-        <v>1300</v>
+      <c r="K7" s="121">
+        <f>SUMIF('Vendor Summary'!E5:E16,"&gt;0")</f>
+        <v/>
       </c>
       <c r="L7" s="113" t="n"/>
       <c r="M7" s="6" t="n"/>
@@ -3174,14 +3258,14 @@
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="116" t="inlineStr">
         <is>
-          <t>Billed value received</t>
+          <t>Net billed value of materials</t>
         </is>
       </c>
       <c r="F8" s="117" t="n"/>
       <c r="G8" s="6" t="n"/>
       <c r="H8" s="116" t="inlineStr">
         <is>
-          <t>Advance with Brick Co.</t>
+          <t>Advance paid beyond billed (all vendors)</t>
         </is>
       </c>
       <c r="I8" s="117" t="n"/>
@@ -3289,11 +3373,11 @@
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>Self-GPay</t>
+          <t>Avinash</t>
         </is>
       </c>
       <c r="C12" s="13">
-        <f>SUMIF('Payment Tracker'!C:C,B12,'Payment Tracker'!G:G)</f>
+        <f>SUMIF('Payment Tracker'!C:C,"Self",'Payment Tracker'!G:G)+SUMIF('Payment Tracker'!C:C,"Self-GPay",'Payment Tracker'!G:G)+SUMIF('Payment Tracker'!C:C,"Self-Bank Transfer",'Payment Tracker'!G:G)</f>
         <v/>
       </c>
       <c r="D12" s="6" t="n"/>
@@ -3335,7 +3419,7 @@
       <c r="A13" s="6" t="n"/>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>Self-Bank Transfer</t>
+          <t>Papa</t>
         </is>
       </c>
       <c r="C13" s="18">
@@ -3345,7 +3429,7 @@
       <c r="D13" s="6" t="n"/>
       <c r="E13" s="17" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F13" s="19">
@@ -3355,7 +3439,7 @@
       <c r="G13" s="6" t="n"/>
       <c r="H13" s="17" t="inlineStr">
         <is>
-          <t>Brick Company</t>
+          <t>Econ Builder</t>
         </is>
       </c>
       <c r="I13" s="20">
@@ -3381,7 +3465,7 @@
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>Papa</t>
+          <t>Chota Bhai</t>
         </is>
       </c>
       <c r="C14" s="13">
@@ -3391,7 +3475,7 @@
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Professional Fees</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="F14" s="14">
@@ -3401,7 +3485,7 @@
       <c r="G14" s="6" t="n"/>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Econ Builder</t>
+          <t>Brick Company</t>
         </is>
       </c>
       <c r="I14" s="15">
@@ -3425,19 +3509,12 @@
     </row>
     <row r="15" ht="15" customHeight="1" s="99">
       <c r="A15" s="6" t="n"/>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>Chota Bhai</t>
-        </is>
-      </c>
-      <c r="C15" s="18">
-        <f>SUMIF('Payment Tracker'!C:C,B15,'Payment Tracker'!G:G)</f>
-        <v/>
-      </c>
+      <c r="B15" s="17" t="n"/>
+      <c r="C15" s="18" t="n"/>
       <c r="D15" s="6" t="n"/>
       <c r="E15" s="17" t="inlineStr">
         <is>
-          <t>Land Development</t>
+          <t>Labour</t>
         </is>
       </c>
       <c r="F15" s="19">
@@ -3471,19 +3548,12 @@
     </row>
     <row r="16" ht="15" customHeight="1" s="99">
       <c r="A16" s="6" t="n"/>
-      <c r="B16" s="12" t="inlineStr">
-        <is>
-          <t>Through Sonbhai</t>
-        </is>
-      </c>
-      <c r="C16" s="13">
-        <f>SUMIF('Payment Tracker'!C:C,B16,'Payment Tracker'!G:G)</f>
-        <v/>
-      </c>
+      <c r="B16" s="12" t="n"/>
+      <c r="C16" s="13" t="n"/>
       <c r="D16" s="6" t="n"/>
       <c r="E16" s="12" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F16" s="14">
@@ -3529,7 +3599,7 @@
       <c r="D17" s="6" t="n"/>
       <c r="E17" s="17" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Land Development</t>
         </is>
       </c>
       <c r="F17" s="19">
@@ -3568,7 +3638,7 @@
       <c r="D18" s="6" t="n"/>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Food/Provisions</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F18" s="14">
@@ -3578,7 +3648,7 @@
       <c r="G18" s="6" t="n"/>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Naveen Hardware</t>
+          <t>Daily Labour</t>
         </is>
       </c>
       <c r="I18" s="15">
@@ -3605,19 +3675,12 @@
       <c r="B19" s="6" t="n"/>
       <c r="C19" s="6" t="n"/>
       <c r="D19" s="6" t="n"/>
-      <c r="E19" s="17" t="inlineStr">
-        <is>
-          <t>Miscellaneous</t>
-        </is>
-      </c>
-      <c r="F19" s="19">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,E19)</f>
-        <v/>
-      </c>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="19" t="n"/>
       <c r="G19" s="6" t="n"/>
       <c r="H19" s="17" t="inlineStr">
         <is>
-          <t>Daily Labour</t>
+          <t>Khutauna Chirai mill</t>
         </is>
       </c>
       <c r="I19" s="20">
@@ -3688,15 +3751,15 @@
       <c r="G21" s="6" t="n"/>
       <c r="H21" s="17" t="inlineStr">
         <is>
-          <t>Sonbhai-Coordinator</t>
+          <t>Other vendors</t>
         </is>
       </c>
       <c r="I21" s="20">
-        <f>SUMIF('All Transactions'!H:H,H21,'All Transactions'!O:O)</f>
+        <f>'Vendor Summary'!C17-SUM(I12:I20)</f>
         <v/>
       </c>
       <c r="J21" s="20">
-        <f>SUMIF('Payment Tracker'!D:D,H21,'Payment Tracker'!G:G)</f>
+        <f>'Vendor Summary'!D17-SUM(J12:J20)</f>
         <v/>
       </c>
       <c r="K21" s="20">
@@ -5841,6 +5904,11 @@
           <t>Pcs</t>
         </is>
       </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Daily Labour</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
           <t>Dhalai Machine Rent</t>
@@ -5868,6 +5936,11 @@
           <t>Pcs</t>
         </is>
       </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Khutauna Chirai mill</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Dr Fixit</t>
@@ -5895,6 +5968,11 @@
           <t>Pcs</t>
         </is>
       </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>Engineer Labour Charge</t>
@@ -5920,6 +5998,11 @@
       <c r="C21" s="41" t="inlineStr">
         <is>
           <t>Pcs</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Mittal Electric</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -6539,7 +6622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R648"/>
+  <dimension ref="A1:R699"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -6827,7 +6910,7 @@
       </c>
       <c r="E7" s="55" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F7" s="55" t="inlineStr">
@@ -6900,7 +6983,7 @@
       </c>
       <c r="E8" s="47" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F8" s="47" t="inlineStr">
@@ -6973,7 +7056,7 @@
       </c>
       <c r="E9" s="55" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F9" s="55" t="inlineStr">
@@ -7186,7 +7269,7 @@
       </c>
       <c r="E12" s="47" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F12" s="47" t="inlineStr">
@@ -7568,7 +7651,7 @@
         </is>
       </c>
       <c r="K17" s="57" t="n">
-        <v>55</v>
+        <v>59.78260869565217</v>
       </c>
       <c r="L17" s="58">
         <f>IF(OR(I17="",K17=""),"",I17*K17)</f>
@@ -7639,7 +7722,7 @@
         </is>
       </c>
       <c r="K18" s="49" t="n">
-        <v>55</v>
+        <v>59.91285403050109</v>
       </c>
       <c r="L18" s="50">
         <f>IF(OR(I18="",K18=""),"",I18*K18)</f>
@@ -8159,7 +8242,7 @@
       </c>
       <c r="E26" s="55" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F26" s="55" t="inlineStr">
@@ -8227,7 +8310,7 @@
       </c>
       <c r="E27" s="47" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F27" s="47" t="inlineStr">
@@ -8295,7 +8378,7 @@
       </c>
       <c r="E28" s="55" t="inlineStr">
         <is>
-          <t>Food/Provisions</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F28" s="55" t="inlineStr">
@@ -8635,7 +8718,7 @@
       </c>
       <c r="E33" s="47" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F33" s="47" t="inlineStr">
@@ -8771,7 +8854,7 @@
       </c>
       <c r="E35" s="47" t="inlineStr">
         <is>
-          <t>Miscellaneous</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F35" s="47" t="inlineStr">
@@ -9315,7 +9398,7 @@
       </c>
       <c r="E43" s="47" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F43" s="47" t="inlineStr">
@@ -9803,7 +9886,7 @@
       </c>
       <c r="E50" s="55" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F50" s="55" t="inlineStr">
@@ -9876,7 +9959,7 @@
       </c>
       <c r="E51" s="47" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F51" s="47" t="inlineStr">
@@ -9949,7 +10032,7 @@
       </c>
       <c r="E52" s="55" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F52" s="55" t="inlineStr">
@@ -10022,7 +10105,7 @@
       </c>
       <c r="E53" s="47" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F53" s="47" t="inlineStr">
@@ -10235,7 +10318,7 @@
       </c>
       <c r="E56" s="55" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F56" s="55" t="inlineStr">
@@ -10590,7 +10673,7 @@
       </c>
       <c r="E61" s="47" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="F61" s="47" t="inlineStr">
@@ -10661,7 +10744,7 @@
       </c>
       <c r="E62" s="55" t="inlineStr">
         <is>
-          <t>Transport</t>
+          <t>Transport · Food · Misc</t>
         </is>
       </c>
       <c r="F62" s="55" t="inlineStr">
@@ -33085,6 +33168,57 @@
       <c r="P648" s="60" t="n"/>
       <c r="Q648" s="60" t="n"/>
     </row>
+    <row r="649"/>
+    <row r="650"/>
+    <row r="651"/>
+    <row r="652"/>
+    <row r="653"/>
+    <row r="654"/>
+    <row r="655"/>
+    <row r="656"/>
+    <row r="657"/>
+    <row r="658"/>
+    <row r="659"/>
+    <row r="660"/>
+    <row r="661"/>
+    <row r="662"/>
+    <row r="663"/>
+    <row r="664"/>
+    <row r="665"/>
+    <row r="666"/>
+    <row r="667"/>
+    <row r="668"/>
+    <row r="669"/>
+    <row r="670"/>
+    <row r="671"/>
+    <row r="672"/>
+    <row r="673"/>
+    <row r="674"/>
+    <row r="675"/>
+    <row r="676"/>
+    <row r="677"/>
+    <row r="678"/>
+    <row r="679"/>
+    <row r="680"/>
+    <row r="681"/>
+    <row r="682"/>
+    <row r="683"/>
+    <row r="684"/>
+    <row r="685"/>
+    <row r="686"/>
+    <row r="687"/>
+    <row r="688"/>
+    <row r="689"/>
+    <row r="690"/>
+    <row r="691"/>
+    <row r="692"/>
+    <row r="693"/>
+    <row r="694"/>
+    <row r="695"/>
+    <row r="696"/>
+    <row r="697"/>
+    <row r="698"/>
+    <row r="699"/>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
   <mergeCells count="2">
@@ -33146,7 +33280,7 @@
     <row r="1" ht="17.25" customHeight="1" s="99">
       <c r="A1" s="100" t="inlineStr">
         <is>
-          <t>VENDOR BILL / INVOICE — LINE ENTRY</t>
+          <t>VENDOR BILL / INVOICE — LINE ENTRY  (RETIRED — not maintained since May; use All Transactions)</t>
         </is>
       </c>
     </row>
@@ -45213,7 +45347,7 @@
         </is>
       </c>
       <c r="L6" s="93">
-        <f>IF(G7="","",IF(L6="",G7,L6+G7))</f>
+        <f>IF(G6="","",IF(L5="",G6,L5+G6))</f>
         <v/>
       </c>
       <c r="M6" s="47" t="n"/>
@@ -45257,7 +45391,7 @@
         </is>
       </c>
       <c r="L7" s="95">
-        <f>IF(G8="","",IF(L7="",G8,L7+G8))</f>
+        <f>IF(G7="","",IF(L6="",G7,L6+G7))</f>
         <v/>
       </c>
       <c r="M7" s="55" t="n"/>
@@ -45301,7 +45435,7 @@
         </is>
       </c>
       <c r="L8" s="93">
-        <f>IF(G9="","",IF(L8="",G9,L8+G9))</f>
+        <f>IF(G8="","",IF(L7="",G8,L7+G8))</f>
         <v/>
       </c>
       <c r="M8" s="47" t="n"/>
@@ -45345,7 +45479,7 @@
         </is>
       </c>
       <c r="L9" s="95">
-        <f>IF(G10="","",IF(L9="",G10,L9+G10))</f>
+        <f>IF(G9="","",IF(L8="",G9,L8+G9))</f>
         <v/>
       </c>
       <c r="M9" s="55" t="n"/>
@@ -45389,7 +45523,7 @@
         </is>
       </c>
       <c r="L10" s="93">
-        <f>IF(G11="","",IF(L10="",G11,L10+G11))</f>
+        <f>IF(G10="","",IF(L9="",G10,L9+G10))</f>
         <v/>
       </c>
       <c r="M10" s="47" t="n"/>
@@ -45433,7 +45567,7 @@
         </is>
       </c>
       <c r="L11" s="95">
-        <f>IF(G12="","",IF(L11="",G12,L11+G12))</f>
+        <f>IF(G11="","",IF(L10="",G11,L10+G11))</f>
         <v/>
       </c>
       <c r="M11" s="55" t="n"/>
@@ -45477,7 +45611,7 @@
         </is>
       </c>
       <c r="L12" s="93">
-        <f>IF(G13="","",IF(L12="",G13,L12+G13))</f>
+        <f>IF(G12="","",IF(L11="",G12,L11+G12))</f>
         <v/>
       </c>
       <c r="M12" s="47" t="n"/>
@@ -45521,7 +45655,7 @@
         </is>
       </c>
       <c r="L13" s="95">
-        <f>IF(G14="","",IF(L13="",G14,L13+G14))</f>
+        <f>IF(G13="","",IF(L12="",G13,L12+G13))</f>
         <v/>
       </c>
       <c r="M13" s="55" t="n"/>
@@ -45565,7 +45699,7 @@
         </is>
       </c>
       <c r="L14" s="95">
-        <f>IF(G16="","",IF(L15="",G16,L15+G16))</f>
+        <f>IF(G14="","",IF(L13="",G14,L13+G14))</f>
         <v/>
       </c>
       <c r="M14" s="55" t="n"/>
@@ -45609,7 +45743,7 @@
         </is>
       </c>
       <c r="L15" s="93">
-        <f>IF(G17="","",IF(L16="",G17,L16+G17))</f>
+        <f>IF(G15="","",IF(L14="",G15,L14+G15))</f>
         <v/>
       </c>
       <c r="M15" s="47" t="n"/>
@@ -45653,7 +45787,7 @@
         </is>
       </c>
       <c r="L16" s="95">
-        <f>IF(G18="","",IF(L17="",G18,L17+G18))</f>
+        <f>IF(G16="","",IF(L15="",G16,L15+G16))</f>
         <v/>
       </c>
       <c r="M16" s="55" t="n"/>
@@ -45697,7 +45831,7 @@
         </is>
       </c>
       <c r="L17" s="93">
-        <f>IF(G19="","",IF(L18="",G19,L18+G19))</f>
+        <f>IF(G17="","",IF(L16="",G17,L16+G17))</f>
         <v/>
       </c>
       <c r="M17" s="47" t="n"/>
@@ -45741,7 +45875,7 @@
         </is>
       </c>
       <c r="L18" s="95">
-        <f>IF(G20="","",IF(L19="",G20,L19+G20))</f>
+        <f>IF(G18="","",IF(L17="",G18,L17+G18))</f>
         <v/>
       </c>
       <c r="M18" s="55" t="n"/>
@@ -45785,7 +45919,7 @@
         </is>
       </c>
       <c r="L19" s="93">
-        <f>IF(G21="","",IF(L20="",G21,L20+G21))</f>
+        <f>IF(G19="","",IF(L18="",G19,L18+G19))</f>
         <v/>
       </c>
       <c r="M19" s="47" t="n"/>
@@ -45829,7 +45963,7 @@
         </is>
       </c>
       <c r="L20" s="95">
-        <f>IF(G22="","",IF(L21="",G22,L21+G22))</f>
+        <f>IF(G20="","",IF(L19="",G20,L19+G20))</f>
         <v/>
       </c>
       <c r="M20" s="55" t="n"/>
@@ -45873,7 +46007,7 @@
         </is>
       </c>
       <c r="L21" s="95">
-        <f>IF(G24="","",IF(L23="",G24,L23+G24))</f>
+        <f>IF(G21="","",IF(L20="",G21,L20+G21))</f>
         <v/>
       </c>
       <c r="M21" s="55" t="n"/>
@@ -45917,7 +46051,7 @@
         </is>
       </c>
       <c r="L22" s="93">
-        <f>IF(G25="","",IF(L24="",G25,L24+G25))</f>
+        <f>IF(G22="","",IF(L21="",G22,L21+G22))</f>
         <v/>
       </c>
       <c r="M22" s="47" t="n"/>
@@ -45961,7 +46095,7 @@
         </is>
       </c>
       <c r="L23" s="95">
-        <f>IF(G26="","",IF(L25="",G26,L25+G26))</f>
+        <f>IF(G23="","",IF(L22="",G23,L22+G23))</f>
         <v/>
       </c>
       <c r="M23" s="55" t="n"/>
@@ -46005,7 +46139,7 @@
         </is>
       </c>
       <c r="L24" s="93">
-        <f>IF(G27="","",IF(L26="",G27,L26+G27))</f>
+        <f>IF(G24="","",IF(L23="",G24,L23+G24))</f>
         <v/>
       </c>
       <c r="M24" s="47" t="n"/>
@@ -46049,7 +46183,7 @@
         </is>
       </c>
       <c r="L25" s="95">
-        <f>IF(G28="","",IF(L27="",G28,L27+G28))</f>
+        <f>IF(G25="","",IF(L24="",G25,L24+G25))</f>
         <v/>
       </c>
       <c r="M25" s="55" t="n"/>
@@ -46093,7 +46227,7 @@
         </is>
       </c>
       <c r="L26" s="93">
-        <f>IF(G29="","",IF(L28="",G29,L28+G29))</f>
+        <f>IF(G26="","",IF(L25="",G26,L25+G26))</f>
         <v/>
       </c>
       <c r="M26" s="47" t="n"/>
@@ -46141,7 +46275,7 @@
         </is>
       </c>
       <c r="L27" s="58">
-        <f>L29+G30</f>
+        <f>IF(G27="","",IF(L26="",G27,L26+G27))</f>
         <v/>
       </c>
       <c r="M27" s="55" t="n"/>
@@ -46189,7 +46323,7 @@
         </is>
       </c>
       <c r="L28" s="50">
-        <f>L30+G31</f>
+        <f>IF(G28="","",IF(L27="",G28,L27+G28))</f>
         <v/>
       </c>
       <c r="M28" s="47" t="n"/>
@@ -46237,7 +46371,7 @@
         </is>
       </c>
       <c r="L29" s="58">
-        <f>L31+G32</f>
+        <f>IF(G29="","",IF(L28="",G29,L28+G29))</f>
         <v/>
       </c>
       <c r="M29" s="55" t="n"/>
@@ -46285,7 +46419,7 @@
         </is>
       </c>
       <c r="L30" s="50">
-        <f>L32+G33</f>
+        <f>IF(G30="","",IF(L29="",G30,L29+G30))</f>
         <v/>
       </c>
       <c r="M30" s="47" t="n"/>
@@ -46333,7 +46467,7 @@
         </is>
       </c>
       <c r="L31" s="58">
-        <f>L33+G34</f>
+        <f>IF(G31="","",IF(L30="",G31,L30+G31))</f>
         <v/>
       </c>
       <c r="M31" s="55" t="n"/>
@@ -46381,7 +46515,7 @@
         </is>
       </c>
       <c r="L32" s="58">
-        <f>L35+G36</f>
+        <f>IF(G32="","",IF(L31="",G32,L31+G32))</f>
         <v/>
       </c>
       <c r="M32" s="55" t="n"/>
@@ -46429,7 +46563,7 @@
         </is>
       </c>
       <c r="L33" s="50">
-        <f>L36+G37</f>
+        <f>IF(G33="","",IF(L32="",G33,L32+G33))</f>
         <v/>
       </c>
       <c r="M33" s="47" t="n"/>
@@ -46477,7 +46611,7 @@
         </is>
       </c>
       <c r="L34" s="58">
-        <f>L37+G38</f>
+        <f>IF(G34="","",IF(L33="",G34,L33+G34))</f>
         <v/>
       </c>
       <c r="M34" s="55" t="n"/>
@@ -46525,7 +46659,7 @@
         </is>
       </c>
       <c r="L35" s="50">
-        <f>L38+G39</f>
+        <f>IF(G35="","",IF(L34="",G35,L34+G35))</f>
         <v/>
       </c>
       <c r="M35" s="47" t="n"/>
@@ -46573,7 +46707,7 @@
         </is>
       </c>
       <c r="L36" s="58">
-        <f>L39+G40</f>
+        <f>IF(G36="","",IF(L35="",G36,L35+G36))</f>
         <v/>
       </c>
       <c r="M36" s="55" t="n"/>
@@ -46621,7 +46755,7 @@
         </is>
       </c>
       <c r="L37" s="58">
-        <f>L41+G42</f>
+        <f>IF(G37="","",IF(L36="",G37,L36+G37))</f>
         <v/>
       </c>
       <c r="M37" s="55" t="n"/>
@@ -46668,7 +46802,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L38" s="58" t="n"/>
+      <c r="L38" s="58">
+        <f>IF(G38="","",IF(L37="",G38,L37+G38))</f>
+        <v/>
+      </c>
       <c r="M38" s="55" t="n"/>
     </row>
     <row r="39" ht="15.75" customHeight="1" s="99">
@@ -46713,7 +46850,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L39" s="58" t="n"/>
+      <c r="L39" s="58">
+        <f>IF(G39="","",IF(L38="",G39,L38+G39))</f>
+        <v/>
+      </c>
       <c r="M39" s="55" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" s="99">
@@ -46758,7 +46898,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L40" s="50" t="n"/>
+      <c r="L40" s="50">
+        <f>IF(G40="","",IF(L39="",G40,L39+G40))</f>
+        <v/>
+      </c>
       <c r="M40" s="47" t="n"/>
     </row>
     <row r="41" ht="15.75" customHeight="1" s="99">
@@ -46803,7 +46946,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L41" s="58" t="n"/>
+      <c r="L41" s="58">
+        <f>IF(G41="","",IF(L40="",G41,L40+G41))</f>
+        <v/>
+      </c>
       <c r="M41" s="55" t="n"/>
     </row>
     <row r="42" ht="15.75" customHeight="1" s="99">
@@ -46848,7 +46994,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L42" s="50" t="n"/>
+      <c r="L42" s="50">
+        <f>IF(G42="","",IF(L41="",G42,L41+G42))</f>
+        <v/>
+      </c>
       <c r="M42" s="47" t="n"/>
     </row>
     <row r="43" ht="15.75" customHeight="1" s="99">
@@ -46893,7 +47042,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L43" s="58" t="n"/>
+      <c r="L43" s="58">
+        <f>IF(G43="","",IF(L42="",G43,L42+G43))</f>
+        <v/>
+      </c>
       <c r="M43" s="55" t="n"/>
     </row>
     <row r="44" ht="15.75" customHeight="1" s="99">
@@ -46938,7 +47090,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L44" s="50" t="n"/>
+      <c r="L44" s="50">
+        <f>IF(G44="","",IF(L43="",G44,L43+G44))</f>
+        <v/>
+      </c>
       <c r="M44" s="47" t="n"/>
     </row>
     <row r="45" ht="15.75" customHeight="1" s="99">
@@ -46983,7 +47138,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L45" s="58" t="n"/>
+      <c r="L45" s="58">
+        <f>IF(G45="","",IF(L44="",G45,L44+G45))</f>
+        <v/>
+      </c>
       <c r="M45" s="55" t="n"/>
     </row>
     <row r="46" ht="15.75" customHeight="1" s="99">
@@ -47028,7 +47186,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L46" s="58" t="n"/>
+      <c r="L46" s="58">
+        <f>IF(G46="","",IF(L45="",G46,L45+G46))</f>
+        <v/>
+      </c>
       <c r="M46" s="55" t="n"/>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="99">
@@ -47073,7 +47234,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L47" s="58" t="n"/>
+      <c r="L47" s="58">
+        <f>IF(G47="","",IF(L46="",G47,L46+G47))</f>
+        <v/>
+      </c>
       <c r="M47" s="55" t="n"/>
     </row>
     <row r="48" ht="15.75" customHeight="1" s="99">
@@ -47118,7 +47282,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L48" s="50" t="n"/>
+      <c r="L48" s="50">
+        <f>IF(G48="","",IF(L47="",G48,L47+G48))</f>
+        <v/>
+      </c>
       <c r="M48" s="47" t="n"/>
     </row>
     <row r="49" ht="15.75" customHeight="1" s="99">
@@ -47163,7 +47330,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L49" s="50" t="n"/>
+      <c r="L49" s="50">
+        <f>IF(G49="","",IF(L48="",G49,L48+G49))</f>
+        <v/>
+      </c>
       <c r="M49" s="47" t="n"/>
     </row>
     <row r="50" ht="15.75" customHeight="1" s="99">
@@ -47208,7 +47378,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L50" s="58" t="n"/>
+      <c r="L50" s="58">
+        <f>IF(G50="","",IF(L49="",G50,L49+G50))</f>
+        <v/>
+      </c>
       <c r="M50" s="55" t="n"/>
     </row>
     <row r="51" ht="15.75" customHeight="1" s="99">
@@ -47253,7 +47426,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L51" s="50" t="n"/>
+      <c r="L51" s="50">
+        <f>IF(G51="","",IF(L50="",G51,L50+G51))</f>
+        <v/>
+      </c>
       <c r="M51" s="47" t="n"/>
     </row>
     <row r="52" ht="15.75" customHeight="1" s="99">
@@ -47298,7 +47474,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L52" s="58" t="n"/>
+      <c r="L52" s="58">
+        <f>IF(G52="","",IF(L51="",G52,L51+G52))</f>
+        <v/>
+      </c>
       <c r="M52" s="55" t="n"/>
     </row>
     <row r="53" ht="15.75" customHeight="1" s="99">
@@ -47343,7 +47522,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L53" s="50" t="n"/>
+      <c r="L53" s="50">
+        <f>IF(G53="","",IF(L52="",G53,L52+G53))</f>
+        <v/>
+      </c>
       <c r="M53" s="47" t="n"/>
     </row>
     <row r="54" ht="15.75" customHeight="1" s="99">
@@ -47388,7 +47570,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L54" s="58" t="n"/>
+      <c r="L54" s="58">
+        <f>IF(G54="","",IF(L53="",G54,L53+G54))</f>
+        <v/>
+      </c>
       <c r="M54" s="55" t="n"/>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="99">
@@ -47433,7 +47618,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L55" s="50" t="n"/>
+      <c r="L55" s="50">
+        <f>IF(G55="","",IF(L54="",G55,L54+G55))</f>
+        <v/>
+      </c>
       <c r="M55" s="47" t="n"/>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="99">
@@ -47478,7 +47666,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L56" s="58" t="n"/>
+      <c r="L56" s="58">
+        <f>IF(G56="","",IF(L55="",G56,L55+G56))</f>
+        <v/>
+      </c>
       <c r="M56" s="55" t="n"/>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="99">
@@ -47523,7 +47714,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L57" s="50" t="n"/>
+      <c r="L57" s="50">
+        <f>IF(G57="","",IF(L56="",G57,L56+G57))</f>
+        <v/>
+      </c>
       <c r="M57" s="47" t="n"/>
     </row>
     <row r="58" ht="15.75" customHeight="1" s="99">
@@ -47568,7 +47762,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L58" s="58" t="n"/>
+      <c r="L58" s="58">
+        <f>IF(G58="","",IF(L57="",G58,L57+G58))</f>
+        <v/>
+      </c>
       <c r="M58" s="55" t="n"/>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="99">
@@ -47613,7 +47810,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L59" s="50" t="n"/>
+      <c r="L59" s="50">
+        <f>IF(G59="","",IF(L58="",G59,L58+G59))</f>
+        <v/>
+      </c>
       <c r="M59" s="47" t="n"/>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="99">
@@ -47658,7 +47858,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L60" s="58" t="n"/>
+      <c r="L60" s="58">
+        <f>IF(G60="","",IF(L59="",G60,L59+G60))</f>
+        <v/>
+      </c>
       <c r="M60" s="55" t="n"/>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="99">
@@ -47703,7 +47906,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L61" s="50" t="n"/>
+      <c r="L61" s="50">
+        <f>IF(G61="","",IF(L60="",G61,L60+G61))</f>
+        <v/>
+      </c>
       <c r="M61" s="47" t="n"/>
     </row>
     <row r="62" ht="15.75" customHeight="1" s="99">
@@ -47748,7 +47954,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L62" s="58" t="n"/>
+      <c r="L62" s="58">
+        <f>IF(G62="","",IF(L61="",G62,L61+G62))</f>
+        <v/>
+      </c>
       <c r="M62" s="55" t="n"/>
     </row>
     <row r="63" ht="15.75" customHeight="1" s="99">
@@ -47793,7 +48002,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L63" s="50" t="n"/>
+      <c r="L63" s="50">
+        <f>IF(G63="","",IF(L62="",G63,L62+G63))</f>
+        <v/>
+      </c>
       <c r="M63" s="47" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="99">
@@ -47838,7 +48050,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L64" s="58" t="n"/>
+      <c r="L64" s="58">
+        <f>IF(G64="","",IF(L63="",G64,L63+G64))</f>
+        <v/>
+      </c>
       <c r="M64" s="55" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="99">
@@ -47883,7 +48098,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L65" s="50" t="n"/>
+      <c r="L65" s="50">
+        <f>IF(G65="","",IF(L64="",G65,L64+G65))</f>
+        <v/>
+      </c>
       <c r="M65" s="47" t="n"/>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="99">
@@ -47928,7 +48146,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L66" s="58" t="n"/>
+      <c r="L66" s="58">
+        <f>IF(G66="","",IF(L65="",G66,L65+G66))</f>
+        <v/>
+      </c>
       <c r="M66" s="55" t="n"/>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="99">
@@ -47973,7 +48194,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L67" s="50" t="n"/>
+      <c r="L67" s="50">
+        <f>IF(G67="","",IF(L66="",G67,L66+G67))</f>
+        <v/>
+      </c>
       <c r="M67" s="47" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="99">
@@ -48018,7 +48242,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L68" s="58" t="n"/>
+      <c r="L68" s="58">
+        <f>IF(G68="","",IF(L67="",G68,L67+G68))</f>
+        <v/>
+      </c>
       <c r="M68" s="55" t="n"/>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="99">
@@ -48063,7 +48290,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L69" s="50" t="n"/>
+      <c r="L69" s="50">
+        <f>IF(G69="","",IF(L68="",G69,L68+G69))</f>
+        <v/>
+      </c>
       <c r="M69" s="47" t="n"/>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="99">
@@ -48108,7 +48338,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L70" s="58" t="n"/>
+      <c r="L70" s="58">
+        <f>IF(G70="","",IF(L69="",G70,L69+G70))</f>
+        <v/>
+      </c>
       <c r="M70" s="55" t="n"/>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="99">
@@ -48153,7 +48386,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L71" s="50" t="n"/>
+      <c r="L71" s="50">
+        <f>IF(G71="","",IF(L70="",G71,L70+G71))</f>
+        <v/>
+      </c>
       <c r="M71" s="47" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="99">
@@ -48198,7 +48434,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L72" s="58" t="n"/>
+      <c r="L72" s="58">
+        <f>IF(G72="","",IF(L71="",G72,L71+G72))</f>
+        <v/>
+      </c>
       <c r="M72" s="55" t="n"/>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="99">
@@ -48243,7 +48482,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L73" s="50" t="n"/>
+      <c r="L73" s="50">
+        <f>IF(G73="","",IF(L72="",G73,L72+G73))</f>
+        <v/>
+      </c>
       <c r="M73" s="47" t="n"/>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="99">
@@ -48288,7 +48530,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L74" s="58" t="n"/>
+      <c r="L74" s="58">
+        <f>IF(G74="","",IF(L73="",G74,L73+G74))</f>
+        <v/>
+      </c>
       <c r="M74" s="55" t="n"/>
     </row>
     <row r="75" ht="15.75" customHeight="1" s="99">
@@ -48333,7 +48578,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L75" s="50" t="n"/>
+      <c r="L75" s="50">
+        <f>IF(G75="","",IF(L74="",G75,L74+G75))</f>
+        <v/>
+      </c>
       <c r="M75" s="47" t="n"/>
     </row>
     <row r="76" ht="15.75" customHeight="1" s="99">
@@ -48378,7 +48626,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L76" s="58" t="n"/>
+      <c r="L76" s="58">
+        <f>IF(G76="","",IF(L75="",G76,L75+G76))</f>
+        <v/>
+      </c>
       <c r="M76" s="55" t="n"/>
     </row>
     <row r="77" ht="15.75" customHeight="1" s="99">
@@ -48423,7 +48674,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L77" s="50" t="n"/>
+      <c r="L77" s="50">
+        <f>IF(G77="","",IF(L76="",G77,L76+G77))</f>
+        <v/>
+      </c>
       <c r="M77" s="47" t="n"/>
     </row>
     <row r="78" ht="15.75" customHeight="1" s="99">
@@ -48468,7 +48722,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L78" s="58" t="n"/>
+      <c r="L78" s="58">
+        <f>IF(G78="","",IF(L77="",G78,L77+G78))</f>
+        <v/>
+      </c>
       <c r="M78" s="55" t="n"/>
     </row>
     <row r="79" ht="15.75" customHeight="1" s="99">
@@ -48513,7 +48770,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L79" s="50" t="n"/>
+      <c r="L79" s="50">
+        <f>IF(G79="","",IF(L78="",G79,L78+G79))</f>
+        <v/>
+      </c>
       <c r="M79" s="47" t="n"/>
     </row>
     <row r="80" ht="15.75" customHeight="1" s="99">
@@ -48558,7 +48818,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L80" s="58" t="n"/>
+      <c r="L80" s="58">
+        <f>IF(G80="","",IF(L79="",G80,L79+G80))</f>
+        <v/>
+      </c>
       <c r="M80" s="55" t="n"/>
     </row>
     <row r="81" ht="15.75" customHeight="1" s="99">
@@ -48603,7 +48866,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L81" s="50" t="n"/>
+      <c r="L81" s="50">
+        <f>IF(G81="","",IF(L80="",G81,L80+G81))</f>
+        <v/>
+      </c>
       <c r="M81" s="47" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="99">
@@ -48648,7 +48914,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L82" s="58" t="n"/>
+      <c r="L82" s="58">
+        <f>IF(G82="","",IF(L81="",G82,L81+G82))</f>
+        <v/>
+      </c>
       <c r="M82" s="55" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="99">
@@ -48693,7 +48962,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L83" s="50" t="n"/>
+      <c r="L83" s="50">
+        <f>IF(G83="","",IF(L82="",G83,L82+G83))</f>
+        <v/>
+      </c>
       <c r="M83" s="47" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="99">
@@ -48738,7 +49010,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L84" s="58" t="n"/>
+      <c r="L84" s="58">
+        <f>IF(G84="","",IF(L83="",G84,L83+G84))</f>
+        <v/>
+      </c>
       <c r="M84" s="55" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="99">
@@ -48783,7 +49058,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L85" s="50" t="n"/>
+      <c r="L85" s="50">
+        <f>IF(G85="","",IF(L84="",G85,L84+G85))</f>
+        <v/>
+      </c>
       <c r="M85" s="47" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="99">
@@ -48828,7 +49106,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L86" s="58" t="n"/>
+      <c r="L86" s="58">
+        <f>IF(G86="","",IF(L85="",G86,L85+G86))</f>
+        <v/>
+      </c>
       <c r="M86" s="55" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="99">
@@ -48873,7 +49154,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L87" s="50" t="n"/>
+      <c r="L87" s="50">
+        <f>IF(G87="","",IF(L86="",G87,L86+G87))</f>
+        <v/>
+      </c>
       <c r="M87" s="47" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="99">
@@ -48918,7 +49202,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L88" s="58" t="n"/>
+      <c r="L88" s="58">
+        <f>IF(G88="","",IF(L87="",G88,L87+G88))</f>
+        <v/>
+      </c>
       <c r="M88" s="55" t="n"/>
     </row>
     <row r="89" ht="15.75" customHeight="1" s="99">
@@ -48963,7 +49250,10 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="L89" s="50" t="n"/>
+      <c r="L89" s="50">
+        <f>IF(G89="","",IF(L88="",G89,L88+G89))</f>
+        <v/>
+      </c>
       <c r="M89" s="47" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="99">
@@ -49009,7 +49299,7 @@
         </is>
       </c>
       <c r="L90" s="58">
-        <f>IF(G100="","",IF(L99="",G100,L99+G100))</f>
+        <f>IF(G90="","",IF(L89="",G90,L89+G90))</f>
         <v/>
       </c>
       <c r="M90" s="55" t="n"/>
@@ -49057,7 +49347,7 @@
         </is>
       </c>
       <c r="L91" s="50">
-        <f>IF(G101="","",IF(L100="",G101,L100+G101))</f>
+        <f>IF(G91="","",IF(L90="",G91,L90+G91))</f>
         <v/>
       </c>
       <c r="M91" s="47" t="n"/>
@@ -49105,7 +49395,7 @@
         </is>
       </c>
       <c r="L92" s="58">
-        <f>IF(G102="","",IF(L101="",G102,L101+G102))</f>
+        <f>IF(G92="","",IF(L91="",G92,L91+G92))</f>
         <v/>
       </c>
       <c r="M92" s="55" t="n"/>
@@ -49153,7 +49443,7 @@
         </is>
       </c>
       <c r="L93" s="50">
-        <f>IF(G103="","",IF(L102="",G103,L102+G103))</f>
+        <f>IF(G93="","",IF(L92="",G93,L92+G93))</f>
         <v/>
       </c>
       <c r="M93" s="47" t="n"/>
@@ -49201,7 +49491,7 @@
         </is>
       </c>
       <c r="L94" s="58">
-        <f>IF(G104="","",IF(L103="",G104,L103+G104))</f>
+        <f>IF(G94="","",IF(L93="",G94,L93+G94))</f>
         <v/>
       </c>
       <c r="M94" s="55" t="n"/>
@@ -49249,7 +49539,7 @@
         </is>
       </c>
       <c r="L95" s="50">
-        <f>IF(G105="","",IF(L104="",G105,L104+G105))</f>
+        <f>IF(G95="","",IF(L94="",G95,L94+G95))</f>
         <v/>
       </c>
       <c r="M95" s="47" t="n"/>
@@ -49297,7 +49587,7 @@
         </is>
       </c>
       <c r="L96" s="58">
-        <f>IF(G106="","",IF(L105="",G106,L105+G106))</f>
+        <f>IF(G96="","",IF(L95="",G96,L95+G96))</f>
         <v/>
       </c>
       <c r="M96" s="55" t="n"/>
@@ -49345,7 +49635,7 @@
         </is>
       </c>
       <c r="L97" s="50">
-        <f>IF(G107="","",IF(L106="",G107,L106+G107))</f>
+        <f>IF(G97="","",IF(L96="",G97,L96+G97))</f>
         <v/>
       </c>
       <c r="M97" s="47" t="n"/>
@@ -49393,7 +49683,7 @@
         </is>
       </c>
       <c r="L98" s="58">
-        <f>IF(G108="","",IF(L107="",G108,L107+G108))</f>
+        <f>IF(G98="","",IF(L97="",G98,L97+G98))</f>
         <v/>
       </c>
       <c r="M98" s="55" t="n"/>
@@ -49441,7 +49731,7 @@
         </is>
       </c>
       <c r="L99" s="50">
-        <f>IF(G109="","",IF(L108="",G109,L108+G109))</f>
+        <f>IF(G99="","",IF(L98="",G99,L98+G99))</f>
         <v/>
       </c>
       <c r="M99" s="47" t="n"/>
@@ -49489,7 +49779,7 @@
         </is>
       </c>
       <c r="L100" s="58">
-        <f>IF(G110="","",IF(L109="",G110,L109+G110))</f>
+        <f>IF(G100="","",IF(L99="",G100,L99+G100))</f>
         <v/>
       </c>
       <c r="M100" s="55" t="n"/>
@@ -49537,7 +49827,7 @@
         </is>
       </c>
       <c r="L101" s="50">
-        <f>IF(G111="","",IF(L110="",G111,L110+G111))</f>
+        <f>IF(G101="","",IF(L100="",G101,L100+G101))</f>
         <v/>
       </c>
       <c r="M101" s="47" t="n"/>
@@ -49585,7 +49875,7 @@
         </is>
       </c>
       <c r="L102" s="58">
-        <f>IF(G112="","",IF(L111="",G112,L111+G112))</f>
+        <f>IF(G102="","",IF(L101="",G102,L101+G102))</f>
         <v/>
       </c>
       <c r="M102" s="55" t="n"/>
@@ -49633,7 +49923,7 @@
         </is>
       </c>
       <c r="L103" s="50">
-        <f>IF(G113="","",IF(L112="",G113,L112+G113))</f>
+        <f>IF(G103="","",IF(L102="",G103,L102+G103))</f>
         <v/>
       </c>
       <c r="M103" s="47" t="n"/>
@@ -49681,7 +49971,7 @@
         </is>
       </c>
       <c r="L104" s="58">
-        <f>IF(G114="","",IF(L113="",G114,L113+G114))</f>
+        <f>IF(G104="","",IF(L103="",G104,L103+G104))</f>
         <v/>
       </c>
       <c r="M104" s="55" t="n"/>
@@ -49729,7 +50019,7 @@
         </is>
       </c>
       <c r="L105" s="50">
-        <f>IF(G115="","",IF(L114="",G115,L114+G115))</f>
+        <f>IF(G105="","",IF(L104="",G105,L104+G105))</f>
         <v/>
       </c>
       <c r="M105" s="47" t="n"/>
@@ -49777,7 +50067,7 @@
         </is>
       </c>
       <c r="L106" s="58">
-        <f>IF(G116="","",IF(L115="",G116,L115+G116))</f>
+        <f>IF(G106="","",IF(L105="",G106,L105+G106))</f>
         <v/>
       </c>
       <c r="M106" s="55" t="n"/>
@@ -49825,7 +50115,7 @@
         </is>
       </c>
       <c r="L107" s="50">
-        <f>IF(G117="","",IF(L116="",G117,L116+G117))</f>
+        <f>IF(G107="","",IF(L106="",G107,L106+G107))</f>
         <v/>
       </c>
       <c r="M107" s="47" t="n"/>
@@ -49873,7 +50163,7 @@
         </is>
       </c>
       <c r="L108" s="58">
-        <f>IF(G118="","",IF(L117="",G118,L117+G118))</f>
+        <f>IF(G108="","",IF(L107="",G108,L107+G108))</f>
         <v/>
       </c>
       <c r="M108" s="55" t="n"/>
@@ -49921,7 +50211,7 @@
         </is>
       </c>
       <c r="L109" s="50">
-        <f>IF(G119="","",IF(L118="",G119,L118+G119))</f>
+        <f>IF(G109="","",IF(L108="",G109,L108+G109))</f>
         <v/>
       </c>
       <c r="M109" s="47" t="n"/>
@@ -49941,7 +50231,7 @@
       <c r="J110" s="55" t="n"/>
       <c r="K110" s="55" t="n"/>
       <c r="L110" s="58">
-        <f>IF(G120="","",IF(L119="",G120,L119+G120))</f>
+        <f>IF(G110="","",IF(L109="",G110,L109+G110))</f>
         <v/>
       </c>
       <c r="M110" s="55" t="n"/>
@@ -49961,7 +50251,7 @@
       <c r="J111" s="47" t="n"/>
       <c r="K111" s="47" t="n"/>
       <c r="L111" s="50">
-        <f>IF(G121="","",IF(L120="",G121,L120+G121))</f>
+        <f>IF(G111="","",IF(L110="",G111,L110+G111))</f>
         <v/>
       </c>
       <c r="M111" s="47" t="n"/>
@@ -49981,7 +50271,7 @@
       <c r="J112" s="55" t="n"/>
       <c r="K112" s="55" t="n"/>
       <c r="L112" s="58">
-        <f>IF(G122="","",IF(L121="",G122,L121+G122))</f>
+        <f>IF(G112="","",IF(L111="",G112,L111+G112))</f>
         <v/>
       </c>
       <c r="M112" s="55" t="n"/>
@@ -50001,7 +50291,7 @@
       <c r="J113" s="47" t="n"/>
       <c r="K113" s="47" t="n"/>
       <c r="L113" s="50">
-        <f>IF(G123="","",IF(L122="",G123,L122+G123))</f>
+        <f>IF(G113="","",IF(L112="",G113,L112+G113))</f>
         <v/>
       </c>
       <c r="M113" s="47" t="n"/>
@@ -50021,7 +50311,7 @@
       <c r="J114" s="55" t="n"/>
       <c r="K114" s="55" t="n"/>
       <c r="L114" s="58">
-        <f>IF(G124="","",IF(L123="",G124,L123+G124))</f>
+        <f>IF(G114="","",IF(L113="",G114,L113+G114))</f>
         <v/>
       </c>
       <c r="M114" s="55" t="n"/>
@@ -50041,7 +50331,7 @@
       <c r="J115" s="47" t="n"/>
       <c r="K115" s="47" t="n"/>
       <c r="L115" s="50">
-        <f>IF(G125="","",IF(L124="",G125,L124+G125))</f>
+        <f>IF(G115="","",IF(L114="",G115,L114+G115))</f>
         <v/>
       </c>
       <c r="M115" s="47" t="n"/>
@@ -50061,7 +50351,7 @@
       <c r="J116" s="55" t="n"/>
       <c r="K116" s="55" t="n"/>
       <c r="L116" s="58">
-        <f>IF(G126="","",IF(L125="",G126,L125+G126))</f>
+        <f>IF(G116="","",IF(L115="",G116,L115+G116))</f>
         <v/>
       </c>
       <c r="M116" s="55" t="n"/>
@@ -50081,7 +50371,7 @@
       <c r="J117" s="47" t="n"/>
       <c r="K117" s="47" t="n"/>
       <c r="L117" s="50">
-        <f>IF(G127="","",IF(L126="",G127,L126+G127))</f>
+        <f>IF(G117="","",IF(L116="",G117,L116+G117))</f>
         <v/>
       </c>
       <c r="M117" s="47" t="n"/>
@@ -50101,7 +50391,7 @@
       <c r="J118" s="55" t="n"/>
       <c r="K118" s="55" t="n"/>
       <c r="L118" s="58">
-        <f>IF(G128="","",IF(L127="",G128,L127+G128))</f>
+        <f>IF(G118="","",IF(L117="",G118,L117+G118))</f>
         <v/>
       </c>
       <c r="M118" s="55" t="n"/>
@@ -50121,7 +50411,7 @@
       <c r="J119" s="47" t="n"/>
       <c r="K119" s="47" t="n"/>
       <c r="L119" s="50">
-        <f>IF(G129="","",IF(L128="",G129,L128+G129))</f>
+        <f>IF(G119="","",IF(L118="",G119,L118+G119))</f>
         <v/>
       </c>
       <c r="M119" s="47" t="n"/>
@@ -50141,7 +50431,7 @@
       <c r="J120" s="55" t="n"/>
       <c r="K120" s="55" t="n"/>
       <c r="L120" s="58">
-        <f>IF(G130="","",IF(L129="",G130,L129+G130))</f>
+        <f>IF(G120="","",IF(L119="",G120,L119+G120))</f>
         <v/>
       </c>
       <c r="M120" s="55" t="n"/>
@@ -50161,7 +50451,7 @@
       <c r="J121" s="47" t="n"/>
       <c r="K121" s="47" t="n"/>
       <c r="L121" s="50">
-        <f>IF(G131="","",IF(L130="",G131,L130+G131))</f>
+        <f>IF(G121="","",IF(L120="",G121,L120+G121))</f>
         <v/>
       </c>
       <c r="M121" s="47" t="n"/>
@@ -50181,7 +50471,7 @@
       <c r="J122" s="55" t="n"/>
       <c r="K122" s="55" t="n"/>
       <c r="L122" s="58">
-        <f>IF(G132="","",IF(L131="",G132,L131+G132))</f>
+        <f>IF(G122="","",IF(L121="",G122,L121+G122))</f>
         <v/>
       </c>
       <c r="M122" s="55" t="n"/>
@@ -50201,7 +50491,7 @@
       <c r="J123" s="47" t="n"/>
       <c r="K123" s="47" t="n"/>
       <c r="L123" s="50">
-        <f>IF(G133="","",IF(L132="",G133,L132+G133))</f>
+        <f>IF(G123="","",IF(L122="",G123,L122+G123))</f>
         <v/>
       </c>
       <c r="M123" s="47" t="n"/>
@@ -50221,7 +50511,7 @@
       <c r="J124" s="55" t="n"/>
       <c r="K124" s="55" t="n"/>
       <c r="L124" s="58">
-        <f>IF(G134="","",IF(L133="",G134,L133+G134))</f>
+        <f>IF(G124="","",IF(L123="",G124,L123+G124))</f>
         <v/>
       </c>
       <c r="M124" s="55" t="n"/>
@@ -50241,7 +50531,7 @@
       <c r="J125" s="47" t="n"/>
       <c r="K125" s="47" t="n"/>
       <c r="L125" s="50">
-        <f>IF(G135="","",IF(L134="",G135,L134+G135))</f>
+        <f>IF(G125="","",IF(L124="",G125,L124+G125))</f>
         <v/>
       </c>
       <c r="M125" s="47" t="n"/>
@@ -50261,7 +50551,7 @@
       <c r="J126" s="55" t="n"/>
       <c r="K126" s="55" t="n"/>
       <c r="L126" s="58">
-        <f>IF(G136="","",IF(L135="",G136,L135+G136))</f>
+        <f>IF(G126="","",IF(L125="",G126,L125+G126))</f>
         <v/>
       </c>
       <c r="M126" s="55" t="n"/>
@@ -50281,7 +50571,7 @@
       <c r="J127" s="47" t="n"/>
       <c r="K127" s="47" t="n"/>
       <c r="L127" s="50">
-        <f>IF(G137="","",IF(L136="",G137,L136+G137))</f>
+        <f>IF(G127="","",IF(L126="",G127,L126+G127))</f>
         <v/>
       </c>
       <c r="M127" s="47" t="n"/>
@@ -50301,7 +50591,7 @@
       <c r="J128" s="55" t="n"/>
       <c r="K128" s="55" t="n"/>
       <c r="L128" s="58">
-        <f>IF(G138="","",IF(L137="",G138,L137+G138))</f>
+        <f>IF(G128="","",IF(L127="",G128,L127+G128))</f>
         <v/>
       </c>
       <c r="M128" s="55" t="n"/>
@@ -50321,7 +50611,7 @@
       <c r="J129" s="47" t="n"/>
       <c r="K129" s="47" t="n"/>
       <c r="L129" s="50">
-        <f>IF(G139="","",IF(L138="",G139,L138+G139))</f>
+        <f>IF(G129="","",IF(L128="",G129,L128+G129))</f>
         <v/>
       </c>
       <c r="M129" s="47" t="n"/>
@@ -50341,7 +50631,7 @@
       <c r="J130" s="55" t="n"/>
       <c r="K130" s="55" t="n"/>
       <c r="L130" s="58">
-        <f>IF(G140="","",IF(L139="",G140,L139+G140))</f>
+        <f>IF(G130="","",IF(L129="",G130,L129+G130))</f>
         <v/>
       </c>
       <c r="M130" s="55" t="n"/>
@@ -50361,7 +50651,7 @@
       <c r="J131" s="47" t="n"/>
       <c r="K131" s="47" t="n"/>
       <c r="L131" s="50">
-        <f>IF(G141="","",IF(L140="",G141,L140+G141))</f>
+        <f>IF(G131="","",IF(L130="",G131,L130+G131))</f>
         <v/>
       </c>
       <c r="M131" s="47" t="n"/>
@@ -50381,7 +50671,7 @@
       <c r="J132" s="55" t="n"/>
       <c r="K132" s="55" t="n"/>
       <c r="L132" s="58">
-        <f>IF(G142="","",IF(L141="",G142,L141+G142))</f>
+        <f>IF(G132="","",IF(L131="",G132,L131+G132))</f>
         <v/>
       </c>
       <c r="M132" s="55" t="n"/>
@@ -50401,7 +50691,7 @@
       <c r="J133" s="47" t="n"/>
       <c r="K133" s="47" t="n"/>
       <c r="L133" s="50">
-        <f>IF(G143="","",IF(L142="",G143,L142+G143))</f>
+        <f>IF(G133="","",IF(L132="",G133,L132+G133))</f>
         <v/>
       </c>
       <c r="M133" s="47" t="n"/>
@@ -50421,7 +50711,7 @@
       <c r="J134" s="55" t="n"/>
       <c r="K134" s="55" t="n"/>
       <c r="L134" s="58">
-        <f>IF(G144="","",IF(L143="",G144,L143+G144))</f>
+        <f>IF(G134="","",IF(L133="",G134,L133+G134))</f>
         <v/>
       </c>
       <c r="M134" s="55" t="n"/>
@@ -50441,7 +50731,7 @@
       <c r="J135" s="47" t="n"/>
       <c r="K135" s="47" t="n"/>
       <c r="L135" s="50">
-        <f>IF(G145="","",IF(L144="",G145,L144+G145))</f>
+        <f>IF(G135="","",IF(L134="",G135,L134+G135))</f>
         <v/>
       </c>
       <c r="M135" s="47" t="n"/>
@@ -50461,7 +50751,7 @@
       <c r="J136" s="55" t="n"/>
       <c r="K136" s="55" t="n"/>
       <c r="L136" s="58">
-        <f>IF(G146="","",IF(L145="",G146,L145+G146))</f>
+        <f>IF(G136="","",IF(L135="",G136,L135+G136))</f>
         <v/>
       </c>
       <c r="M136" s="55" t="n"/>
@@ -50481,7 +50771,7 @@
       <c r="J137" s="47" t="n"/>
       <c r="K137" s="47" t="n"/>
       <c r="L137" s="50">
-        <f>IF(G147="","",IF(L146="",G147,L146+G147))</f>
+        <f>IF(G137="","",IF(L136="",G137,L136+G137))</f>
         <v/>
       </c>
       <c r="M137" s="47" t="n"/>
@@ -50501,7 +50791,7 @@
       <c r="J138" s="55" t="n"/>
       <c r="K138" s="55" t="n"/>
       <c r="L138" s="58">
-        <f>IF(G148="","",IF(L147="",G148,L147+G148))</f>
+        <f>IF(G138="","",IF(L137="",G138,L137+G138))</f>
         <v/>
       </c>
       <c r="M138" s="55" t="n"/>
@@ -50521,7 +50811,7 @@
       <c r="J139" s="47" t="n"/>
       <c r="K139" s="47" t="n"/>
       <c r="L139" s="50">
-        <f>IF(G149="","",IF(L148="",G149,L148+G149))</f>
+        <f>IF(G139="","",IF(L138="",G139,L138+G139))</f>
         <v/>
       </c>
       <c r="M139" s="47" t="n"/>
@@ -50541,7 +50831,7 @@
       <c r="J140" s="55" t="n"/>
       <c r="K140" s="55" t="n"/>
       <c r="L140" s="58">
-        <f>IF(G150="","",IF(L149="",G150,L149+G150))</f>
+        <f>IF(G140="","",IF(L139="",G140,L139+G140))</f>
         <v/>
       </c>
       <c r="M140" s="55" t="n"/>
@@ -50561,7 +50851,7 @@
       <c r="J141" s="47" t="n"/>
       <c r="K141" s="47" t="n"/>
       <c r="L141" s="50">
-        <f>IF(G151="","",IF(L150="",G151,L150+G151))</f>
+        <f>IF(G141="","",IF(L140="",G141,L140+G141))</f>
         <v/>
       </c>
       <c r="M141" s="47" t="n"/>
@@ -50581,7 +50871,7 @@
       <c r="J142" s="55" t="n"/>
       <c r="K142" s="55" t="n"/>
       <c r="L142" s="58">
-        <f>IF(G152="","",IF(L151="",G152,L151+G152))</f>
+        <f>IF(G142="","",IF(L141="",G142,L141+G142))</f>
         <v/>
       </c>
       <c r="M142" s="55" t="n"/>
@@ -50601,7 +50891,7 @@
       <c r="J143" s="47" t="n"/>
       <c r="K143" s="47" t="n"/>
       <c r="L143" s="50">
-        <f>IF(G153="","",IF(L152="",G153,L152+G153))</f>
+        <f>IF(G143="","",IF(L142="",G143,L142+G143))</f>
         <v/>
       </c>
       <c r="M143" s="47" t="n"/>
@@ -50621,7 +50911,7 @@
       <c r="J144" s="55" t="n"/>
       <c r="K144" s="55" t="n"/>
       <c r="L144" s="58">
-        <f>IF(G154="","",IF(L153="",G154,L153+G154))</f>
+        <f>IF(G144="","",IF(L143="",G144,L143+G144))</f>
         <v/>
       </c>
       <c r="M144" s="55" t="n"/>
@@ -50641,7 +50931,7 @@
       <c r="J145" s="47" t="n"/>
       <c r="K145" s="47" t="n"/>
       <c r="L145" s="50">
-        <f>IF(G155="","",IF(L154="",G155,L154+G155))</f>
+        <f>IF(G145="","",IF(L144="",G145,L144+G145))</f>
         <v/>
       </c>
       <c r="M145" s="47" t="n"/>
@@ -50661,7 +50951,7 @@
       <c r="J146" s="55" t="n"/>
       <c r="K146" s="55" t="n"/>
       <c r="L146" s="58">
-        <f>IF(G156="","",IF(L155="",G156,L155+G156))</f>
+        <f>IF(G146="","",IF(L145="",G146,L145+G146))</f>
         <v/>
       </c>
       <c r="M146" s="55" t="n"/>
@@ -50681,7 +50971,7 @@
       <c r="J147" s="47" t="n"/>
       <c r="K147" s="47" t="n"/>
       <c r="L147" s="50">
-        <f>IF(G157="","",IF(L156="",G157,L156+G157))</f>
+        <f>IF(G147="","",IF(L146="",G147,L146+G147))</f>
         <v/>
       </c>
       <c r="M147" s="47" t="n"/>
@@ -50701,7 +50991,7 @@
       <c r="J148" s="55" t="n"/>
       <c r="K148" s="55" t="n"/>
       <c r="L148" s="58">
-        <f>IF(G158="","",IF(L157="",G158,L157+G158))</f>
+        <f>IF(G148="","",IF(L147="",G148,L147+G148))</f>
         <v/>
       </c>
       <c r="M148" s="55" t="n"/>
@@ -50721,7 +51011,7 @@
       <c r="J149" s="47" t="n"/>
       <c r="K149" s="47" t="n"/>
       <c r="L149" s="50">
-        <f>IF(G159="","",IF(L158="",G159,L158+G159))</f>
+        <f>IF(G149="","",IF(L148="",G149,L148+G149))</f>
         <v/>
       </c>
       <c r="M149" s="47" t="n"/>
@@ -50741,7 +51031,7 @@
       <c r="J150" s="55" t="n"/>
       <c r="K150" s="55" t="n"/>
       <c r="L150" s="58">
-        <f>IF(G160="","",IF(L159="",G160,L159+G160))</f>
+        <f>IF(G150="","",IF(L149="",G150,L149+G150))</f>
         <v/>
       </c>
       <c r="M150" s="55" t="n"/>
@@ -50761,7 +51051,7 @@
       <c r="J151" s="47" t="n"/>
       <c r="K151" s="47" t="n"/>
       <c r="L151" s="50">
-        <f>IF(G161="","",IF(L160="",G161,L160+G161))</f>
+        <f>IF(G151="","",IF(L150="",G151,L150+G151))</f>
         <v/>
       </c>
       <c r="M151" s="47" t="n"/>
@@ -50781,7 +51071,7 @@
       <c r="J152" s="55" t="n"/>
       <c r="K152" s="55" t="n"/>
       <c r="L152" s="58">
-        <f>IF(G162="","",IF(L161="",G162,L161+G162))</f>
+        <f>IF(G152="","",IF(L151="",G152,L151+G152))</f>
         <v/>
       </c>
       <c r="M152" s="55" t="n"/>
@@ -50801,7 +51091,7 @@
       <c r="J153" s="47" t="n"/>
       <c r="K153" s="47" t="n"/>
       <c r="L153" s="50">
-        <f>IF(G163="","",IF(L162="",G163,L162+G163))</f>
+        <f>IF(G153="","",IF(L152="",G153,L152+G153))</f>
         <v/>
       </c>
       <c r="M153" s="47" t="n"/>
@@ -50821,7 +51111,7 @@
       <c r="J154" s="55" t="n"/>
       <c r="K154" s="55" t="n"/>
       <c r="L154" s="58">
-        <f>IF(G164="","",IF(L163="",G164,L163+G164))</f>
+        <f>IF(G154="","",IF(L153="",G154,L153+G154))</f>
         <v/>
       </c>
       <c r="M154" s="55" t="n"/>
@@ -50841,7 +51131,7 @@
       <c r="J155" s="47" t="n"/>
       <c r="K155" s="47" t="n"/>
       <c r="L155" s="50">
-        <f>IF(G165="","",IF(L164="",G165,L164+G165))</f>
+        <f>IF(G155="","",IF(L154="",G155,L154+G155))</f>
         <v/>
       </c>
       <c r="M155" s="47" t="n"/>
@@ -50861,7 +51151,7 @@
       <c r="J156" s="55" t="n"/>
       <c r="K156" s="55" t="n"/>
       <c r="L156" s="58">
-        <f>IF(G166="","",IF(L165="",G166,L165+G166))</f>
+        <f>IF(G156="","",IF(L155="",G156,L155+G156))</f>
         <v/>
       </c>
       <c r="M156" s="55" t="n"/>
@@ -50881,7 +51171,7 @@
       <c r="J157" s="47" t="n"/>
       <c r="K157" s="47" t="n"/>
       <c r="L157" s="50">
-        <f>IF(G167="","",IF(L166="",G167,L166+G167))</f>
+        <f>IF(G157="","",IF(L156="",G157,L156+G157))</f>
         <v/>
       </c>
       <c r="M157" s="47" t="n"/>
@@ -50901,7 +51191,7 @@
       <c r="J158" s="55" t="n"/>
       <c r="K158" s="55" t="n"/>
       <c r="L158" s="58">
-        <f>IF(G168="","",IF(L167="",G168,L167+G168))</f>
+        <f>IF(G158="","",IF(L157="",G158,L157+G158))</f>
         <v/>
       </c>
       <c r="M158" s="55" t="n"/>
@@ -50921,7 +51211,7 @@
       <c r="J159" s="47" t="n"/>
       <c r="K159" s="47" t="n"/>
       <c r="L159" s="50">
-        <f>IF(G169="","",IF(L168="",G169,L168+G169))</f>
+        <f>IF(G159="","",IF(L158="",G159,L158+G159))</f>
         <v/>
       </c>
       <c r="M159" s="47" t="n"/>
@@ -50941,7 +51231,7 @@
       <c r="J160" s="55" t="n"/>
       <c r="K160" s="55" t="n"/>
       <c r="L160" s="58">
-        <f>IF(G170="","",IF(L169="",G170,L169+G170))</f>
+        <f>IF(G160="","",IF(L159="",G160,L159+G160))</f>
         <v/>
       </c>
       <c r="M160" s="55" t="n"/>
@@ -50961,7 +51251,7 @@
       <c r="J161" s="47" t="n"/>
       <c r="K161" s="47" t="n"/>
       <c r="L161" s="50">
-        <f>IF(G171="","",IF(L170="",G171,L170+G171))</f>
+        <f>IF(G161="","",IF(L160="",G161,L160+G161))</f>
         <v/>
       </c>
       <c r="M161" s="47" t="n"/>
@@ -50981,7 +51271,7 @@
       <c r="J162" s="55" t="n"/>
       <c r="K162" s="55" t="n"/>
       <c r="L162" s="58">
-        <f>IF(G172="","",IF(L171="",G172,L171+G172))</f>
+        <f>IF(G162="","",IF(L161="",G162,L161+G162))</f>
         <v/>
       </c>
       <c r="M162" s="55" t="n"/>
@@ -51001,7 +51291,7 @@
       <c r="J163" s="47" t="n"/>
       <c r="K163" s="47" t="n"/>
       <c r="L163" s="50">
-        <f>IF(G173="","",IF(L172="",G173,L172+G173))</f>
+        <f>IF(G163="","",IF(L162="",G163,L162+G163))</f>
         <v/>
       </c>
       <c r="M163" s="47" t="n"/>
@@ -51021,7 +51311,7 @@
       <c r="J164" s="55" t="n"/>
       <c r="K164" s="55" t="n"/>
       <c r="L164" s="58">
-        <f>IF(G174="","",IF(L173="",G174,L173+G174))</f>
+        <f>IF(G164="","",IF(L163="",G164,L163+G164))</f>
         <v/>
       </c>
       <c r="M164" s="55" t="n"/>
@@ -51041,7 +51331,7 @@
       <c r="J165" s="47" t="n"/>
       <c r="K165" s="47" t="n"/>
       <c r="L165" s="50">
-        <f>IF(G175="","",IF(L174="",G175,L174+G175))</f>
+        <f>IF(G165="","",IF(L164="",G165,L164+G165))</f>
         <v/>
       </c>
       <c r="M165" s="47" t="n"/>
@@ -51061,7 +51351,7 @@
       <c r="J166" s="55" t="n"/>
       <c r="K166" s="55" t="n"/>
       <c r="L166" s="58">
-        <f>IF(G176="","",IF(L175="",G176,L175+G176))</f>
+        <f>IF(G166="","",IF(L165="",G166,L165+G166))</f>
         <v/>
       </c>
       <c r="M166" s="55" t="n"/>
@@ -51081,7 +51371,7 @@
       <c r="J167" s="47" t="n"/>
       <c r="K167" s="47" t="n"/>
       <c r="L167" s="50">
-        <f>IF(G177="","",IF(L176="",G177,L176+G177))</f>
+        <f>IF(G167="","",IF(L166="",G167,L166+G167))</f>
         <v/>
       </c>
       <c r="M167" s="47" t="n"/>
@@ -51101,7 +51391,7 @@
       <c r="J168" s="55" t="n"/>
       <c r="K168" s="55" t="n"/>
       <c r="L168" s="58">
-        <f>IF(G178="","",IF(L177="",G178,L177+G178))</f>
+        <f>IF(G168="","",IF(L167="",G168,L167+G168))</f>
         <v/>
       </c>
       <c r="M168" s="55" t="n"/>
@@ -51121,7 +51411,7 @@
       <c r="J169" s="47" t="n"/>
       <c r="K169" s="47" t="n"/>
       <c r="L169" s="50">
-        <f>IF(G179="","",IF(L178="",G179,L178+G179))</f>
+        <f>IF(G169="","",IF(L168="",G169,L168+G169))</f>
         <v/>
       </c>
       <c r="M169" s="47" t="n"/>
@@ -51141,7 +51431,7 @@
       <c r="J170" s="55" t="n"/>
       <c r="K170" s="55" t="n"/>
       <c r="L170" s="58">
-        <f>IF(G180="","",IF(L179="",G180,L179+G180))</f>
+        <f>IF(G170="","",IF(L169="",G170,L169+G170))</f>
         <v/>
       </c>
       <c r="M170" s="55" t="n"/>
@@ -51161,7 +51451,7 @@
       <c r="J171" s="47" t="n"/>
       <c r="K171" s="47" t="n"/>
       <c r="L171" s="50">
-        <f>IF(G181="","",IF(L180="",G181,L180+G181))</f>
+        <f>IF(G171="","",IF(L170="",G171,L170+G171))</f>
         <v/>
       </c>
       <c r="M171" s="47" t="n"/>
@@ -51181,7 +51471,7 @@
       <c r="J172" s="55" t="n"/>
       <c r="K172" s="55" t="n"/>
       <c r="L172" s="58">
-        <f>IF(G182="","",IF(L181="",G182,L181+G182))</f>
+        <f>IF(G172="","",IF(L171="",G172,L171+G172))</f>
         <v/>
       </c>
       <c r="M172" s="55" t="n"/>
@@ -51201,7 +51491,7 @@
       <c r="J173" s="47" t="n"/>
       <c r="K173" s="47" t="n"/>
       <c r="L173" s="50">
-        <f>IF(G183="","",IF(L182="",G183,L182+G183))</f>
+        <f>IF(G173="","",IF(L172="",G173,L172+G173))</f>
         <v/>
       </c>
       <c r="M173" s="47" t="n"/>
@@ -51221,7 +51511,7 @@
       <c r="J174" s="55" t="n"/>
       <c r="K174" s="55" t="n"/>
       <c r="L174" s="58">
-        <f>IF(G184="","",IF(L183="",G184,L183+G184))</f>
+        <f>IF(G174="","",IF(L173="",G174,L173+G174))</f>
         <v/>
       </c>
       <c r="M174" s="55" t="n"/>
@@ -51241,7 +51531,7 @@
       <c r="J175" s="47" t="n"/>
       <c r="K175" s="47" t="n"/>
       <c r="L175" s="50">
-        <f>IF(G185="","",IF(L184="",G185,L184+G185))</f>
+        <f>IF(G175="","",IF(L174="",G175,L174+G175))</f>
         <v/>
       </c>
       <c r="M175" s="47" t="n"/>
@@ -51261,7 +51551,7 @@
       <c r="J176" s="55" t="n"/>
       <c r="K176" s="55" t="n"/>
       <c r="L176" s="58">
-        <f>IF(G186="","",IF(L185="",G186,L185+G186))</f>
+        <f>IF(G176="","",IF(L175="",G176,L175+G176))</f>
         <v/>
       </c>
       <c r="M176" s="55" t="n"/>
@@ -51281,7 +51571,7 @@
       <c r="J177" s="47" t="n"/>
       <c r="K177" s="47" t="n"/>
       <c r="L177" s="50">
-        <f>IF(G187="","",IF(L186="",G187,L186+G187))</f>
+        <f>IF(G177="","",IF(L176="",G177,L176+G177))</f>
         <v/>
       </c>
       <c r="M177" s="47" t="n"/>
@@ -51301,7 +51591,7 @@
       <c r="J178" s="55" t="n"/>
       <c r="K178" s="55" t="n"/>
       <c r="L178" s="58">
-        <f>IF(G188="","",IF(L187="",G188,L187+G188))</f>
+        <f>IF(G178="","",IF(L177="",G178,L177+G178))</f>
         <v/>
       </c>
       <c r="M178" s="55" t="n"/>
@@ -51321,7 +51611,7 @@
       <c r="J179" s="47" t="n"/>
       <c r="K179" s="47" t="n"/>
       <c r="L179" s="50">
-        <f>IF(G189="","",IF(L188="",G189,L188+G189))</f>
+        <f>IF(G179="","",IF(L178="",G179,L178+G179))</f>
         <v/>
       </c>
       <c r="M179" s="47" t="n"/>
@@ -51341,7 +51631,7 @@
       <c r="J180" s="55" t="n"/>
       <c r="K180" s="55" t="n"/>
       <c r="L180" s="58">
-        <f>IF(G190="","",IF(L189="",G190,L189+G190))</f>
+        <f>IF(G180="","",IF(L179="",G180,L179+G180))</f>
         <v/>
       </c>
       <c r="M180" s="55" t="n"/>
@@ -51361,7 +51651,7 @@
       <c r="J181" s="47" t="n"/>
       <c r="K181" s="47" t="n"/>
       <c r="L181" s="50">
-        <f>IF(G191="","",IF(L190="",G191,L190+G191))</f>
+        <f>IF(G181="","",IF(L180="",G181,L180+G181))</f>
         <v/>
       </c>
       <c r="M181" s="47" t="n"/>
@@ -51381,7 +51671,7 @@
       <c r="J182" s="55" t="n"/>
       <c r="K182" s="55" t="n"/>
       <c r="L182" s="58">
-        <f>IF(G192="","",IF(L191="",G192,L191+G192))</f>
+        <f>IF(G182="","",IF(L181="",G182,L181+G182))</f>
         <v/>
       </c>
       <c r="M182" s="55" t="n"/>
@@ -51401,7 +51691,7 @@
       <c r="J183" s="47" t="n"/>
       <c r="K183" s="47" t="n"/>
       <c r="L183" s="50">
-        <f>IF(G193="","",IF(L192="",G193,L192+G193))</f>
+        <f>IF(G183="","",IF(L182="",G183,L182+G183))</f>
         <v/>
       </c>
       <c r="M183" s="47" t="n"/>
@@ -51421,7 +51711,7 @@
       <c r="J184" s="55" t="n"/>
       <c r="K184" s="55" t="n"/>
       <c r="L184" s="58">
-        <f>IF(G194="","",IF(L193="",G194,L193+G194))</f>
+        <f>IF(G184="","",IF(L183="",G184,L183+G184))</f>
         <v/>
       </c>
       <c r="M184" s="55" t="n"/>
@@ -51441,7 +51731,7 @@
       <c r="J185" s="47" t="n"/>
       <c r="K185" s="47" t="n"/>
       <c r="L185" s="50">
-        <f>IF(G195="","",IF(L194="",G195,L194+G195))</f>
+        <f>IF(G185="","",IF(L184="",G185,L184+G185))</f>
         <v/>
       </c>
       <c r="M185" s="47" t="n"/>
@@ -51461,7 +51751,7 @@
       <c r="J186" s="55" t="n"/>
       <c r="K186" s="55" t="n"/>
       <c r="L186" s="58">
-        <f>IF(G196="","",IF(L195="",G196,L195+G196))</f>
+        <f>IF(G186="","",IF(L185="",G186,L185+G186))</f>
         <v/>
       </c>
       <c r="M186" s="55" t="n"/>
@@ -51481,7 +51771,7 @@
       <c r="J187" s="47" t="n"/>
       <c r="K187" s="47" t="n"/>
       <c r="L187" s="50">
-        <f>IF(G197="","",IF(L196="",G197,L196+G197))</f>
+        <f>IF(G187="","",IF(L186="",G187,L186+G187))</f>
         <v/>
       </c>
       <c r="M187" s="47" t="n"/>
@@ -51501,7 +51791,7 @@
       <c r="J188" s="55" t="n"/>
       <c r="K188" s="55" t="n"/>
       <c r="L188" s="58">
-        <f>IF(G198="","",IF(L197="",G198,L197+G198))</f>
+        <f>IF(G188="","",IF(L187="",G188,L187+G188))</f>
         <v/>
       </c>
       <c r="M188" s="55" t="n"/>
@@ -51521,7 +51811,7 @@
       <c r="J189" s="47" t="n"/>
       <c r="K189" s="47" t="n"/>
       <c r="L189" s="50">
-        <f>IF(G199="","",IF(L198="",G199,L198+G199))</f>
+        <f>IF(G189="","",IF(L188="",G189,L188+G189))</f>
         <v/>
       </c>
       <c r="M189" s="47" t="n"/>
@@ -51541,7 +51831,7 @@
       <c r="J190" s="55" t="n"/>
       <c r="K190" s="55" t="n"/>
       <c r="L190" s="58">
-        <f>IF(G200="","",IF(L199="",G200,L199+G200))</f>
+        <f>IF(G190="","",IF(L189="",G190,L189+G190))</f>
         <v/>
       </c>
       <c r="M190" s="55" t="n"/>
@@ -51561,7 +51851,7 @@
       <c r="J191" s="47" t="n"/>
       <c r="K191" s="47" t="n"/>
       <c r="L191" s="50">
-        <f>IF(G201="","",IF(L200="",G201,L200+G201))</f>
+        <f>IF(G191="","",IF(L190="",G191,L190+G191))</f>
         <v/>
       </c>
       <c r="M191" s="47" t="n"/>
@@ -51581,7 +51871,7 @@
       <c r="J192" s="55" t="n"/>
       <c r="K192" s="55" t="n"/>
       <c r="L192" s="58">
-        <f>IF(G202="","",IF(L201="",G202,L201+G202))</f>
+        <f>IF(G192="","",IF(L191="",G192,L191+G192))</f>
         <v/>
       </c>
       <c r="M192" s="55" t="n"/>
@@ -51601,7 +51891,7 @@
       <c r="J193" s="47" t="n"/>
       <c r="K193" s="47" t="n"/>
       <c r="L193" s="50">
-        <f>IF(G203="","",IF(L202="",G203,L202+G203))</f>
+        <f>IF(G193="","",IF(L192="",G193,L192+G193))</f>
         <v/>
       </c>
       <c r="M193" s="47" t="n"/>
@@ -51621,7 +51911,7 @@
       <c r="J194" s="55" t="n"/>
       <c r="K194" s="55" t="n"/>
       <c r="L194" s="58">
-        <f>IF(G204="","",IF(L203="",G204,L203+G204))</f>
+        <f>IF(G194="","",IF(L193="",G194,L193+G194))</f>
         <v/>
       </c>
       <c r="M194" s="55" t="n"/>
@@ -51641,7 +51931,7 @@
       <c r="J195" s="47" t="n"/>
       <c r="K195" s="47" t="n"/>
       <c r="L195" s="50">
-        <f>IF(G205="","",IF(L204="",G205,L204+G205))</f>
+        <f>IF(G195="","",IF(L194="",G195,L194+G195))</f>
         <v/>
       </c>
       <c r="M195" s="47" t="n"/>
@@ -51661,7 +51951,7 @@
       <c r="J196" s="55" t="n"/>
       <c r="K196" s="55" t="n"/>
       <c r="L196" s="58">
-        <f>IF(G206="","",IF(L205="",G206,L205+G206))</f>
+        <f>IF(G196="","",IF(L195="",G196,L195+G196))</f>
         <v/>
       </c>
       <c r="M196" s="55" t="n"/>
@@ -51681,7 +51971,7 @@
       <c r="J197" s="47" t="n"/>
       <c r="K197" s="47" t="n"/>
       <c r="L197" s="50">
-        <f>IF(G207="","",IF(L206="",G207,L206+G207))</f>
+        <f>IF(G197="","",IF(L196="",G197,L196+G197))</f>
         <v/>
       </c>
       <c r="M197" s="47" t="n"/>
@@ -51701,7 +51991,7 @@
       <c r="J198" s="55" t="n"/>
       <c r="K198" s="55" t="n"/>
       <c r="L198" s="58">
-        <f>IF(G208="","",IF(L207="",G208,L207+G208))</f>
+        <f>IF(G198="","",IF(L197="",G198,L197+G198))</f>
         <v/>
       </c>
       <c r="M198" s="55" t="n"/>
@@ -51721,7 +52011,7 @@
       <c r="J199" s="47" t="n"/>
       <c r="K199" s="47" t="n"/>
       <c r="L199" s="50">
-        <f>IF(G209="","",IF(L208="",G209,L208+G209))</f>
+        <f>IF(G199="","",IF(L198="",G199,L198+G199))</f>
         <v/>
       </c>
       <c r="M199" s="47" t="n"/>
@@ -51741,7 +52031,7 @@
       <c r="J200" s="55" t="n"/>
       <c r="K200" s="55" t="n"/>
       <c r="L200" s="58">
-        <f>IF(G210="","",IF(L209="",G210,L209+G210))</f>
+        <f>IF(G200="","",IF(L199="",G200,L199+G200))</f>
         <v/>
       </c>
       <c r="M200" s="55" t="n"/>
@@ -51761,7 +52051,7 @@
       <c r="J201" s="47" t="n"/>
       <c r="K201" s="47" t="n"/>
       <c r="L201" s="50">
-        <f>IF(G211="","",IF(L210="",G211,L210+G211))</f>
+        <f>IF(G201="","",IF(L200="",G201,L200+G201))</f>
         <v/>
       </c>
       <c r="M201" s="47" t="n"/>
@@ -51781,7 +52071,7 @@
       <c r="J202" s="55" t="n"/>
       <c r="K202" s="55" t="n"/>
       <c r="L202" s="58">
-        <f>IF(G212="","",IF(L211="",G212,L211+G212))</f>
+        <f>IF(G202="","",IF(L201="",G202,L201+G202))</f>
         <v/>
       </c>
       <c r="M202" s="55" t="n"/>
@@ -51801,7 +52091,7 @@
       <c r="J203" s="47" t="n"/>
       <c r="K203" s="47" t="n"/>
       <c r="L203" s="50">
-        <f>IF(G213="","",IF(L212="",G213,L212+G213))</f>
+        <f>IF(G203="","",IF(L202="",G203,L202+G203))</f>
         <v/>
       </c>
       <c r="M203" s="47" t="n"/>
@@ -51821,7 +52111,7 @@
       <c r="J204" s="55" t="n"/>
       <c r="K204" s="55" t="n"/>
       <c r="L204" s="58">
-        <f>IF(G214="","",IF(L213="",G214,L213+G214))</f>
+        <f>IF(G204="","",IF(L203="",G204,L203+G204))</f>
         <v/>
       </c>
       <c r="M204" s="55" t="n"/>
@@ -51841,7 +52131,7 @@
       <c r="J205" s="47" t="n"/>
       <c r="K205" s="47" t="n"/>
       <c r="L205" s="50">
-        <f>IF(G215="","",IF(L214="",G215,L214+G215))</f>
+        <f>IF(G205="","",IF(L204="",G205,L204+G205))</f>
         <v/>
       </c>
       <c r="M205" s="47" t="n"/>
@@ -51861,7 +52151,7 @@
       <c r="J206" s="55" t="n"/>
       <c r="K206" s="55" t="n"/>
       <c r="L206" s="58">
-        <f>IF(G216="","",IF(L215="",G216,L215+G216))</f>
+        <f>IF(G206="","",IF(L205="",G206,L205+G206))</f>
         <v/>
       </c>
       <c r="M206" s="55" t="n"/>
@@ -51881,7 +52171,7 @@
       <c r="J207" s="47" t="n"/>
       <c r="K207" s="47" t="n"/>
       <c r="L207" s="50">
-        <f>IF(G217="","",IF(L216="",G217,L216+G217))</f>
+        <f>IF(G207="","",IF(L206="",G207,L206+G207))</f>
         <v/>
       </c>
       <c r="M207" s="47" t="n"/>
@@ -51901,7 +52191,7 @@
       <c r="J208" s="55" t="n"/>
       <c r="K208" s="55" t="n"/>
       <c r="L208" s="58">
-        <f>IF(G218="","",IF(L217="",G218,L217+G218))</f>
+        <f>IF(G208="","",IF(L207="",G208,L207+G208))</f>
         <v/>
       </c>
       <c r="M208" s="55" t="n"/>
@@ -51921,7 +52211,7 @@
       <c r="J209" s="47" t="n"/>
       <c r="K209" s="47" t="n"/>
       <c r="L209" s="50">
-        <f>IF(G219="","",IF(L218="",G219,L218+G219))</f>
+        <f>IF(G209="","",IF(L208="",G209,L208+G209))</f>
         <v/>
       </c>
       <c r="M209" s="47" t="n"/>
@@ -51941,7 +52231,7 @@
       <c r="J210" s="55" t="n"/>
       <c r="K210" s="55" t="n"/>
       <c r="L210" s="58">
-        <f>IF(G220="","",IF(L219="",G220,L219+G220))</f>
+        <f>IF(G210="","",IF(L209="",G210,L209+G210))</f>
         <v/>
       </c>
       <c r="M210" s="55" t="n"/>
@@ -51961,7 +52251,7 @@
       <c r="J211" s="47" t="n"/>
       <c r="K211" s="47" t="n"/>
       <c r="L211" s="50">
-        <f>IF(G221="","",IF(L220="",G221,L220+G221))</f>
+        <f>IF(G211="","",IF(L210="",G211,L210+G211))</f>
         <v/>
       </c>
       <c r="M211" s="47" t="n"/>
@@ -51981,7 +52271,7 @@
       <c r="J212" s="55" t="n"/>
       <c r="K212" s="55" t="n"/>
       <c r="L212" s="58">
-        <f>IF(G222="","",IF(L221="",G222,L221+G222))</f>
+        <f>IF(G212="","",IF(L211="",G212,L211+G212))</f>
         <v/>
       </c>
       <c r="M212" s="55" t="n"/>
@@ -52001,7 +52291,7 @@
       <c r="J213" s="47" t="n"/>
       <c r="K213" s="47" t="n"/>
       <c r="L213" s="50">
-        <f>IF(G223="","",IF(L222="",G223,L222+G223))</f>
+        <f>IF(G213="","",IF(L212="",G213,L212+G213))</f>
         <v/>
       </c>
       <c r="M213" s="47" t="n"/>
@@ -52021,7 +52311,7 @@
       <c r="J214" s="55" t="n"/>
       <c r="K214" s="55" t="n"/>
       <c r="L214" s="58">
-        <f>IF(G224="","",IF(L223="",G224,L223+G224))</f>
+        <f>IF(G214="","",IF(L213="",G214,L213+G214))</f>
         <v/>
       </c>
       <c r="M214" s="55" t="n"/>
@@ -52041,7 +52331,7 @@
       <c r="J215" s="47" t="n"/>
       <c r="K215" s="47" t="n"/>
       <c r="L215" s="50">
-        <f>IF(G225="","",IF(L224="",G225,L224+G225))</f>
+        <f>IF(G215="","",IF(L214="",G215,L214+G215))</f>
         <v/>
       </c>
       <c r="M215" s="47" t="n"/>
@@ -52061,7 +52351,7 @@
       <c r="J216" s="55" t="n"/>
       <c r="K216" s="55" t="n"/>
       <c r="L216" s="58">
-        <f>IF(G226="","",IF(L225="",G226,L225+G226))</f>
+        <f>IF(G216="","",IF(L215="",G216,L215+G216))</f>
         <v/>
       </c>
       <c r="M216" s="55" t="n"/>
@@ -52081,7 +52371,7 @@
       <c r="J217" s="47" t="n"/>
       <c r="K217" s="47" t="n"/>
       <c r="L217" s="50">
-        <f>IF(G227="","",IF(L226="",G227,L226+G227))</f>
+        <f>IF(G217="","",IF(L216="",G217,L216+G217))</f>
         <v/>
       </c>
       <c r="M217" s="47" t="n"/>
@@ -52101,7 +52391,7 @@
       <c r="J218" s="55" t="n"/>
       <c r="K218" s="55" t="n"/>
       <c r="L218" s="58">
-        <f>IF(G228="","",IF(L227="",G228,L227+G228))</f>
+        <f>IF(G218="","",IF(L217="",G218,L217+G218))</f>
         <v/>
       </c>
       <c r="M218" s="55" t="n"/>
@@ -52121,7 +52411,7 @@
       <c r="J219" s="47" t="n"/>
       <c r="K219" s="47" t="n"/>
       <c r="L219" s="50">
-        <f>IF(G229="","",IF(L228="",G229,L228+G229))</f>
+        <f>IF(G219="","",IF(L218="",G219,L218+G219))</f>
         <v/>
       </c>
       <c r="M219" s="47" t="n"/>
@@ -52141,7 +52431,7 @@
       <c r="J220" s="55" t="n"/>
       <c r="K220" s="55" t="n"/>
       <c r="L220" s="58">
-        <f>IF(G230="","",IF(L229="",G230,L229+G230))</f>
+        <f>IF(G220="","",IF(L219="",G220,L219+G220))</f>
         <v/>
       </c>
       <c r="M220" s="55" t="n"/>
@@ -52161,7 +52451,7 @@
       <c r="J221" s="47" t="n"/>
       <c r="K221" s="47" t="n"/>
       <c r="L221" s="50">
-        <f>IF(G231="","",IF(L230="",G231,L230+G231))</f>
+        <f>IF(G221="","",IF(L220="",G221,L220+G221))</f>
         <v/>
       </c>
       <c r="M221" s="47" t="n"/>
@@ -52181,7 +52471,7 @@
       <c r="J222" s="55" t="n"/>
       <c r="K222" s="55" t="n"/>
       <c r="L222" s="58">
-        <f>IF(G232="","",IF(L231="",G232,L231+G232))</f>
+        <f>IF(G222="","",IF(L221="",G222,L221+G222))</f>
         <v/>
       </c>
       <c r="M222" s="55" t="n"/>
@@ -52201,7 +52491,7 @@
       <c r="J223" s="47" t="n"/>
       <c r="K223" s="47" t="n"/>
       <c r="L223" s="50">
-        <f>IF(G233="","",IF(L232="",G233,L232+G233))</f>
+        <f>IF(G223="","",IF(L222="",G223,L222+G223))</f>
         <v/>
       </c>
       <c r="M223" s="47" t="n"/>
@@ -52221,7 +52511,7 @@
       <c r="J224" s="55" t="n"/>
       <c r="K224" s="55" t="n"/>
       <c r="L224" s="58">
-        <f>IF(G234="","",IF(L233="",G234,L233+G234))</f>
+        <f>IF(G224="","",IF(L223="",G224,L223+G224))</f>
         <v/>
       </c>
       <c r="M224" s="55" t="n"/>
@@ -52241,7 +52531,7 @@
       <c r="J225" s="47" t="n"/>
       <c r="K225" s="47" t="n"/>
       <c r="L225" s="50">
-        <f>IF(G235="","",IF(L234="",G235,L234+G235))</f>
+        <f>IF(G225="","",IF(L224="",G225,L224+G225))</f>
         <v/>
       </c>
       <c r="M225" s="47" t="n"/>
@@ -52261,7 +52551,7 @@
       <c r="J226" s="55" t="n"/>
       <c r="K226" s="55" t="n"/>
       <c r="L226" s="58">
-        <f>IF(G236="","",IF(L235="",G236,L235+G236))</f>
+        <f>IF(G226="","",IF(L225="",G226,L225+G226))</f>
         <v/>
       </c>
       <c r="M226" s="55" t="n"/>
@@ -52281,7 +52571,7 @@
       <c r="J227" s="47" t="n"/>
       <c r="K227" s="47" t="n"/>
       <c r="L227" s="50">
-        <f>IF(G237="","",IF(L236="",G237,L236+G237))</f>
+        <f>IF(G227="","",IF(L226="",G227,L226+G227))</f>
         <v/>
       </c>
       <c r="M227" s="47" t="n"/>
@@ -52301,7 +52591,7 @@
       <c r="J228" s="55" t="n"/>
       <c r="K228" s="55" t="n"/>
       <c r="L228" s="58">
-        <f>IF(G238="","",IF(L237="",G238,L237+G238))</f>
+        <f>IF(G228="","",IF(L227="",G228,L227+G228))</f>
         <v/>
       </c>
       <c r="M228" s="55" t="n"/>
@@ -52321,7 +52611,7 @@
       <c r="J229" s="47" t="n"/>
       <c r="K229" s="47" t="n"/>
       <c r="L229" s="50">
-        <f>IF(G239="","",IF(L238="",G239,L238+G239))</f>
+        <f>IF(G229="","",IF(L228="",G229,L228+G229))</f>
         <v/>
       </c>
       <c r="M229" s="47" t="n"/>
@@ -52341,7 +52631,7 @@
       <c r="J230" s="55" t="n"/>
       <c r="K230" s="55" t="n"/>
       <c r="L230" s="58">
-        <f>IF(G240="","",IF(L239="",G240,L239+G240))</f>
+        <f>IF(G230="","",IF(L229="",G230,L229+G230))</f>
         <v/>
       </c>
       <c r="M230" s="55" t="n"/>
@@ -52361,7 +52651,7 @@
       <c r="J231" s="47" t="n"/>
       <c r="K231" s="47" t="n"/>
       <c r="L231" s="50">
-        <f>IF(G241="","",IF(L240="",G241,L240+G241))</f>
+        <f>IF(G231="","",IF(L230="",G231,L230+G231))</f>
         <v/>
       </c>
       <c r="M231" s="47" t="n"/>
@@ -52381,7 +52671,7 @@
       <c r="J232" s="55" t="n"/>
       <c r="K232" s="55" t="n"/>
       <c r="L232" s="58">
-        <f>IF(G242="","",IF(L241="",G242,L241+G242))</f>
+        <f>IF(G232="","",IF(L231="",G232,L231+G232))</f>
         <v/>
       </c>
       <c r="M232" s="55" t="n"/>
@@ -52401,7 +52691,7 @@
       <c r="J233" s="47" t="n"/>
       <c r="K233" s="47" t="n"/>
       <c r="L233" s="50">
-        <f>IF(G243="","",IF(L242="",G243,L242+G243))</f>
+        <f>IF(G233="","",IF(L232="",G233,L232+G233))</f>
         <v/>
       </c>
       <c r="M233" s="47" t="n"/>
@@ -52421,7 +52711,7 @@
       <c r="J234" s="55" t="n"/>
       <c r="K234" s="55" t="n"/>
       <c r="L234" s="58">
-        <f>IF(G244="","",IF(L243="",G244,L243+G244))</f>
+        <f>IF(G234="","",IF(L233="",G234,L233+G234))</f>
         <v/>
       </c>
       <c r="M234" s="55" t="n"/>
@@ -52441,7 +52731,7 @@
       <c r="J235" s="47" t="n"/>
       <c r="K235" s="47" t="n"/>
       <c r="L235" s="50">
-        <f>IF(G245="","",IF(L244="",G245,L244+G245))</f>
+        <f>IF(G235="","",IF(L234="",G235,L234+G235))</f>
         <v/>
       </c>
       <c r="M235" s="47" t="n"/>
@@ -52461,7 +52751,7 @@
       <c r="J236" s="55" t="n"/>
       <c r="K236" s="55" t="n"/>
       <c r="L236" s="58">
-        <f>IF(G246="","",IF(L245="",G246,L245+G246))</f>
+        <f>IF(G236="","",IF(L235="",G236,L235+G236))</f>
         <v/>
       </c>
       <c r="M236" s="55" t="n"/>
@@ -52481,7 +52771,7 @@
       <c r="J237" s="47" t="n"/>
       <c r="K237" s="47" t="n"/>
       <c r="L237" s="50">
-        <f>IF(G247="","",IF(L246="",G247,L246+G247))</f>
+        <f>IF(G237="","",IF(L236="",G237,L236+G237))</f>
         <v/>
       </c>
       <c r="M237" s="47" t="n"/>
@@ -52501,7 +52791,7 @@
       <c r="J238" s="55" t="n"/>
       <c r="K238" s="55" t="n"/>
       <c r="L238" s="58">
-        <f>IF(G248="","",IF(L247="",G248,L247+G248))</f>
+        <f>IF(G238="","",IF(L237="",G238,L237+G238))</f>
         <v/>
       </c>
       <c r="M238" s="55" t="n"/>
@@ -52521,7 +52811,7 @@
       <c r="J239" s="47" t="n"/>
       <c r="K239" s="47" t="n"/>
       <c r="L239" s="50">
-        <f>IF(G249="","",IF(L248="",G249,L248+G249))</f>
+        <f>IF(G239="","",IF(L238="",G239,L238+G239))</f>
         <v/>
       </c>
       <c r="M239" s="47" t="n"/>
@@ -52541,7 +52831,7 @@
       <c r="J240" s="55" t="n"/>
       <c r="K240" s="55" t="n"/>
       <c r="L240" s="58">
-        <f>IF(G250="","",IF(L249="",G250,L249+G250))</f>
+        <f>IF(G240="","",IF(L239="",G240,L239+G240))</f>
         <v/>
       </c>
       <c r="M240" s="55" t="n"/>
@@ -52561,7 +52851,7 @@
       <c r="J241" s="47" t="n"/>
       <c r="K241" s="47" t="n"/>
       <c r="L241" s="50">
-        <f>IF(G251="","",IF(L250="",G251,L250+G251))</f>
+        <f>IF(G241="","",IF(L240="",G241,L240+G241))</f>
         <v/>
       </c>
       <c r="M241" s="47" t="n"/>
@@ -52581,7 +52871,7 @@
       <c r="J242" s="55" t="n"/>
       <c r="K242" s="55" t="n"/>
       <c r="L242" s="58">
-        <f>IF(G252="","",IF(L251="",G252,L251+G252))</f>
+        <f>IF(G242="","",IF(L241="",G242,L241+G242))</f>
         <v/>
       </c>
       <c r="M242" s="55" t="n"/>
@@ -52601,7 +52891,7 @@
       <c r="J243" s="47" t="n"/>
       <c r="K243" s="47" t="n"/>
       <c r="L243" s="50">
-        <f>IF(G253="","",IF(L252="",G253,L252+G253))</f>
+        <f>IF(G243="","",IF(L242="",G243,L242+G243))</f>
         <v/>
       </c>
       <c r="M243" s="47" t="n"/>
@@ -52621,7 +52911,7 @@
       <c r="J244" s="55" t="n"/>
       <c r="K244" s="55" t="n"/>
       <c r="L244" s="58">
-        <f>IF(G254="","",IF(L253="",G254,L253+G254))</f>
+        <f>IF(G244="","",IF(L243="",G244,L243+G244))</f>
         <v/>
       </c>
       <c r="M244" s="55" t="n"/>
@@ -52641,7 +52931,7 @@
       <c r="J245" s="47" t="n"/>
       <c r="K245" s="47" t="n"/>
       <c r="L245" s="50">
-        <f>IF(G255="","",IF(L254="",G255,L254+G255))</f>
+        <f>IF(G245="","",IF(L244="",G245,L244+G245))</f>
         <v/>
       </c>
       <c r="M245" s="47" t="n"/>
@@ -52661,7 +52951,7 @@
       <c r="J246" s="55" t="n"/>
       <c r="K246" s="55" t="n"/>
       <c r="L246" s="58">
-        <f>IF(G256="","",IF(L255="",G256,L255+G256))</f>
+        <f>IF(G246="","",IF(L245="",G246,L245+G246))</f>
         <v/>
       </c>
       <c r="M246" s="55" t="n"/>
@@ -52681,7 +52971,7 @@
       <c r="J247" s="47" t="n"/>
       <c r="K247" s="47" t="n"/>
       <c r="L247" s="50">
-        <f>IF(G257="","",IF(L256="",G257,L256+G257))</f>
+        <f>IF(G247="","",IF(L246="",G247,L246+G247))</f>
         <v/>
       </c>
       <c r="M247" s="47" t="n"/>
@@ -52701,7 +52991,7 @@
       <c r="J248" s="55" t="n"/>
       <c r="K248" s="55" t="n"/>
       <c r="L248" s="58">
-        <f>IF(G258="","",IF(L257="",G258,L257+G258))</f>
+        <f>IF(G248="","",IF(L247="",G248,L247+G248))</f>
         <v/>
       </c>
       <c r="M248" s="55" t="n"/>
@@ -52721,7 +53011,7 @@
       <c r="J249" s="47" t="n"/>
       <c r="K249" s="47" t="n"/>
       <c r="L249" s="50">
-        <f>IF(G259="","",IF(L258="",G259,L258+G259))</f>
+        <f>IF(G249="","",IF(L248="",G249,L248+G249))</f>
         <v/>
       </c>
       <c r="M249" s="47" t="n"/>
@@ -52741,7 +53031,7 @@
       <c r="J250" s="55" t="n"/>
       <c r="K250" s="55" t="n"/>
       <c r="L250" s="58">
-        <f>IF(G260="","",IF(L259="",G260,L259+G260))</f>
+        <f>IF(G250="","",IF(L249="",G250,L249+G250))</f>
         <v/>
       </c>
       <c r="M250" s="55" t="n"/>
@@ -52761,7 +53051,7 @@
       <c r="J251" s="47" t="n"/>
       <c r="K251" s="47" t="n"/>
       <c r="L251" s="50">
-        <f>IF(G261="","",IF(L260="",G261,L260+G261))</f>
+        <f>IF(G251="","",IF(L250="",G251,L250+G251))</f>
         <v/>
       </c>
       <c r="M251" s="47" t="n"/>
@@ -52781,7 +53071,7 @@
       <c r="J252" s="55" t="n"/>
       <c r="K252" s="55" t="n"/>
       <c r="L252" s="58">
-        <f>IF(G262="","",IF(L261="",G262,L261+G262))</f>
+        <f>IF(G252="","",IF(L251="",G252,L251+G252))</f>
         <v/>
       </c>
       <c r="M252" s="55" t="n"/>
@@ -52801,7 +53091,7 @@
       <c r="J253" s="47" t="n"/>
       <c r="K253" s="47" t="n"/>
       <c r="L253" s="50">
-        <f>IF(G263="","",IF(L262="",G263,L262+G263))</f>
+        <f>IF(G253="","",IF(L252="",G253,L252+G253))</f>
         <v/>
       </c>
       <c r="M253" s="47" t="n"/>
@@ -52821,7 +53111,7 @@
       <c r="J254" s="55" t="n"/>
       <c r="K254" s="55" t="n"/>
       <c r="L254" s="58">
-        <f>IF(G264="","",IF(L263="",G264,L263+G264))</f>
+        <f>IF(G254="","",IF(L253="",G254,L253+G254))</f>
         <v/>
       </c>
       <c r="M254" s="55" t="n"/>
@@ -52841,7 +53131,7 @@
       <c r="J255" s="47" t="n"/>
       <c r="K255" s="47" t="n"/>
       <c r="L255" s="50">
-        <f>IF(G265="","",IF(L264="",G265,L264+G265))</f>
+        <f>IF(G255="","",IF(L254="",G255,L254+G255))</f>
         <v/>
       </c>
       <c r="M255" s="47" t="n"/>
@@ -52861,7 +53151,7 @@
       <c r="J256" s="55" t="n"/>
       <c r="K256" s="55" t="n"/>
       <c r="L256" s="58">
-        <f>IF(G266="","",IF(L265="",G266,L265+G266))</f>
+        <f>IF(G256="","",IF(L255="",G256,L255+G256))</f>
         <v/>
       </c>
       <c r="M256" s="55" t="n"/>
@@ -52881,7 +53171,7 @@
       <c r="J257" s="47" t="n"/>
       <c r="K257" s="47" t="n"/>
       <c r="L257" s="50">
-        <f>IF(G267="","",IF(L266="",G267,L266+G267))</f>
+        <f>IF(G257="","",IF(L256="",G257,L256+G257))</f>
         <v/>
       </c>
       <c r="M257" s="47" t="n"/>
@@ -52901,7 +53191,7 @@
       <c r="J258" s="55" t="n"/>
       <c r="K258" s="55" t="n"/>
       <c r="L258" s="58">
-        <f>IF(G268="","",IF(L267="",G268,L267+G268))</f>
+        <f>IF(G258="","",IF(L257="",G258,L257+G258))</f>
         <v/>
       </c>
       <c r="M258" s="55" t="n"/>
@@ -52921,7 +53211,7 @@
       <c r="J259" s="47" t="n"/>
       <c r="K259" s="47" t="n"/>
       <c r="L259" s="50">
-        <f>IF(G269="","",IF(L268="",G269,L268+G269))</f>
+        <f>IF(G259="","",IF(L258="",G259,L258+G259))</f>
         <v/>
       </c>
       <c r="M259" s="47" t="n"/>
@@ -52941,7 +53231,7 @@
       <c r="J260" s="55" t="n"/>
       <c r="K260" s="55" t="n"/>
       <c r="L260" s="58">
-        <f>IF(G270="","",IF(L269="",G270,L269+G270))</f>
+        <f>IF(G260="","",IF(L259="",G260,L259+G260))</f>
         <v/>
       </c>
       <c r="M260" s="55" t="n"/>
@@ -52961,7 +53251,7 @@
       <c r="J261" s="47" t="n"/>
       <c r="K261" s="47" t="n"/>
       <c r="L261" s="50">
-        <f>IF(G271="","",IF(L270="",G271,L270+G271))</f>
+        <f>IF(G261="","",IF(L260="",G261,L260+G261))</f>
         <v/>
       </c>
       <c r="M261" s="47" t="n"/>
@@ -52981,7 +53271,7 @@
       <c r="J262" s="55" t="n"/>
       <c r="K262" s="55" t="n"/>
       <c r="L262" s="58">
-        <f>IF(G272="","",IF(L271="",G272,L271+G272))</f>
+        <f>IF(G262="","",IF(L261="",G262,L261+G262))</f>
         <v/>
       </c>
       <c r="M262" s="55" t="n"/>
@@ -53001,7 +53291,7 @@
       <c r="J263" s="47" t="n"/>
       <c r="K263" s="47" t="n"/>
       <c r="L263" s="50">
-        <f>IF(G273="","",IF(L272="",G273,L272+G273))</f>
+        <f>IF(G263="","",IF(L262="",G263,L262+G263))</f>
         <v/>
       </c>
       <c r="M263" s="47" t="n"/>
@@ -53021,7 +53311,7 @@
       <c r="J264" s="55" t="n"/>
       <c r="K264" s="55" t="n"/>
       <c r="L264" s="58">
-        <f>IF(G274="","",IF(L273="",G274,L273+G274))</f>
+        <f>IF(G264="","",IF(L263="",G264,L263+G264))</f>
         <v/>
       </c>
       <c r="M264" s="55" t="n"/>
@@ -53041,7 +53331,7 @@
       <c r="J265" s="47" t="n"/>
       <c r="K265" s="47" t="n"/>
       <c r="L265" s="50">
-        <f>IF(G275="","",IF(L274="",G275,L274+G275))</f>
+        <f>IF(G265="","",IF(L264="",G265,L264+G265))</f>
         <v/>
       </c>
       <c r="M265" s="47" t="n"/>
@@ -53061,7 +53351,7 @@
       <c r="J266" s="55" t="n"/>
       <c r="K266" s="55" t="n"/>
       <c r="L266" s="58">
-        <f>IF(G276="","",IF(L275="",G276,L275+G276))</f>
+        <f>IF(G266="","",IF(L265="",G266,L265+G266))</f>
         <v/>
       </c>
       <c r="M266" s="55" t="n"/>
@@ -53081,7 +53371,7 @@
       <c r="J267" s="47" t="n"/>
       <c r="K267" s="47" t="n"/>
       <c r="L267" s="50">
-        <f>IF(G277="","",IF(L276="",G277,L276+G277))</f>
+        <f>IF(G267="","",IF(L266="",G267,L266+G267))</f>
         <v/>
       </c>
       <c r="M267" s="47" t="n"/>
@@ -53101,7 +53391,7 @@
       <c r="J268" s="55" t="n"/>
       <c r="K268" s="55" t="n"/>
       <c r="L268" s="58">
-        <f>IF(G278="","",IF(L277="",G278,L277+G278))</f>
+        <f>IF(G268="","",IF(L267="",G268,L267+G268))</f>
         <v/>
       </c>
       <c r="M268" s="55" t="n"/>
@@ -53121,7 +53411,7 @@
       <c r="J269" s="47" t="n"/>
       <c r="K269" s="47" t="n"/>
       <c r="L269" s="50">
-        <f>IF(G279="","",IF(L278="",G279,L278+G279))</f>
+        <f>IF(G269="","",IF(L268="",G269,L268+G269))</f>
         <v/>
       </c>
       <c r="M269" s="47" t="n"/>
@@ -53141,7 +53431,7 @@
       <c r="J270" s="55" t="n"/>
       <c r="K270" s="55" t="n"/>
       <c r="L270" s="58">
-        <f>IF(G280="","",IF(L279="",G280,L279+G280))</f>
+        <f>IF(G270="","",IF(L269="",G270,L269+G270))</f>
         <v/>
       </c>
       <c r="M270" s="55" t="n"/>
@@ -53161,7 +53451,7 @@
       <c r="J271" s="47" t="n"/>
       <c r="K271" s="47" t="n"/>
       <c r="L271" s="50">
-        <f>IF(G281="","",IF(L280="",G281,L280+G281))</f>
+        <f>IF(G271="","",IF(L270="",G271,L270+G271))</f>
         <v/>
       </c>
       <c r="M271" s="47" t="n"/>
@@ -53181,7 +53471,7 @@
       <c r="J272" s="55" t="n"/>
       <c r="K272" s="55" t="n"/>
       <c r="L272" s="58">
-        <f>IF(G282="","",IF(L281="",G282,L281+G282))</f>
+        <f>IF(G272="","",IF(L271="",G272,L271+G272))</f>
         <v/>
       </c>
       <c r="M272" s="55" t="n"/>
@@ -53201,7 +53491,7 @@
       <c r="J273" s="47" t="n"/>
       <c r="K273" s="47" t="n"/>
       <c r="L273" s="50">
-        <f>IF(G283="","",IF(L282="",G283,L282+G283))</f>
+        <f>IF(G273="","",IF(L272="",G273,L272+G273))</f>
         <v/>
       </c>
       <c r="M273" s="47" t="n"/>
@@ -53221,7 +53511,7 @@
       <c r="J274" s="55" t="n"/>
       <c r="K274" s="55" t="n"/>
       <c r="L274" s="58">
-        <f>IF(G284="","",IF(L283="",G284,L283+G284))</f>
+        <f>IF(G274="","",IF(L273="",G274,L273+G274))</f>
         <v/>
       </c>
       <c r="M274" s="55" t="n"/>
@@ -53241,7 +53531,7 @@
       <c r="J275" s="47" t="n"/>
       <c r="K275" s="47" t="n"/>
       <c r="L275" s="50">
-        <f>IF(G285="","",IF(L284="",G285,L284+G285))</f>
+        <f>IF(G275="","",IF(L274="",G275,L274+G275))</f>
         <v/>
       </c>
       <c r="M275" s="47" t="n"/>
@@ -53261,7 +53551,7 @@
       <c r="J276" s="55" t="n"/>
       <c r="K276" s="55" t="n"/>
       <c r="L276" s="58">
-        <f>IF(G286="","",IF(L285="",G286,L285+G286))</f>
+        <f>IF(G276="","",IF(L275="",G276,L275+G276))</f>
         <v/>
       </c>
       <c r="M276" s="55" t="n"/>
@@ -53281,7 +53571,7 @@
       <c r="J277" s="47" t="n"/>
       <c r="K277" s="47" t="n"/>
       <c r="L277" s="50">
-        <f>IF(G287="","",IF(L286="",G287,L286+G287))</f>
+        <f>IF(G277="","",IF(L276="",G277,L276+G277))</f>
         <v/>
       </c>
       <c r="M277" s="47" t="n"/>
@@ -53301,7 +53591,7 @@
       <c r="J278" s="55" t="n"/>
       <c r="K278" s="55" t="n"/>
       <c r="L278" s="58">
-        <f>IF(G288="","",IF(L287="",G288,L287+G288))</f>
+        <f>IF(G278="","",IF(L277="",G278,L277+G278))</f>
         <v/>
       </c>
       <c r="M278" s="55" t="n"/>
@@ -53321,7 +53611,7 @@
       <c r="J279" s="47" t="n"/>
       <c r="K279" s="47" t="n"/>
       <c r="L279" s="50">
-        <f>IF(G289="","",IF(L288="",G289,L288+G289))</f>
+        <f>IF(G279="","",IF(L278="",G279,L278+G279))</f>
         <v/>
       </c>
       <c r="M279" s="47" t="n"/>
@@ -53341,7 +53631,7 @@
       <c r="J280" s="55" t="n"/>
       <c r="K280" s="55" t="n"/>
       <c r="L280" s="58">
-        <f>IF(G290="","",IF(L289="",G290,L289+G290))</f>
+        <f>IF(G280="","",IF(L279="",G280,L279+G280))</f>
         <v/>
       </c>
       <c r="M280" s="55" t="n"/>
@@ -53361,7 +53651,7 @@
       <c r="J281" s="47" t="n"/>
       <c r="K281" s="47" t="n"/>
       <c r="L281" s="50">
-        <f>IF(G291="","",IF(L290="",G291,L290+G291))</f>
+        <f>IF(G281="","",IF(L280="",G281,L280+G281))</f>
         <v/>
       </c>
       <c r="M281" s="47" t="n"/>
@@ -53381,7 +53671,7 @@
       <c r="J282" s="55" t="n"/>
       <c r="K282" s="55" t="n"/>
       <c r="L282" s="58">
-        <f>IF(G292="","",IF(L291="",G292,L291+G292))</f>
+        <f>IF(G282="","",IF(L281="",G282,L281+G282))</f>
         <v/>
       </c>
       <c r="M282" s="55" t="n"/>
@@ -53401,7 +53691,7 @@
       <c r="J283" s="47" t="n"/>
       <c r="K283" s="47" t="n"/>
       <c r="L283" s="50">
-        <f>IF(G293="","",IF(L292="",G293,L292+G293))</f>
+        <f>IF(G283="","",IF(L282="",G283,L282+G283))</f>
         <v/>
       </c>
       <c r="M283" s="47" t="n"/>
@@ -53421,7 +53711,7 @@
       <c r="J284" s="55" t="n"/>
       <c r="K284" s="55" t="n"/>
       <c r="L284" s="58">
-        <f>IF(G294="","",IF(L293="",G294,L293+G294))</f>
+        <f>IF(G284="","",IF(L283="",G284,L283+G284))</f>
         <v/>
       </c>
       <c r="M284" s="55" t="n"/>
@@ -53441,7 +53731,7 @@
       <c r="J285" s="47" t="n"/>
       <c r="K285" s="47" t="n"/>
       <c r="L285" s="50">
-        <f>IF(G295="","",IF(L294="",G295,L294+G295))</f>
+        <f>IF(G285="","",IF(L284="",G285,L284+G285))</f>
         <v/>
       </c>
       <c r="M285" s="47" t="n"/>
@@ -53461,7 +53751,7 @@
       <c r="J286" s="55" t="n"/>
       <c r="K286" s="55" t="n"/>
       <c r="L286" s="58">
-        <f>IF(G296="","",IF(L295="",G296,L295+G296))</f>
+        <f>IF(G286="","",IF(L285="",G286,L285+G286))</f>
         <v/>
       </c>
       <c r="M286" s="55" t="n"/>
@@ -53481,7 +53771,7 @@
       <c r="J287" s="47" t="n"/>
       <c r="K287" s="47" t="n"/>
       <c r="L287" s="50">
-        <f>IF(G297="","",IF(L296="",G297,L296+G297))</f>
+        <f>IF(G287="","",IF(L286="",G287,L286+G287))</f>
         <v/>
       </c>
       <c r="M287" s="47" t="n"/>
@@ -53501,7 +53791,7 @@
       <c r="J288" s="55" t="n"/>
       <c r="K288" s="55" t="n"/>
       <c r="L288" s="58">
-        <f>IF(G298="","",IF(L297="",G298,L297+G298))</f>
+        <f>IF(G288="","",IF(L287="",G288,L287+G288))</f>
         <v/>
       </c>
       <c r="M288" s="55" t="n"/>
@@ -53521,7 +53811,7 @@
       <c r="J289" s="47" t="n"/>
       <c r="K289" s="47" t="n"/>
       <c r="L289" s="50">
-        <f>IF(G299="","",IF(L298="",G299,L298+G299))</f>
+        <f>IF(G289="","",IF(L288="",G289,L288+G289))</f>
         <v/>
       </c>
       <c r="M289" s="47" t="n"/>
@@ -53541,7 +53831,7 @@
       <c r="J290" s="55" t="n"/>
       <c r="K290" s="55" t="n"/>
       <c r="L290" s="58">
-        <f>IF(G300="","",IF(L299="",G300,L299+G300))</f>
+        <f>IF(G290="","",IF(L289="",G290,L289+G290))</f>
         <v/>
       </c>
       <c r="M290" s="55" t="n"/>
@@ -53561,7 +53851,7 @@
       <c r="J291" s="47" t="n"/>
       <c r="K291" s="47" t="n"/>
       <c r="L291" s="50">
-        <f>IF(G301="","",IF(L300="",G301,L300+G301))</f>
+        <f>IF(G291="","",IF(L290="",G291,L290+G291))</f>
         <v/>
       </c>
       <c r="M291" s="47" t="n"/>
@@ -53581,7 +53871,7 @@
       <c r="J292" s="55" t="n"/>
       <c r="K292" s="55" t="n"/>
       <c r="L292" s="58">
-        <f>IF(G302="","",IF(L301="",G302,L301+G302))</f>
+        <f>IF(G292="","",IF(L291="",G292,L291+G292))</f>
         <v/>
       </c>
       <c r="M292" s="55" t="n"/>
@@ -53601,7 +53891,7 @@
       <c r="J293" s="47" t="n"/>
       <c r="K293" s="47" t="n"/>
       <c r="L293" s="50">
-        <f>IF(G303="","",IF(L302="",G303,L302+G303))</f>
+        <f>IF(G293="","",IF(L292="",G293,L292+G293))</f>
         <v/>
       </c>
       <c r="M293" s="47" t="n"/>
@@ -53621,7 +53911,7 @@
       <c r="J294" s="55" t="n"/>
       <c r="K294" s="55" t="n"/>
       <c r="L294" s="58">
-        <f>IF(G304="","",IF(L303="",G304,L303+G304))</f>
+        <f>IF(G294="","",IF(L293="",G294,L293+G294))</f>
         <v/>
       </c>
       <c r="M294" s="55" t="n"/>
@@ -53641,7 +53931,7 @@
       <c r="J295" s="47" t="n"/>
       <c r="K295" s="47" t="n"/>
       <c r="L295" s="50">
-        <f>IF(G305="","",IF(L304="",G305,L304+G305))</f>
+        <f>IF(G295="","",IF(L294="",G295,L294+G295))</f>
         <v/>
       </c>
       <c r="M295" s="47" t="n"/>
@@ -53661,7 +53951,7 @@
       <c r="J296" s="55" t="n"/>
       <c r="K296" s="55" t="n"/>
       <c r="L296" s="58">
-        <f>IF(G306="","",IF(L305="",G306,L305+G306))</f>
+        <f>IF(G296="","",IF(L295="",G296,L295+G296))</f>
         <v/>
       </c>
       <c r="M296" s="55" t="n"/>
@@ -53681,7 +53971,7 @@
       <c r="J297" s="47" t="n"/>
       <c r="K297" s="47" t="n"/>
       <c r="L297" s="50">
-        <f>IF(G307="","",IF(L306="",G307,L306+G307))</f>
+        <f>IF(G297="","",IF(L296="",G297,L296+G297))</f>
         <v/>
       </c>
       <c r="M297" s="47" t="n"/>
@@ -53701,7 +53991,7 @@
       <c r="J298" s="55" t="n"/>
       <c r="K298" s="55" t="n"/>
       <c r="L298" s="58">
-        <f>IF(G308="","",IF(L307="",G308,L307+G308))</f>
+        <f>IF(G298="","",IF(L297="",G298,L297+G298))</f>
         <v/>
       </c>
       <c r="M298" s="55" t="n"/>
@@ -53721,7 +54011,7 @@
       <c r="J299" s="47" t="n"/>
       <c r="K299" s="47" t="n"/>
       <c r="L299" s="50">
-        <f>IF(G309="","",IF(L308="",G309,L308+G309))</f>
+        <f>IF(G299="","",IF(L298="",G299,L298+G299))</f>
         <v/>
       </c>
       <c r="M299" s="47" t="n"/>
@@ -53741,7 +54031,7 @@
       <c r="J300" s="55" t="n"/>
       <c r="K300" s="55" t="n"/>
       <c r="L300" s="58">
-        <f>IF(G310="","",IF(L309="",G310,L309+G310))</f>
+        <f>IF(G300="","",IF(L299="",G300,L299+G300))</f>
         <v/>
       </c>
       <c r="M300" s="55" t="n"/>
@@ -53761,7 +54051,7 @@
       <c r="J301" s="47" t="n"/>
       <c r="K301" s="47" t="n"/>
       <c r="L301" s="50">
-        <f>IF(G311="","",IF(L310="",G311,L310+G311))</f>
+        <f>IF(G301="","",IF(L300="",G301,L300+G301))</f>
         <v/>
       </c>
       <c r="M301" s="47" t="n"/>
@@ -53781,7 +54071,7 @@
       <c r="J302" s="55" t="n"/>
       <c r="K302" s="55" t="n"/>
       <c r="L302" s="58">
-        <f>IF(G312="","",IF(L311="",G312,L311+G312))</f>
+        <f>IF(G302="","",IF(L301="",G302,L301+G302))</f>
         <v/>
       </c>
       <c r="M302" s="55" t="n"/>
@@ -53801,7 +54091,7 @@
       <c r="J303" s="47" t="n"/>
       <c r="K303" s="47" t="n"/>
       <c r="L303" s="50">
-        <f>IF(G313="","",IF(L312="",G313,L312+G313))</f>
+        <f>IF(G303="","",IF(L302="",G303,L302+G303))</f>
         <v/>
       </c>
       <c r="M303" s="47" t="n"/>
@@ -53821,7 +54111,7 @@
       <c r="J304" s="55" t="n"/>
       <c r="K304" s="55" t="n"/>
       <c r="L304" s="58">
-        <f>IF(G314="","",IF(L313="",G314,L313+G314))</f>
+        <f>IF(G304="","",IF(L303="",G304,L303+G304))</f>
         <v/>
       </c>
       <c r="M304" s="55" t="n"/>
@@ -53841,7 +54131,7 @@
       <c r="J305" s="47" t="n"/>
       <c r="K305" s="47" t="n"/>
       <c r="L305" s="50">
-        <f>IF(G315="","",IF(L314="",G315,L314+G315))</f>
+        <f>IF(G305="","",IF(L304="",G305,L304+G305))</f>
         <v/>
       </c>
       <c r="M305" s="47" t="n"/>
@@ -53861,7 +54151,7 @@
       <c r="J306" s="55" t="n"/>
       <c r="K306" s="55" t="n"/>
       <c r="L306" s="58">
-        <f>IF(G316="","",IF(L315="",G316,L315+G316))</f>
+        <f>IF(G306="","",IF(L305="",G306,L305+G306))</f>
         <v/>
       </c>
       <c r="M306" s="55" t="n"/>
@@ -53881,7 +54171,7 @@
       <c r="J307" s="47" t="n"/>
       <c r="K307" s="47" t="n"/>
       <c r="L307" s="50">
-        <f>IF(G317="","",IF(L316="",G317,L316+G317))</f>
+        <f>IF(G307="","",IF(L306="",G307,L306+G307))</f>
         <v/>
       </c>
       <c r="M307" s="47" t="n"/>
@@ -53901,7 +54191,7 @@
       <c r="J308" s="55" t="n"/>
       <c r="K308" s="55" t="n"/>
       <c r="L308" s="58">
-        <f>IF(G318="","",IF(L317="",G318,L317+G318))</f>
+        <f>IF(G308="","",IF(L307="",G308,L307+G308))</f>
         <v/>
       </c>
       <c r="M308" s="55" t="n"/>
@@ -53921,7 +54211,7 @@
       <c r="J309" s="47" t="n"/>
       <c r="K309" s="47" t="n"/>
       <c r="L309" s="50">
-        <f>IF(G319="","",IF(L318="",G319,L318+G319))</f>
+        <f>IF(G309="","",IF(L308="",G309,L308+G309))</f>
         <v/>
       </c>
       <c r="M309" s="47" t="n"/>
@@ -53941,7 +54231,7 @@
       <c r="J310" s="55" t="n"/>
       <c r="K310" s="55" t="n"/>
       <c r="L310" s="58">
-        <f>IF(G320="","",IF(L319="",G320,L319+G320))</f>
+        <f>IF(G310="","",IF(L309="",G310,L309+G310))</f>
         <v/>
       </c>
       <c r="M310" s="55" t="n"/>
@@ -53961,7 +54251,7 @@
       <c r="J311" s="47" t="n"/>
       <c r="K311" s="47" t="n"/>
       <c r="L311" s="50">
-        <f>IF(G321="","",IF(L320="",G321,L320+G321))</f>
+        <f>IF(G311="","",IF(L310="",G311,L310+G311))</f>
         <v/>
       </c>
       <c r="M311" s="47" t="n"/>
@@ -53981,7 +54271,7 @@
       <c r="J312" s="55" t="n"/>
       <c r="K312" s="55" t="n"/>
       <c r="L312" s="58">
-        <f>IF(G322="","",IF(L321="",G322,L321+G322))</f>
+        <f>IF(G312="","",IF(L311="",G312,L311+G312))</f>
         <v/>
       </c>
       <c r="M312" s="55" t="n"/>
@@ -54001,7 +54291,7 @@
       <c r="J313" s="47" t="n"/>
       <c r="K313" s="47" t="n"/>
       <c r="L313" s="50">
-        <f>IF(G323="","",IF(L322="",G323,L322+G323))</f>
+        <f>IF(G313="","",IF(L312="",G313,L312+G313))</f>
         <v/>
       </c>
       <c r="M313" s="47" t="n"/>
@@ -54021,7 +54311,7 @@
       <c r="J314" s="55" t="n"/>
       <c r="K314" s="55" t="n"/>
       <c r="L314" s="58">
-        <f>IF(G324="","",IF(L323="",G324,L323+G324))</f>
+        <f>IF(G314="","",IF(L313="",G314,L313+G314))</f>
         <v/>
       </c>
       <c r="M314" s="55" t="n"/>
@@ -54041,7 +54331,7 @@
       <c r="J315" s="47" t="n"/>
       <c r="K315" s="47" t="n"/>
       <c r="L315" s="50">
-        <f>IF(G325="","",IF(L324="",G325,L324+G325))</f>
+        <f>IF(G315="","",IF(L314="",G315,L314+G315))</f>
         <v/>
       </c>
       <c r="M315" s="47" t="n"/>
@@ -54061,7 +54351,7 @@
       <c r="J316" s="55" t="n"/>
       <c r="K316" s="55" t="n"/>
       <c r="L316" s="58">
-        <f>IF(G326="","",IF(L325="",G326,L325+G326))</f>
+        <f>IF(G316="","",IF(L315="",G316,L315+G316))</f>
         <v/>
       </c>
       <c r="M316" s="55" t="n"/>
@@ -54081,7 +54371,7 @@
       <c r="J317" s="47" t="n"/>
       <c r="K317" s="47" t="n"/>
       <c r="L317" s="50">
-        <f>IF(G327="","",IF(L326="",G327,L326+G327))</f>
+        <f>IF(G317="","",IF(L316="",G317,L316+G317))</f>
         <v/>
       </c>
       <c r="M317" s="47" t="n"/>
@@ -54101,7 +54391,7 @@
       <c r="J318" s="55" t="n"/>
       <c r="K318" s="55" t="n"/>
       <c r="L318" s="58">
-        <f>IF(G328="","",IF(L327="",G328,L327+G328))</f>
+        <f>IF(G318="","",IF(L317="",G318,L317+G318))</f>
         <v/>
       </c>
       <c r="M318" s="55" t="n"/>
@@ -54121,7 +54411,7 @@
       <c r="J319" s="47" t="n"/>
       <c r="K319" s="47" t="n"/>
       <c r="L319" s="50">
-        <f>IF(G329="","",IF(L328="",G329,L328+G329))</f>
+        <f>IF(G319="","",IF(L318="",G319,L318+G319))</f>
         <v/>
       </c>
       <c r="M319" s="47" t="n"/>
@@ -54141,7 +54431,7 @@
       <c r="J320" s="55" t="n"/>
       <c r="K320" s="55" t="n"/>
       <c r="L320" s="58">
-        <f>IF(G330="","",IF(L329="",G330,L329+G330))</f>
+        <f>IF(G320="","",IF(L319="",G320,L319+G320))</f>
         <v/>
       </c>
       <c r="M320" s="55" t="n"/>
@@ -54161,7 +54451,7 @@
       <c r="J321" s="47" t="n"/>
       <c r="K321" s="47" t="n"/>
       <c r="L321" s="50">
-        <f>IF(G331="","",IF(L330="",G331,L330+G331))</f>
+        <f>IF(G321="","",IF(L320="",G321,L320+G321))</f>
         <v/>
       </c>
       <c r="M321" s="47" t="n"/>
@@ -54181,7 +54471,7 @@
       <c r="J322" s="55" t="n"/>
       <c r="K322" s="55" t="n"/>
       <c r="L322" s="58">
-        <f>IF(G332="","",IF(L331="",G332,L331+G332))</f>
+        <f>IF(G322="","",IF(L321="",G322,L321+G322))</f>
         <v/>
       </c>
       <c r="M322" s="55" t="n"/>
@@ -54201,7 +54491,7 @@
       <c r="J323" s="47" t="n"/>
       <c r="K323" s="47" t="n"/>
       <c r="L323" s="50">
-        <f>IF(G333="","",IF(L332="",G333,L332+G333))</f>
+        <f>IF(G323="","",IF(L322="",G323,L322+G323))</f>
         <v/>
       </c>
       <c r="M323" s="47" t="n"/>
@@ -54221,7 +54511,7 @@
       <c r="J324" s="55" t="n"/>
       <c r="K324" s="55" t="n"/>
       <c r="L324" s="58">
-        <f>IF(G334="","",IF(L333="",G334,L333+G334))</f>
+        <f>IF(G324="","",IF(L323="",G324,L323+G324))</f>
         <v/>
       </c>
       <c r="M324" s="55" t="n"/>
@@ -54241,7 +54531,7 @@
       <c r="J325" s="47" t="n"/>
       <c r="K325" s="47" t="n"/>
       <c r="L325" s="50">
-        <f>IF(G335="","",IF(L334="",G335,L334+G335))</f>
+        <f>IF(G325="","",IF(L324="",G325,L324+G325))</f>
         <v/>
       </c>
       <c r="M325" s="47" t="n"/>
@@ -54261,7 +54551,7 @@
       <c r="J326" s="55" t="n"/>
       <c r="K326" s="55" t="n"/>
       <c r="L326" s="58">
-        <f>IF(G336="","",IF(L335="",G336,L335+G336))</f>
+        <f>IF(G326="","",IF(L325="",G326,L325+G326))</f>
         <v/>
       </c>
       <c r="M326" s="55" t="n"/>
@@ -54281,7 +54571,7 @@
       <c r="J327" s="47" t="n"/>
       <c r="K327" s="47" t="n"/>
       <c r="L327" s="50">
-        <f>IF(G337="","",IF(L336="",G337,L336+G337))</f>
+        <f>IF(G327="","",IF(L326="",G327,L326+G327))</f>
         <v/>
       </c>
       <c r="M327" s="47" t="n"/>
@@ -54301,7 +54591,7 @@
       <c r="J328" s="55" t="n"/>
       <c r="K328" s="55" t="n"/>
       <c r="L328" s="58">
-        <f>IF(G338="","",IF(L337="",G338,L337+G338))</f>
+        <f>IF(G328="","",IF(L327="",G328,L327+G328))</f>
         <v/>
       </c>
       <c r="M328" s="55" t="n"/>
@@ -54321,7 +54611,7 @@
       <c r="J329" s="47" t="n"/>
       <c r="K329" s="47" t="n"/>
       <c r="L329" s="50">
-        <f>IF(G339="","",IF(L338="",G339,L338+G339))</f>
+        <f>IF(G329="","",IF(L328="",G329,L328+G329))</f>
         <v/>
       </c>
       <c r="M329" s="47" t="n"/>
@@ -54341,7 +54631,7 @@
       <c r="J330" s="55" t="n"/>
       <c r="K330" s="55" t="n"/>
       <c r="L330" s="58">
-        <f>IF(G340="","",IF(L339="",G340,L339+G340))</f>
+        <f>IF(G330="","",IF(L329="",G330,L329+G330))</f>
         <v/>
       </c>
       <c r="M330" s="55" t="n"/>
@@ -54361,7 +54651,7 @@
       <c r="J331" s="47" t="n"/>
       <c r="K331" s="47" t="n"/>
       <c r="L331" s="50">
-        <f>IF(G341="","",IF(L340="",G341,L340+G341))</f>
+        <f>IF(G331="","",IF(L330="",G331,L330+G331))</f>
         <v/>
       </c>
       <c r="M331" s="47" t="n"/>
@@ -54381,7 +54671,7 @@
       <c r="J332" s="55" t="n"/>
       <c r="K332" s="55" t="n"/>
       <c r="L332" s="58">
-        <f>IF(G342="","",IF(L341="",G342,L341+G342))</f>
+        <f>IF(G332="","",IF(L331="",G332,L331+G332))</f>
         <v/>
       </c>
       <c r="M332" s="55" t="n"/>
@@ -54401,7 +54691,7 @@
       <c r="J333" s="47" t="n"/>
       <c r="K333" s="47" t="n"/>
       <c r="L333" s="50">
-        <f>IF(G343="","",IF(L342="",G343,L342+G343))</f>
+        <f>IF(G333="","",IF(L332="",G333,L332+G333))</f>
         <v/>
       </c>
       <c r="M333" s="47" t="n"/>
@@ -54421,7 +54711,7 @@
       <c r="J334" s="55" t="n"/>
       <c r="K334" s="55" t="n"/>
       <c r="L334" s="58">
-        <f>IF(G344="","",IF(L343="",G344,L343+G344))</f>
+        <f>IF(G334="","",IF(L333="",G334,L333+G334))</f>
         <v/>
       </c>
       <c r="M334" s="55" t="n"/>
@@ -54441,7 +54731,7 @@
       <c r="J335" s="47" t="n"/>
       <c r="K335" s="47" t="n"/>
       <c r="L335" s="50">
-        <f>IF(G345="","",IF(L344="",G345,L344+G345))</f>
+        <f>IF(G335="","",IF(L334="",G335,L334+G335))</f>
         <v/>
       </c>
       <c r="M335" s="47" t="n"/>
@@ -54461,7 +54751,7 @@
       <c r="J336" s="55" t="n"/>
       <c r="K336" s="55" t="n"/>
       <c r="L336" s="58">
-        <f>IF(G346="","",IF(L345="",G346,L345+G346))</f>
+        <f>IF(G336="","",IF(L335="",G336,L335+G336))</f>
         <v/>
       </c>
       <c r="M336" s="55" t="n"/>
@@ -54481,7 +54771,7 @@
       <c r="J337" s="47" t="n"/>
       <c r="K337" s="47" t="n"/>
       <c r="L337" s="50">
-        <f>IF(G347="","",IF(L346="",G347,L346+G347))</f>
+        <f>IF(G337="","",IF(L336="",G337,L336+G337))</f>
         <v/>
       </c>
       <c r="M337" s="47" t="n"/>
@@ -54501,7 +54791,7 @@
       <c r="J338" s="55" t="n"/>
       <c r="K338" s="55" t="n"/>
       <c r="L338" s="58">
-        <f>IF(G348="","",IF(L347="",G348,L347+G348))</f>
+        <f>IF(G338="","",IF(L337="",G338,L337+G338))</f>
         <v/>
       </c>
       <c r="M338" s="55" t="n"/>
@@ -54521,7 +54811,7 @@
       <c r="J339" s="47" t="n"/>
       <c r="K339" s="47" t="n"/>
       <c r="L339" s="50">
-        <f>IF(G349="","",IF(L348="",G349,L348+G349))</f>
+        <f>IF(G339="","",IF(L338="",G339,L338+G339))</f>
         <v/>
       </c>
       <c r="M339" s="47" t="n"/>
@@ -54541,7 +54831,7 @@
       <c r="J340" s="55" t="n"/>
       <c r="K340" s="55" t="n"/>
       <c r="L340" s="58">
-        <f>IF(G350="","",IF(L349="",G350,L349+G350))</f>
+        <f>IF(G340="","",IF(L339="",G340,L339+G340))</f>
         <v/>
       </c>
       <c r="M340" s="55" t="n"/>
@@ -54561,7 +54851,7 @@
       <c r="J341" s="47" t="n"/>
       <c r="K341" s="47" t="n"/>
       <c r="L341" s="50">
-        <f>IF(G351="","",IF(L350="",G351,L350+G351))</f>
+        <f>IF(G341="","",IF(L340="",G341,L340+G341))</f>
         <v/>
       </c>
       <c r="M341" s="47" t="n"/>
@@ -54581,7 +54871,7 @@
       <c r="J342" s="55" t="n"/>
       <c r="K342" s="55" t="n"/>
       <c r="L342" s="58">
-        <f>IF(G352="","",IF(L351="",G352,L351+G352))</f>
+        <f>IF(G342="","",IF(L341="",G342,L341+G342))</f>
         <v/>
       </c>
       <c r="M342" s="55" t="n"/>
@@ -54601,7 +54891,7 @@
       <c r="J343" s="47" t="n"/>
       <c r="K343" s="47" t="n"/>
       <c r="L343" s="50">
-        <f>IF(G353="","",IF(L352="",G353,L352+G353))</f>
+        <f>IF(G343="","",IF(L342="",G343,L342+G343))</f>
         <v/>
       </c>
       <c r="M343" s="47" t="n"/>
@@ -54621,7 +54911,7 @@
       <c r="J344" s="55" t="n"/>
       <c r="K344" s="55" t="n"/>
       <c r="L344" s="58">
-        <f>IF(G354="","",IF(L353="",G354,L353+G354))</f>
+        <f>IF(G344="","",IF(L343="",G344,L343+G344))</f>
         <v/>
       </c>
       <c r="M344" s="55" t="n"/>
@@ -54641,7 +54931,7 @@
       <c r="J345" s="47" t="n"/>
       <c r="K345" s="47" t="n"/>
       <c r="L345" s="50">
-        <f>IF(G355="","",IF(L354="",G355,L354+G355))</f>
+        <f>IF(G345="","",IF(L344="",G345,L344+G345))</f>
         <v/>
       </c>
       <c r="M345" s="47" t="n"/>
@@ -54661,7 +54951,7 @@
       <c r="J346" s="55" t="n"/>
       <c r="K346" s="55" t="n"/>
       <c r="L346" s="58">
-        <f>IF(G356="","",IF(L355="",G356,L355+G356))</f>
+        <f>IF(G346="","",IF(L345="",G346,L345+G346))</f>
         <v/>
       </c>
       <c r="M346" s="55" t="n"/>
@@ -54681,7 +54971,7 @@
       <c r="J347" s="47" t="n"/>
       <c r="K347" s="47" t="n"/>
       <c r="L347" s="50">
-        <f>IF(G357="","",IF(L356="",G357,L356+G357))</f>
+        <f>IF(G347="","",IF(L346="",G347,L346+G347))</f>
         <v/>
       </c>
       <c r="M347" s="47" t="n"/>
@@ -54701,7 +54991,7 @@
       <c r="J348" s="55" t="n"/>
       <c r="K348" s="55" t="n"/>
       <c r="L348" s="58">
-        <f>IF(G358="","",IF(L357="",G358,L357+G358))</f>
+        <f>IF(G348="","",IF(L347="",G348,L347+G348))</f>
         <v/>
       </c>
       <c r="M348" s="55" t="n"/>
@@ -54721,7 +55011,7 @@
       <c r="J349" s="47" t="n"/>
       <c r="K349" s="47" t="n"/>
       <c r="L349" s="50">
-        <f>IF(G359="","",IF(L358="",G359,L358+G359))</f>
+        <f>IF(G349="","",IF(L348="",G349,L348+G349))</f>
         <v/>
       </c>
       <c r="M349" s="47" t="n"/>
@@ -54741,7 +55031,7 @@
       <c r="J350" s="55" t="n"/>
       <c r="K350" s="55" t="n"/>
       <c r="L350" s="58">
-        <f>IF(G360="","",IF(L359="",G360,L359+G360))</f>
+        <f>IF(G350="","",IF(L349="",G350,L349+G350))</f>
         <v/>
       </c>
       <c r="M350" s="55" t="n"/>
@@ -54761,7 +55051,7 @@
       <c r="J351" s="47" t="n"/>
       <c r="K351" s="47" t="n"/>
       <c r="L351" s="50">
-        <f>IF(G361="","",IF(L360="",G361,L360+G361))</f>
+        <f>IF(G351="","",IF(L350="",G351,L350+G351))</f>
         <v/>
       </c>
       <c r="M351" s="47" t="n"/>
@@ -54781,7 +55071,7 @@
       <c r="J352" s="55" t="n"/>
       <c r="K352" s="55" t="n"/>
       <c r="L352" s="58">
-        <f>IF(G362="","",IF(L361="",G362,L361+G362))</f>
+        <f>IF(G352="","",IF(L351="",G352,L351+G352))</f>
         <v/>
       </c>
       <c r="M352" s="55" t="n"/>
@@ -54801,7 +55091,7 @@
       <c r="J353" s="47" t="n"/>
       <c r="K353" s="47" t="n"/>
       <c r="L353" s="50">
-        <f>IF(G363="","",IF(L362="",G363,L362+G363))</f>
+        <f>IF(G353="","",IF(L352="",G353,L352+G353))</f>
         <v/>
       </c>
       <c r="M353" s="47" t="n"/>
@@ -54821,7 +55111,7 @@
       <c r="J354" s="55" t="n"/>
       <c r="K354" s="55" t="n"/>
       <c r="L354" s="58">
-        <f>IF(G364="","",IF(L363="",G364,L363+G364))</f>
+        <f>IF(G354="","",IF(L353="",G354,L353+G354))</f>
         <v/>
       </c>
       <c r="M354" s="55" t="n"/>
@@ -54841,7 +55131,7 @@
       <c r="J355" s="47" t="n"/>
       <c r="K355" s="47" t="n"/>
       <c r="L355" s="50">
-        <f>IF(G365="","",IF(L364="",G365,L364+G365))</f>
+        <f>IF(G355="","",IF(L354="",G355,L354+G355))</f>
         <v/>
       </c>
       <c r="M355" s="47" t="n"/>
@@ -54861,7 +55151,7 @@
       <c r="J356" s="55" t="n"/>
       <c r="K356" s="55" t="n"/>
       <c r="L356" s="58">
-        <f>IF(G366="","",IF(L365="",G366,L365+G366))</f>
+        <f>IF(G356="","",IF(L355="",G356,L355+G356))</f>
         <v/>
       </c>
       <c r="M356" s="55" t="n"/>
@@ -54881,7 +55171,7 @@
       <c r="J357" s="47" t="n"/>
       <c r="K357" s="47" t="n"/>
       <c r="L357" s="50">
-        <f>IF(G367="","",IF(L366="",G367,L366+G367))</f>
+        <f>IF(G357="","",IF(L356="",G357,L356+G357))</f>
         <v/>
       </c>
       <c r="M357" s="47" t="n"/>
@@ -54901,7 +55191,7 @@
       <c r="J358" s="55" t="n"/>
       <c r="K358" s="55" t="n"/>
       <c r="L358" s="58">
-        <f>IF(G368="","",IF(L367="",G368,L367+G368))</f>
+        <f>IF(G358="","",IF(L357="",G358,L357+G358))</f>
         <v/>
       </c>
       <c r="M358" s="55" t="n"/>
@@ -54921,7 +55211,7 @@
       <c r="J359" s="47" t="n"/>
       <c r="K359" s="47" t="n"/>
       <c r="L359" s="50">
-        <f>IF(G369="","",IF(L368="",G369,L368+G369))</f>
+        <f>IF(G359="","",IF(L358="",G359,L358+G359))</f>
         <v/>
       </c>
       <c r="M359" s="47" t="n"/>
@@ -54941,7 +55231,7 @@
       <c r="J360" s="55" t="n"/>
       <c r="K360" s="55" t="n"/>
       <c r="L360" s="58">
-        <f>IF(G370="","",IF(L369="",G370,L369+G370))</f>
+        <f>IF(G360="","",IF(L359="",G360,L359+G360))</f>
         <v/>
       </c>
       <c r="M360" s="55" t="n"/>
@@ -54961,7 +55251,7 @@
       <c r="J361" s="47" t="n"/>
       <c r="K361" s="47" t="n"/>
       <c r="L361" s="50">
-        <f>IF(G371="","",IF(L370="",G371,L370+G371))</f>
+        <f>IF(G361="","",IF(L360="",G361,L360+G361))</f>
         <v/>
       </c>
       <c r="M361" s="47" t="n"/>
@@ -54981,7 +55271,7 @@
       <c r="J362" s="55" t="n"/>
       <c r="K362" s="55" t="n"/>
       <c r="L362" s="58">
-        <f>IF(G372="","",IF(L371="",G372,L371+G372))</f>
+        <f>IF(G362="","",IF(L361="",G362,L361+G362))</f>
         <v/>
       </c>
       <c r="M362" s="55" t="n"/>
@@ -55001,7 +55291,7 @@
       <c r="J363" s="47" t="n"/>
       <c r="K363" s="47" t="n"/>
       <c r="L363" s="50">
-        <f>IF(G373="","",IF(L372="",G373,L372+G373))</f>
+        <f>IF(G363="","",IF(L362="",G363,L362+G363))</f>
         <v/>
       </c>
       <c r="M363" s="47" t="n"/>
@@ -55021,7 +55311,7 @@
       <c r="J364" s="55" t="n"/>
       <c r="K364" s="55" t="n"/>
       <c r="L364" s="58">
-        <f>IF(G374="","",IF(L373="",G374,L373+G374))</f>
+        <f>IF(G364="","",IF(L363="",G364,L363+G364))</f>
         <v/>
       </c>
       <c r="M364" s="55" t="n"/>
@@ -55041,7 +55331,7 @@
       <c r="J365" s="47" t="n"/>
       <c r="K365" s="47" t="n"/>
       <c r="L365" s="50">
-        <f>IF(G375="","",IF(L374="",G375,L374+G375))</f>
+        <f>IF(G365="","",IF(L364="",G365,L364+G365))</f>
         <v/>
       </c>
       <c r="M365" s="47" t="n"/>
@@ -55061,7 +55351,7 @@
       <c r="J366" s="55" t="n"/>
       <c r="K366" s="55" t="n"/>
       <c r="L366" s="58">
-        <f>IF(G376="","",IF(L375="",G376,L375+G376))</f>
+        <f>IF(G366="","",IF(L365="",G366,L365+G366))</f>
         <v/>
       </c>
       <c r="M366" s="55" t="n"/>
@@ -55081,7 +55371,7 @@
       <c r="J367" s="47" t="n"/>
       <c r="K367" s="47" t="n"/>
       <c r="L367" s="50">
-        <f>IF(G377="","",IF(L376="",G377,L376+G377))</f>
+        <f>IF(G367="","",IF(L366="",G367,L366+G367))</f>
         <v/>
       </c>
       <c r="M367" s="47" t="n"/>
@@ -55101,7 +55391,7 @@
       <c r="J368" s="55" t="n"/>
       <c r="K368" s="55" t="n"/>
       <c r="L368" s="58">
-        <f>IF(G378="","",IF(L377="",G378,L377+G378))</f>
+        <f>IF(G368="","",IF(L367="",G368,L367+G368))</f>
         <v/>
       </c>
       <c r="M368" s="55" t="n"/>
@@ -55121,7 +55411,7 @@
       <c r="J369" s="47" t="n"/>
       <c r="K369" s="47" t="n"/>
       <c r="L369" s="50">
-        <f>IF(G379="","",IF(L378="",G379,L378+G379))</f>
+        <f>IF(G369="","",IF(L368="",G369,L368+G369))</f>
         <v/>
       </c>
       <c r="M369" s="47" t="n"/>
@@ -55141,7 +55431,7 @@
       <c r="J370" s="55" t="n"/>
       <c r="K370" s="55" t="n"/>
       <c r="L370" s="58">
-        <f>IF(G380="","",IF(L379="",G380,L379+G380))</f>
+        <f>IF(G370="","",IF(L369="",G370,L369+G370))</f>
         <v/>
       </c>
       <c r="M370" s="55" t="n"/>
@@ -55161,7 +55451,7 @@
       <c r="J371" s="47" t="n"/>
       <c r="K371" s="47" t="n"/>
       <c r="L371" s="50">
-        <f>IF(G381="","",IF(L380="",G381,L380+G381))</f>
+        <f>IF(G371="","",IF(L370="",G371,L370+G371))</f>
         <v/>
       </c>
       <c r="M371" s="47" t="n"/>
@@ -55181,7 +55471,7 @@
       <c r="J372" s="55" t="n"/>
       <c r="K372" s="55" t="n"/>
       <c r="L372" s="58">
-        <f>IF(G382="","",IF(L381="",G382,L381+G382))</f>
+        <f>IF(G372="","",IF(L371="",G372,L371+G372))</f>
         <v/>
       </c>
       <c r="M372" s="55" t="n"/>
@@ -55201,7 +55491,7 @@
       <c r="J373" s="47" t="n"/>
       <c r="K373" s="47" t="n"/>
       <c r="L373" s="50">
-        <f>IF(G383="","",IF(L382="",G383,L382+G383))</f>
+        <f>IF(G373="","",IF(L372="",G373,L372+G373))</f>
         <v/>
       </c>
       <c r="M373" s="47" t="n"/>
@@ -55221,7 +55511,7 @@
       <c r="J374" s="55" t="n"/>
       <c r="K374" s="55" t="n"/>
       <c r="L374" s="58">
-        <f>IF(G384="","",IF(L383="",G384,L383+G384))</f>
+        <f>IF(G374="","",IF(L373="",G374,L373+G374))</f>
         <v/>
       </c>
       <c r="M374" s="55" t="n"/>
@@ -55241,7 +55531,7 @@
       <c r="J375" s="47" t="n"/>
       <c r="K375" s="47" t="n"/>
       <c r="L375" s="50">
-        <f>IF(G385="","",IF(L384="",G385,L384+G385))</f>
+        <f>IF(G375="","",IF(L374="",G375,L374+G375))</f>
         <v/>
       </c>
       <c r="M375" s="47" t="n"/>
@@ -55261,7 +55551,7 @@
       <c r="J376" s="55" t="n"/>
       <c r="K376" s="55" t="n"/>
       <c r="L376" s="58">
-        <f>IF(G386="","",IF(L385="",G386,L385+G386))</f>
+        <f>IF(G376="","",IF(L375="",G376,L375+G376))</f>
         <v/>
       </c>
       <c r="M376" s="55" t="n"/>
@@ -55281,7 +55571,7 @@
       <c r="J377" s="47" t="n"/>
       <c r="K377" s="47" t="n"/>
       <c r="L377" s="50">
-        <f>IF(G387="","",IF(L386="",G387,L386+G387))</f>
+        <f>IF(G377="","",IF(L376="",G377,L376+G377))</f>
         <v/>
       </c>
       <c r="M377" s="47" t="n"/>
@@ -55301,7 +55591,7 @@
       <c r="J378" s="55" t="n"/>
       <c r="K378" s="55" t="n"/>
       <c r="L378" s="58">
-        <f>IF(G388="","",IF(L387="",G388,L387+G388))</f>
+        <f>IF(G378="","",IF(L377="",G378,L377+G378))</f>
         <v/>
       </c>
       <c r="M378" s="55" t="n"/>
@@ -55321,7 +55611,7 @@
       <c r="J379" s="47" t="n"/>
       <c r="K379" s="47" t="n"/>
       <c r="L379" s="50">
-        <f>IF(G389="","",IF(L388="",G389,L388+G389))</f>
+        <f>IF(G379="","",IF(L378="",G379,L378+G379))</f>
         <v/>
       </c>
       <c r="M379" s="47" t="n"/>
@@ -55341,7 +55631,7 @@
       <c r="J380" s="55" t="n"/>
       <c r="K380" s="55" t="n"/>
       <c r="L380" s="58">
-        <f>IF(G390="","",IF(L389="",G390,L389+G390))</f>
+        <f>IF(G380="","",IF(L379="",G380,L379+G380))</f>
         <v/>
       </c>
       <c r="M380" s="55" t="n"/>
@@ -55361,7 +55651,7 @@
       <c r="J381" s="47" t="n"/>
       <c r="K381" s="47" t="n"/>
       <c r="L381" s="50">
-        <f>IF(G391="","",IF(L390="",G391,L390+G391))</f>
+        <f>IF(G381="","",IF(L380="",G381,L380+G381))</f>
         <v/>
       </c>
       <c r="M381" s="47" t="n"/>
@@ -55381,7 +55671,7 @@
       <c r="J382" s="55" t="n"/>
       <c r="K382" s="55" t="n"/>
       <c r="L382" s="58">
-        <f>IF(G392="","",IF(L391="",G392,L391+G392))</f>
+        <f>IF(G382="","",IF(L381="",G382,L381+G382))</f>
         <v/>
       </c>
       <c r="M382" s="55" t="n"/>
@@ -55401,7 +55691,7 @@
       <c r="J383" s="47" t="n"/>
       <c r="K383" s="47" t="n"/>
       <c r="L383" s="50">
-        <f>IF(G393="","",IF(L392="",G393,L392+G393))</f>
+        <f>IF(G383="","",IF(L382="",G383,L382+G383))</f>
         <v/>
       </c>
       <c r="M383" s="47" t="n"/>
@@ -55421,7 +55711,7 @@
       <c r="J384" s="55" t="n"/>
       <c r="K384" s="55" t="n"/>
       <c r="L384" s="58">
-        <f>IF(G394="","",IF(L393="",G394,L393+G394))</f>
+        <f>IF(G384="","",IF(L383="",G384,L383+G384))</f>
         <v/>
       </c>
       <c r="M384" s="55" t="n"/>
@@ -55441,7 +55731,7 @@
       <c r="J385" s="47" t="n"/>
       <c r="K385" s="47" t="n"/>
       <c r="L385" s="50">
-        <f>IF(G395="","",IF(L394="",G395,L394+G395))</f>
+        <f>IF(G385="","",IF(L384="",G385,L384+G385))</f>
         <v/>
       </c>
       <c r="M385" s="47" t="n"/>
@@ -55461,7 +55751,7 @@
       <c r="J386" s="55" t="n"/>
       <c r="K386" s="55" t="n"/>
       <c r="L386" s="58">
-        <f>IF(G396="","",IF(L395="",G396,L395+G396))</f>
+        <f>IF(G386="","",IF(L385="",G386,L385+G386))</f>
         <v/>
       </c>
       <c r="M386" s="55" t="n"/>
@@ -55481,7 +55771,7 @@
       <c r="J387" s="47" t="n"/>
       <c r="K387" s="47" t="n"/>
       <c r="L387" s="50">
-        <f>IF(G397="","",IF(L396="",G397,L396+G397))</f>
+        <f>IF(G387="","",IF(L386="",G387,L386+G387))</f>
         <v/>
       </c>
       <c r="M387" s="47" t="n"/>
@@ -55501,7 +55791,7 @@
       <c r="J388" s="55" t="n"/>
       <c r="K388" s="55" t="n"/>
       <c r="L388" s="58">
-        <f>IF(G398="","",IF(L397="",G398,L397+G398))</f>
+        <f>IF(G388="","",IF(L387="",G388,L387+G388))</f>
         <v/>
       </c>
       <c r="M388" s="55" t="n"/>
@@ -55521,7 +55811,7 @@
       <c r="J389" s="47" t="n"/>
       <c r="K389" s="47" t="n"/>
       <c r="L389" s="50">
-        <f>IF(G399="","",IF(L398="",G399,L398+G399))</f>
+        <f>IF(G389="","",IF(L388="",G389,L388+G389))</f>
         <v/>
       </c>
       <c r="M389" s="47" t="n"/>
@@ -55541,7 +55831,7 @@
       <c r="J390" s="55" t="n"/>
       <c r="K390" s="55" t="n"/>
       <c r="L390" s="58">
-        <f>IF(G400="","",IF(L399="",G400,L399+G400))</f>
+        <f>IF(G390="","",IF(L389="",G390,L389+G390))</f>
         <v/>
       </c>
       <c r="M390" s="55" t="n"/>
@@ -55561,7 +55851,7 @@
       <c r="J391" s="47" t="n"/>
       <c r="K391" s="47" t="n"/>
       <c r="L391" s="50">
-        <f>IF(G401="","",IF(L400="",G401,L400+G401))</f>
+        <f>IF(G391="","",IF(L390="",G391,L390+G391))</f>
         <v/>
       </c>
       <c r="M391" s="47" t="n"/>
@@ -55581,7 +55871,7 @@
       <c r="J392" s="55" t="n"/>
       <c r="K392" s="55" t="n"/>
       <c r="L392" s="58">
-        <f>IF(G402="","",IF(L401="",G402,L401+G402))</f>
+        <f>IF(G392="","",IF(L391="",G392,L391+G392))</f>
         <v/>
       </c>
       <c r="M392" s="55" t="n"/>
@@ -55601,7 +55891,7 @@
       <c r="J393" s="47" t="n"/>
       <c r="K393" s="47" t="n"/>
       <c r="L393" s="50">
-        <f>IF(G403="","",IF(L402="",G403,L402+G403))</f>
+        <f>IF(G393="","",IF(L392="",G393,L392+G393))</f>
         <v/>
       </c>
       <c r="M393" s="47" t="n"/>
@@ -55621,7 +55911,7 @@
       <c r="J394" s="55" t="n"/>
       <c r="K394" s="55" t="n"/>
       <c r="L394" s="58">
-        <f>IF(G404="","",IF(L403="",G404,L403+G404))</f>
+        <f>IF(G394="","",IF(L393="",G394,L393+G394))</f>
         <v/>
       </c>
       <c r="M394" s="55" t="n"/>
@@ -55641,7 +55931,7 @@
       <c r="J395" s="47" t="n"/>
       <c r="K395" s="47" t="n"/>
       <c r="L395" s="50">
-        <f>IF(G405="","",IF(L404="",G405,L404+G405))</f>
+        <f>IF(G395="","",IF(L394="",G395,L394+G395))</f>
         <v/>
       </c>
       <c r="M395" s="47" t="n"/>
@@ -55661,7 +55951,7 @@
       <c r="J396" s="55" t="n"/>
       <c r="K396" s="55" t="n"/>
       <c r="L396" s="58">
-        <f>IF(G406="","",IF(L405="",G406,L405+G406))</f>
+        <f>IF(G396="","",IF(L395="",G396,L395+G396))</f>
         <v/>
       </c>
       <c r="M396" s="55" t="n"/>
@@ -55681,7 +55971,7 @@
       <c r="J397" s="47" t="n"/>
       <c r="K397" s="47" t="n"/>
       <c r="L397" s="50">
-        <f>IF(G407="","",IF(L406="",G407,L406+G407))</f>
+        <f>IF(G397="","",IF(L396="",G397,L396+G397))</f>
         <v/>
       </c>
       <c r="M397" s="47" t="n"/>
@@ -55701,7 +55991,7 @@
       <c r="J398" s="55" t="n"/>
       <c r="K398" s="55" t="n"/>
       <c r="L398" s="58">
-        <f>IF(G408="","",IF(L407="",G408,L407+G408))</f>
+        <f>IF(G398="","",IF(L397="",G398,L397+G398))</f>
         <v/>
       </c>
       <c r="M398" s="55" t="n"/>
@@ -55721,7 +56011,7 @@
       <c r="J399" s="47" t="n"/>
       <c r="K399" s="47" t="n"/>
       <c r="L399" s="50">
-        <f>IF(G409="","",IF(L408="",G409,L408+G409))</f>
+        <f>IF(G399="","",IF(L398="",G399,L398+G399))</f>
         <v/>
       </c>
       <c r="M399" s="47" t="n"/>
@@ -55741,7 +56031,7 @@
       <c r="J400" s="55" t="n"/>
       <c r="K400" s="55" t="n"/>
       <c r="L400" s="58">
-        <f>IF(G410="","",IF(L409="",G410,L409+G410))</f>
+        <f>IF(G400="","",IF(L399="",G400,L399+G400))</f>
         <v/>
       </c>
       <c r="M400" s="55" t="n"/>
@@ -55761,7 +56051,7 @@
       <c r="J401" s="47" t="n"/>
       <c r="K401" s="47" t="n"/>
       <c r="L401" s="50">
-        <f>IF(G411="","",IF(L410="",G411,L410+G411))</f>
+        <f>IF(G401="","",IF(L400="",G401,L400+G401))</f>
         <v/>
       </c>
       <c r="M401" s="47" t="n"/>
@@ -55781,7 +56071,7 @@
       <c r="J402" s="55" t="n"/>
       <c r="K402" s="55" t="n"/>
       <c r="L402" s="58">
-        <f>IF(G412="","",IF(L411="",G412,L411+G412))</f>
+        <f>IF(G402="","",IF(L401="",G402,L401+G402))</f>
         <v/>
       </c>
       <c r="M402" s="55" t="n"/>
@@ -55801,7 +56091,7 @@
       <c r="J403" s="47" t="n"/>
       <c r="K403" s="47" t="n"/>
       <c r="L403" s="50">
-        <f>IF(G413="","",IF(L412="",G413,L412+G413))</f>
+        <f>IF(G403="","",IF(L402="",G403,L402+G403))</f>
         <v/>
       </c>
       <c r="M403" s="47" t="n"/>
@@ -55821,7 +56111,7 @@
       <c r="J404" s="55" t="n"/>
       <c r="K404" s="55" t="n"/>
       <c r="L404" s="58">
-        <f>IF(G414="","",IF(L413="",G414,L413+G414))</f>
+        <f>IF(G404="","",IF(L403="",G404,L403+G404))</f>
         <v/>
       </c>
       <c r="M404" s="55" t="n"/>
@@ -55841,7 +56131,7 @@
       <c r="J405" s="47" t="n"/>
       <c r="K405" s="47" t="n"/>
       <c r="L405" s="50">
-        <f>IF(G415="","",IF(L414="",G415,L414+G415))</f>
+        <f>IF(G405="","",IF(L404="",G405,L404+G405))</f>
         <v/>
       </c>
       <c r="M405" s="47" t="n"/>
@@ -55861,7 +56151,7 @@
       <c r="J406" s="55" t="n"/>
       <c r="K406" s="55" t="n"/>
       <c r="L406" s="58">
-        <f>IF(G416="","",IF(L415="",G416,L415+G416))</f>
+        <f>IF(G406="","",IF(L405="",G406,L405+G406))</f>
         <v/>
       </c>
       <c r="M406" s="55" t="n"/>
@@ -55881,7 +56171,7 @@
       <c r="J407" s="47" t="n"/>
       <c r="K407" s="47" t="n"/>
       <c r="L407" s="50">
-        <f>IF(G417="","",IF(L416="",G417,L416+G417))</f>
+        <f>IF(G407="","",IF(L406="",G407,L406+G407))</f>
         <v/>
       </c>
       <c r="M407" s="47" t="n"/>
@@ -55901,7 +56191,7 @@
       <c r="J408" s="55" t="n"/>
       <c r="K408" s="55" t="n"/>
       <c r="L408" s="58">
-        <f>IF(G418="","",IF(L417="",G418,L417+G418))</f>
+        <f>IF(G408="","",IF(L407="",G408,L407+G408))</f>
         <v/>
       </c>
       <c r="M408" s="55" t="n"/>
@@ -55921,7 +56211,7 @@
       <c r="J409" s="47" t="n"/>
       <c r="K409" s="47" t="n"/>
       <c r="L409" s="50">
-        <f>IF(G419="","",IF(L418="",G419,L418+G419))</f>
+        <f>IF(G409="","",IF(L408="",G409,L408+G409))</f>
         <v/>
       </c>
       <c r="M409" s="47" t="n"/>
@@ -55941,7 +56231,7 @@
       <c r="J410" s="55" t="n"/>
       <c r="K410" s="55" t="n"/>
       <c r="L410" s="58">
-        <f>IF(G420="","",IF(L419="",G420,L419+G420))</f>
+        <f>IF(G410="","",IF(L409="",G410,L409+G410))</f>
         <v/>
       </c>
       <c r="M410" s="55" t="n"/>
@@ -55961,7 +56251,7 @@
       <c r="J411" s="47" t="n"/>
       <c r="K411" s="47" t="n"/>
       <c r="L411" s="50">
-        <f>IF(G421="","",IF(L420="",G421,L420+G421))</f>
+        <f>IF(G411="","",IF(L410="",G411,L410+G411))</f>
         <v/>
       </c>
       <c r="M411" s="47" t="n"/>
@@ -55981,7 +56271,7 @@
       <c r="J412" s="55" t="n"/>
       <c r="K412" s="55" t="n"/>
       <c r="L412" s="58">
-        <f>IF(G422="","",IF(L421="",G422,L421+G422))</f>
+        <f>IF(G412="","",IF(L411="",G412,L411+G412))</f>
         <v/>
       </c>
       <c r="M412" s="55" t="n"/>
@@ -56001,7 +56291,7 @@
       <c r="J413" s="47" t="n"/>
       <c r="K413" s="47" t="n"/>
       <c r="L413" s="50">
-        <f>IF(G423="","",IF(L422="",G423,L422+G423))</f>
+        <f>IF(G413="","",IF(L412="",G413,L412+G413))</f>
         <v/>
       </c>
       <c r="M413" s="47" t="n"/>
@@ -56021,7 +56311,7 @@
       <c r="J414" s="55" t="n"/>
       <c r="K414" s="55" t="n"/>
       <c r="L414" s="58">
-        <f>IF(G424="","",IF(L423="",G424,L423+G424))</f>
+        <f>IF(G414="","",IF(L413="",G414,L413+G414))</f>
         <v/>
       </c>
       <c r="M414" s="55" t="n"/>
@@ -56041,7 +56331,7 @@
       <c r="J415" s="47" t="n"/>
       <c r="K415" s="47" t="n"/>
       <c r="L415" s="50">
-        <f>IF(G425="","",IF(L424="",G425,L424+G425))</f>
+        <f>IF(G415="","",IF(L414="",G415,L414+G415))</f>
         <v/>
       </c>
       <c r="M415" s="47" t="n"/>
@@ -56061,7 +56351,7 @@
       <c r="J416" s="55" t="n"/>
       <c r="K416" s="55" t="n"/>
       <c r="L416" s="58">
-        <f>IF(G426="","",IF(L425="",G426,L425+G426))</f>
+        <f>IF(G416="","",IF(L415="",G416,L415+G416))</f>
         <v/>
       </c>
       <c r="M416" s="55" t="n"/>
@@ -56081,7 +56371,7 @@
       <c r="J417" s="47" t="n"/>
       <c r="K417" s="47" t="n"/>
       <c r="L417" s="50">
-        <f>IF(G427="","",IF(L426="",G427,L426+G427))</f>
+        <f>IF(G417="","",IF(L416="",G417,L416+G417))</f>
         <v/>
       </c>
       <c r="M417" s="47" t="n"/>
@@ -56101,7 +56391,7 @@
       <c r="J418" s="55" t="n"/>
       <c r="K418" s="55" t="n"/>
       <c r="L418" s="58">
-        <f>IF(G428="","",IF(L427="",G428,L427+G428))</f>
+        <f>IF(G418="","",IF(L417="",G418,L417+G418))</f>
         <v/>
       </c>
       <c r="M418" s="55" t="n"/>
@@ -56121,7 +56411,7 @@
       <c r="J419" s="47" t="n"/>
       <c r="K419" s="47" t="n"/>
       <c r="L419" s="50">
-        <f>IF(G429="","",IF(L428="",G429,L428+G429))</f>
+        <f>IF(G419="","",IF(L418="",G419,L418+G419))</f>
         <v/>
       </c>
       <c r="M419" s="47" t="n"/>
@@ -56141,7 +56431,7 @@
       <c r="J420" s="55" t="n"/>
       <c r="K420" s="55" t="n"/>
       <c r="L420" s="58">
-        <f>IF(G430="","",IF(L429="",G430,L429+G430))</f>
+        <f>IF(G420="","",IF(L419="",G420,L419+G420))</f>
         <v/>
       </c>
       <c r="M420" s="55" t="n"/>
@@ -56161,7 +56451,7 @@
       <c r="J421" s="47" t="n"/>
       <c r="K421" s="47" t="n"/>
       <c r="L421" s="50">
-        <f>IF(G431="","",IF(L430="",G431,L430+G431))</f>
+        <f>IF(G421="","",IF(L420="",G421,L420+G421))</f>
         <v/>
       </c>
       <c r="M421" s="47" t="n"/>
@@ -56181,7 +56471,7 @@
       <c r="J422" s="55" t="n"/>
       <c r="K422" s="55" t="n"/>
       <c r="L422" s="58">
-        <f>IF(G432="","",IF(L431="",G432,L431+G432))</f>
+        <f>IF(G422="","",IF(L421="",G422,L421+G422))</f>
         <v/>
       </c>
       <c r="M422" s="55" t="n"/>
@@ -56201,7 +56491,7 @@
       <c r="J423" s="47" t="n"/>
       <c r="K423" s="47" t="n"/>
       <c r="L423" s="50">
-        <f>IF(G433="","",IF(L432="",G433,L432+G433))</f>
+        <f>IF(G423="","",IF(L422="",G423,L422+G423))</f>
         <v/>
       </c>
       <c r="M423" s="47" t="n"/>
@@ -56221,7 +56511,7 @@
       <c r="J424" s="55" t="n"/>
       <c r="K424" s="55" t="n"/>
       <c r="L424" s="58">
-        <f>IF(G434="","",IF(L433="",G434,L433+G434))</f>
+        <f>IF(G424="","",IF(L423="",G424,L423+G424))</f>
         <v/>
       </c>
       <c r="M424" s="55" t="n"/>
@@ -56241,7 +56531,7 @@
       <c r="J425" s="47" t="n"/>
       <c r="K425" s="47" t="n"/>
       <c r="L425" s="50">
-        <f>IF(G435="","",IF(L434="",G435,L434+G435))</f>
+        <f>IF(G425="","",IF(L424="",G425,L424+G425))</f>
         <v/>
       </c>
       <c r="M425" s="47" t="n"/>
@@ -56261,7 +56551,7 @@
       <c r="J426" s="55" t="n"/>
       <c r="K426" s="55" t="n"/>
       <c r="L426" s="58">
-        <f>IF(G436="","",IF(L435="",G436,L435+G436))</f>
+        <f>IF(G426="","",IF(L425="",G426,L425+G426))</f>
         <v/>
       </c>
       <c r="M426" s="55" t="n"/>
@@ -56281,7 +56571,7 @@
       <c r="J427" s="47" t="n"/>
       <c r="K427" s="47" t="n"/>
       <c r="L427" s="50">
-        <f>IF(G437="","",IF(L436="",G437,L436+G437))</f>
+        <f>IF(G427="","",IF(L426="",G427,L426+G427))</f>
         <v/>
       </c>
       <c r="M427" s="47" t="n"/>
@@ -56301,7 +56591,7 @@
       <c r="J428" s="55" t="n"/>
       <c r="K428" s="55" t="n"/>
       <c r="L428" s="58">
-        <f>IF(G438="","",IF(L437="",G438,L437+G438))</f>
+        <f>IF(G428="","",IF(L427="",G428,L427+G428))</f>
         <v/>
       </c>
       <c r="M428" s="55" t="n"/>
@@ -56321,7 +56611,7 @@
       <c r="J429" s="47" t="n"/>
       <c r="K429" s="47" t="n"/>
       <c r="L429" s="50">
-        <f>IF(G439="","",IF(L438="",G439,L438+G439))</f>
+        <f>IF(G429="","",IF(L428="",G429,L428+G429))</f>
         <v/>
       </c>
       <c r="M429" s="47" t="n"/>
@@ -56341,7 +56631,7 @@
       <c r="J430" s="55" t="n"/>
       <c r="K430" s="55" t="n"/>
       <c r="L430" s="58">
-        <f>IF(G440="","",IF(L439="",G440,L439+G440))</f>
+        <f>IF(G430="","",IF(L429="",G430,L429+G430))</f>
         <v/>
       </c>
       <c r="M430" s="55" t="n"/>
@@ -56361,7 +56651,7 @@
       <c r="J431" s="47" t="n"/>
       <c r="K431" s="47" t="n"/>
       <c r="L431" s="50">
-        <f>IF(G441="","",IF(L440="",G441,L440+G441))</f>
+        <f>IF(G431="","",IF(L430="",G431,L430+G431))</f>
         <v/>
       </c>
       <c r="M431" s="47" t="n"/>
@@ -56381,7 +56671,7 @@
       <c r="J432" s="55" t="n"/>
       <c r="K432" s="55" t="n"/>
       <c r="L432" s="58">
-        <f>IF(G442="","",IF(L441="",G442,L441+G442))</f>
+        <f>IF(G432="","",IF(L431="",G432,L431+G432))</f>
         <v/>
       </c>
       <c r="M432" s="55" t="n"/>
@@ -56401,7 +56691,7 @@
       <c r="J433" s="47" t="n"/>
       <c r="K433" s="47" t="n"/>
       <c r="L433" s="50">
-        <f>IF(G443="","",IF(L442="",G443,L442+G443))</f>
+        <f>IF(G433="","",IF(L432="",G433,L432+G433))</f>
         <v/>
       </c>
       <c r="M433" s="47" t="n"/>
@@ -56421,7 +56711,7 @@
       <c r="J434" s="55" t="n"/>
       <c r="K434" s="55" t="n"/>
       <c r="L434" s="58">
-        <f>IF(G444="","",IF(L443="",G444,L443+G444))</f>
+        <f>IF(G434="","",IF(L433="",G434,L433+G434))</f>
         <v/>
       </c>
       <c r="M434" s="55" t="n"/>
@@ -56441,7 +56731,7 @@
       <c r="J435" s="47" t="n"/>
       <c r="K435" s="47" t="n"/>
       <c r="L435" s="50">
-        <f>IF(G445="","",IF(L444="",G445,L444+G445))</f>
+        <f>IF(G435="","",IF(L434="",G435,L434+G435))</f>
         <v/>
       </c>
       <c r="M435" s="47" t="n"/>
@@ -56461,7 +56751,7 @@
       <c r="J436" s="55" t="n"/>
       <c r="K436" s="55" t="n"/>
       <c r="L436" s="58">
-        <f>IF(G446="","",IF(L445="",G446,L445+G446))</f>
+        <f>IF(G436="","",IF(L435="",G436,L435+G436))</f>
         <v/>
       </c>
       <c r="M436" s="55" t="n"/>
@@ -56481,7 +56771,7 @@
       <c r="J437" s="47" t="n"/>
       <c r="K437" s="47" t="n"/>
       <c r="L437" s="50">
-        <f>IF(G447="","",IF(L446="",G447,L446+G447))</f>
+        <f>IF(G437="","",IF(L436="",G437,L436+G437))</f>
         <v/>
       </c>
       <c r="M437" s="47" t="n"/>
@@ -56501,7 +56791,7 @@
       <c r="J438" s="55" t="n"/>
       <c r="K438" s="55" t="n"/>
       <c r="L438" s="58">
-        <f>IF(G448="","",IF(L447="",G448,L447+G448))</f>
+        <f>IF(G438="","",IF(L437="",G438,L437+G438))</f>
         <v/>
       </c>
       <c r="M438" s="55" t="n"/>
@@ -56521,7 +56811,7 @@
       <c r="J439" s="47" t="n"/>
       <c r="K439" s="47" t="n"/>
       <c r="L439" s="50">
-        <f>IF(G449="","",IF(L448="",G449,L448+G449))</f>
+        <f>IF(G439="","",IF(L438="",G439,L438+G439))</f>
         <v/>
       </c>
       <c r="M439" s="47" t="n"/>
@@ -56541,7 +56831,7 @@
       <c r="J440" s="55" t="n"/>
       <c r="K440" s="55" t="n"/>
       <c r="L440" s="58">
-        <f>IF(G450="","",IF(L449="",G450,L449+G450))</f>
+        <f>IF(G440="","",IF(L439="",G440,L439+G440))</f>
         <v/>
       </c>
       <c r="M440" s="55" t="n"/>
@@ -56561,7 +56851,7 @@
       <c r="J441" s="47" t="n"/>
       <c r="K441" s="47" t="n"/>
       <c r="L441" s="50">
-        <f>IF(G451="","",IF(L450="",G451,L450+G451))</f>
+        <f>IF(G441="","",IF(L440="",G441,L440+G441))</f>
         <v/>
       </c>
       <c r="M441" s="47" t="n"/>
@@ -56581,7 +56871,7 @@
       <c r="J442" s="55" t="n"/>
       <c r="K442" s="55" t="n"/>
       <c r="L442" s="58">
-        <f>IF(G452="","",IF(L451="",G452,L451+G452))</f>
+        <f>IF(G442="","",IF(L441="",G442,L441+G442))</f>
         <v/>
       </c>
       <c r="M442" s="55" t="n"/>
@@ -56601,7 +56891,7 @@
       <c r="J443" s="47" t="n"/>
       <c r="K443" s="47" t="n"/>
       <c r="L443" s="50">
-        <f>IF(G453="","",IF(L452="",G453,L452+G453))</f>
+        <f>IF(G443="","",IF(L442="",G443,L442+G443))</f>
         <v/>
       </c>
       <c r="M443" s="47" t="n"/>
@@ -56621,7 +56911,7 @@
       <c r="J444" s="55" t="n"/>
       <c r="K444" s="55" t="n"/>
       <c r="L444" s="58">
-        <f>IF(G454="","",IF(L453="",G454,L453+G454))</f>
+        <f>IF(G444="","",IF(L443="",G444,L443+G444))</f>
         <v/>
       </c>
       <c r="M444" s="55" t="n"/>
@@ -56641,7 +56931,7 @@
       <c r="J445" s="47" t="n"/>
       <c r="K445" s="47" t="n"/>
       <c r="L445" s="50">
-        <f>IF(G455="","",IF(L454="",G455,L454+G455))</f>
+        <f>IF(G445="","",IF(L444="",G445,L444+G445))</f>
         <v/>
       </c>
       <c r="M445" s="47" t="n"/>
@@ -56661,7 +56951,7 @@
       <c r="J446" s="55" t="n"/>
       <c r="K446" s="55" t="n"/>
       <c r="L446" s="58">
-        <f>IF(G456="","",IF(L455="",G456,L455+G456))</f>
+        <f>IF(G446="","",IF(L445="",G446,L445+G446))</f>
         <v/>
       </c>
       <c r="M446" s="55" t="n"/>
@@ -56681,7 +56971,7 @@
       <c r="J447" s="47" t="n"/>
       <c r="K447" s="47" t="n"/>
       <c r="L447" s="50">
-        <f>IF(G457="","",IF(L456="",G457,L456+G457))</f>
+        <f>IF(G447="","",IF(L446="",G447,L446+G447))</f>
         <v/>
       </c>
       <c r="M447" s="47" t="n"/>
@@ -56701,7 +56991,7 @@
       <c r="J448" s="55" t="n"/>
       <c r="K448" s="55" t="n"/>
       <c r="L448" s="58">
-        <f>IF(G458="","",IF(L457="",G458,L457+G458))</f>
+        <f>IF(G448="","",IF(L447="",G448,L447+G448))</f>
         <v/>
       </c>
       <c r="M448" s="55" t="n"/>
@@ -56721,7 +57011,7 @@
       <c r="J449" s="47" t="n"/>
       <c r="K449" s="47" t="n"/>
       <c r="L449" s="50">
-        <f>IF(G459="","",IF(L458="",G459,L458+G459))</f>
+        <f>IF(G449="","",IF(L448="",G449,L448+G449))</f>
         <v/>
       </c>
       <c r="M449" s="47" t="n"/>
@@ -56741,7 +57031,7 @@
       <c r="J450" s="55" t="n"/>
       <c r="K450" s="55" t="n"/>
       <c r="L450" s="58">
-        <f>IF(G460="","",IF(L459="",G460,L459+G460))</f>
+        <f>IF(G450="","",IF(L449="",G450,L449+G450))</f>
         <v/>
       </c>
       <c r="M450" s="55" t="n"/>
@@ -56761,7 +57051,7 @@
       <c r="J451" s="47" t="n"/>
       <c r="K451" s="47" t="n"/>
       <c r="L451" s="50">
-        <f>IF(G461="","",IF(L460="",G461,L460+G461))</f>
+        <f>IF(G451="","",IF(L450="",G451,L450+G451))</f>
         <v/>
       </c>
       <c r="M451" s="47" t="n"/>
@@ -56781,7 +57071,7 @@
       <c r="J452" s="55" t="n"/>
       <c r="K452" s="55" t="n"/>
       <c r="L452" s="58">
-        <f>IF(G462="","",IF(L461="",G462,L461+G462))</f>
+        <f>IF(G452="","",IF(L451="",G452,L451+G452))</f>
         <v/>
       </c>
       <c r="M452" s="55" t="n"/>
@@ -56801,7 +57091,7 @@
       <c r="J453" s="47" t="n"/>
       <c r="K453" s="47" t="n"/>
       <c r="L453" s="50">
-        <f>IF(G463="","",IF(L462="",G463,L462+G463))</f>
+        <f>IF(G453="","",IF(L452="",G453,L452+G453))</f>
         <v/>
       </c>
       <c r="M453" s="47" t="n"/>
@@ -56821,7 +57111,7 @@
       <c r="J454" s="55" t="n"/>
       <c r="K454" s="55" t="n"/>
       <c r="L454" s="58">
-        <f>IF(G464="","",IF(L463="",G464,L463+G464))</f>
+        <f>IF(G454="","",IF(L453="",G454,L453+G454))</f>
         <v/>
       </c>
       <c r="M454" s="55" t="n"/>
@@ -56841,7 +57131,7 @@
       <c r="J455" s="47" t="n"/>
       <c r="K455" s="47" t="n"/>
       <c r="L455" s="50">
-        <f>IF(G465="","",IF(L464="",G465,L464+G465))</f>
+        <f>IF(G455="","",IF(L454="",G455,L454+G455))</f>
         <v/>
       </c>
       <c r="M455" s="47" t="n"/>
@@ -56861,7 +57151,7 @@
       <c r="J456" s="55" t="n"/>
       <c r="K456" s="55" t="n"/>
       <c r="L456" s="58">
-        <f>IF(G466="","",IF(L465="",G466,L465+G466))</f>
+        <f>IF(G456="","",IF(L455="",G456,L455+G456))</f>
         <v/>
       </c>
       <c r="M456" s="55" t="n"/>
@@ -56881,7 +57171,7 @@
       <c r="J457" s="47" t="n"/>
       <c r="K457" s="47" t="n"/>
       <c r="L457" s="50">
-        <f>IF(G467="","",IF(L466="",G467,L466+G467))</f>
+        <f>IF(G457="","",IF(L456="",G457,L456+G457))</f>
         <v/>
       </c>
       <c r="M457" s="47" t="n"/>
@@ -56901,7 +57191,7 @@
       <c r="J458" s="55" t="n"/>
       <c r="K458" s="55" t="n"/>
       <c r="L458" s="58">
-        <f>IF(G468="","",IF(L467="",G468,L467+G468))</f>
+        <f>IF(G458="","",IF(L457="",G458,L457+G458))</f>
         <v/>
       </c>
       <c r="M458" s="55" t="n"/>
@@ -56921,7 +57211,7 @@
       <c r="J459" s="47" t="n"/>
       <c r="K459" s="47" t="n"/>
       <c r="L459" s="50">
-        <f>IF(G469="","",IF(L468="",G469,L468+G469))</f>
+        <f>IF(G459="","",IF(L458="",G459,L458+G459))</f>
         <v/>
       </c>
       <c r="M459" s="47" t="n"/>
@@ -56941,7 +57231,7 @@
       <c r="J460" s="55" t="n"/>
       <c r="K460" s="55" t="n"/>
       <c r="L460" s="58">
-        <f>IF(G470="","",IF(L469="",G470,L469+G470))</f>
+        <f>IF(G460="","",IF(L459="",G460,L459+G460))</f>
         <v/>
       </c>
       <c r="M460" s="55" t="n"/>
@@ -56961,7 +57251,7 @@
       <c r="J461" s="47" t="n"/>
       <c r="K461" s="47" t="n"/>
       <c r="L461" s="50">
-        <f>IF(G471="","",IF(L470="",G471,L470+G471))</f>
+        <f>IF(G461="","",IF(L460="",G461,L460+G461))</f>
         <v/>
       </c>
       <c r="M461" s="47" t="n"/>
@@ -56981,7 +57271,7 @@
       <c r="J462" s="55" t="n"/>
       <c r="K462" s="55" t="n"/>
       <c r="L462" s="58">
-        <f>IF(G472="","",IF(L471="",G472,L471+G472))</f>
+        <f>IF(G462="","",IF(L461="",G462,L461+G462))</f>
         <v/>
       </c>
       <c r="M462" s="55" t="n"/>
@@ -57001,7 +57291,7 @@
       <c r="J463" s="47" t="n"/>
       <c r="K463" s="47" t="n"/>
       <c r="L463" s="50">
-        <f>IF(G473="","",IF(L472="",G473,L472+G473))</f>
+        <f>IF(G463="","",IF(L462="",G463,L462+G463))</f>
         <v/>
       </c>
       <c r="M463" s="47" t="n"/>
@@ -57021,7 +57311,7 @@
       <c r="J464" s="55" t="n"/>
       <c r="K464" s="55" t="n"/>
       <c r="L464" s="58">
-        <f>IF(G474="","",IF(L473="",G474,L473+G474))</f>
+        <f>IF(G464="","",IF(L463="",G464,L463+G464))</f>
         <v/>
       </c>
       <c r="M464" s="55" t="n"/>
@@ -57041,7 +57331,7 @@
       <c r="J465" s="47" t="n"/>
       <c r="K465" s="47" t="n"/>
       <c r="L465" s="50">
-        <f>IF(G475="","",IF(L474="",G475,L474+G475))</f>
+        <f>IF(G465="","",IF(L464="",G465,L464+G465))</f>
         <v/>
       </c>
       <c r="M465" s="47" t="n"/>
@@ -57061,7 +57351,7 @@
       <c r="J466" s="55" t="n"/>
       <c r="K466" s="55" t="n"/>
       <c r="L466" s="58">
-        <f>IF(G476="","",IF(L475="",G476,L475+G476))</f>
+        <f>IF(G466="","",IF(L465="",G466,L465+G466))</f>
         <v/>
       </c>
       <c r="M466" s="55" t="n"/>
@@ -57081,7 +57371,7 @@
       <c r="J467" s="47" t="n"/>
       <c r="K467" s="47" t="n"/>
       <c r="L467" s="50">
-        <f>IF(G477="","",IF(L476="",G477,L476+G477))</f>
+        <f>IF(G467="","",IF(L466="",G467,L466+G467))</f>
         <v/>
       </c>
       <c r="M467" s="47" t="n"/>
@@ -57101,7 +57391,7 @@
       <c r="J468" s="55" t="n"/>
       <c r="K468" s="55" t="n"/>
       <c r="L468" s="58">
-        <f>IF(G478="","",IF(L477="",G478,L477+G478))</f>
+        <f>IF(G468="","",IF(L467="",G468,L467+G468))</f>
         <v/>
       </c>
       <c r="M468" s="55" t="n"/>
@@ -57121,7 +57411,7 @@
       <c r="J469" s="47" t="n"/>
       <c r="K469" s="47" t="n"/>
       <c r="L469" s="50">
-        <f>IF(G479="","",IF(L478="",G479,L478+G479))</f>
+        <f>IF(G469="","",IF(L468="",G469,L468+G469))</f>
         <v/>
       </c>
       <c r="M469" s="47" t="n"/>
@@ -57141,7 +57431,7 @@
       <c r="J470" s="55" t="n"/>
       <c r="K470" s="55" t="n"/>
       <c r="L470" s="58">
-        <f>IF(G480="","",IF(L479="",G480,L479+G480))</f>
+        <f>IF(G470="","",IF(L469="",G470,L469+G470))</f>
         <v/>
       </c>
       <c r="M470" s="55" t="n"/>
@@ -57161,7 +57451,7 @@
       <c r="J471" s="47" t="n"/>
       <c r="K471" s="47" t="n"/>
       <c r="L471" s="50">
-        <f>IF(G481="","",IF(L480="",G481,L480+G481))</f>
+        <f>IF(G471="","",IF(L470="",G471,L470+G471))</f>
         <v/>
       </c>
       <c r="M471" s="47" t="n"/>
@@ -57181,7 +57471,7 @@
       <c r="J472" s="55" t="n"/>
       <c r="K472" s="55" t="n"/>
       <c r="L472" s="58">
-        <f>IF(G482="","",IF(L481="",G482,L481+G482))</f>
+        <f>IF(G472="","",IF(L471="",G472,L471+G472))</f>
         <v/>
       </c>
       <c r="M472" s="55" t="n"/>
@@ -57201,7 +57491,7 @@
       <c r="J473" s="47" t="n"/>
       <c r="K473" s="47" t="n"/>
       <c r="L473" s="50">
-        <f>IF(G483="","",IF(L482="",G483,L482+G483))</f>
+        <f>IF(G473="","",IF(L472="",G473,L472+G473))</f>
         <v/>
       </c>
       <c r="M473" s="47" t="n"/>
@@ -57221,7 +57511,7 @@
       <c r="J474" s="55" t="n"/>
       <c r="K474" s="55" t="n"/>
       <c r="L474" s="58">
-        <f>IF(G484="","",IF(L483="",G484,L483+G484))</f>
+        <f>IF(G474="","",IF(L473="",G474,L473+G474))</f>
         <v/>
       </c>
       <c r="M474" s="55" t="n"/>
@@ -57241,7 +57531,7 @@
       <c r="J475" s="47" t="n"/>
       <c r="K475" s="47" t="n"/>
       <c r="L475" s="50">
-        <f>IF(G485="","",IF(L484="",G485,L484+G485))</f>
+        <f>IF(G475="","",IF(L474="",G475,L474+G475))</f>
         <v/>
       </c>
       <c r="M475" s="47" t="n"/>
@@ -57261,7 +57551,7 @@
       <c r="J476" s="55" t="n"/>
       <c r="K476" s="55" t="n"/>
       <c r="L476" s="58">
-        <f>IF(G486="","",IF(L485="",G486,L485+G486))</f>
+        <f>IF(G476="","",IF(L475="",G476,L475+G476))</f>
         <v/>
       </c>
       <c r="M476" s="55" t="n"/>
@@ -57281,7 +57571,7 @@
       <c r="J477" s="47" t="n"/>
       <c r="K477" s="47" t="n"/>
       <c r="L477" s="50">
-        <f>IF(G487="","",IF(L486="",G487,L486+G487))</f>
+        <f>IF(G477="","",IF(L476="",G477,L476+G477))</f>
         <v/>
       </c>
       <c r="M477" s="47" t="n"/>
@@ -57301,7 +57591,7 @@
       <c r="J478" s="55" t="n"/>
       <c r="K478" s="55" t="n"/>
       <c r="L478" s="58">
-        <f>IF(G488="","",IF(L487="",G488,L487+G488))</f>
+        <f>IF(G478="","",IF(L477="",G478,L477+G478))</f>
         <v/>
       </c>
       <c r="M478" s="55" t="n"/>
@@ -57321,7 +57611,7 @@
       <c r="J479" s="47" t="n"/>
       <c r="K479" s="47" t="n"/>
       <c r="L479" s="50">
-        <f>IF(G489="","",IF(L488="",G489,L488+G489))</f>
+        <f>IF(G479="","",IF(L478="",G479,L478+G479))</f>
         <v/>
       </c>
       <c r="M479" s="47" t="n"/>
@@ -57341,7 +57631,7 @@
       <c r="J480" s="55" t="n"/>
       <c r="K480" s="55" t="n"/>
       <c r="L480" s="58">
-        <f>IF(G490="","",IF(L489="",G490,L489+G490))</f>
+        <f>IF(G480="","",IF(L479="",G480,L479+G480))</f>
         <v/>
       </c>
       <c r="M480" s="55" t="n"/>
@@ -57361,7 +57651,7 @@
       <c r="J481" s="47" t="n"/>
       <c r="K481" s="47" t="n"/>
       <c r="L481" s="50">
-        <f>IF(G491="","",IF(L490="",G491,L490+G491))</f>
+        <f>IF(G481="","",IF(L480="",G481,L480+G481))</f>
         <v/>
       </c>
       <c r="M481" s="47" t="n"/>
@@ -57381,7 +57671,7 @@
       <c r="J482" s="55" t="n"/>
       <c r="K482" s="55" t="n"/>
       <c r="L482" s="58">
-        <f>IF(G492="","",IF(L491="",G492,L491+G492))</f>
+        <f>IF(G482="","",IF(L481="",G482,L481+G482))</f>
         <v/>
       </c>
       <c r="M482" s="55" t="n"/>
@@ -57401,7 +57691,7 @@
       <c r="J483" s="47" t="n"/>
       <c r="K483" s="47" t="n"/>
       <c r="L483" s="50">
-        <f>IF(G493="","",IF(L492="",G493,L492+G493))</f>
+        <f>IF(G483="","",IF(L482="",G483,L482+G483))</f>
         <v/>
       </c>
       <c r="M483" s="47" t="n"/>
@@ -57421,7 +57711,7 @@
       <c r="J484" s="55" t="n"/>
       <c r="K484" s="55" t="n"/>
       <c r="L484" s="58">
-        <f>IF(G494="","",IF(L493="",G494,L493+G494))</f>
+        <f>IF(G484="","",IF(L483="",G484,L483+G484))</f>
         <v/>
       </c>
       <c r="M484" s="55" t="n"/>
@@ -57441,7 +57731,7 @@
       <c r="J485" s="47" t="n"/>
       <c r="K485" s="47" t="n"/>
       <c r="L485" s="50">
-        <f>IF(G495="","",IF(L494="",G495,L494+G495))</f>
+        <f>IF(G485="","",IF(L484="",G485,L484+G485))</f>
         <v/>
       </c>
       <c r="M485" s="47" t="n"/>
@@ -57461,7 +57751,7 @@
       <c r="J486" s="55" t="n"/>
       <c r="K486" s="55" t="n"/>
       <c r="L486" s="58">
-        <f>IF(G496="","",IF(L495="",G496,L495+G496))</f>
+        <f>IF(G486="","",IF(L485="",G486,L485+G486))</f>
         <v/>
       </c>
       <c r="M486" s="55" t="n"/>
@@ -57481,7 +57771,7 @@
       <c r="J487" s="47" t="n"/>
       <c r="K487" s="47" t="n"/>
       <c r="L487" s="50">
-        <f>IF(G497="","",IF(L496="",G497,L496+G497))</f>
+        <f>IF(G487="","",IF(L486="",G487,L486+G487))</f>
         <v/>
       </c>
       <c r="M487" s="47" t="n"/>
@@ -57501,7 +57791,7 @@
       <c r="J488" s="55" t="n"/>
       <c r="K488" s="55" t="n"/>
       <c r="L488" s="58">
-        <f>IF(G498="","",IF(L497="",G498,L497+G498))</f>
+        <f>IF(G488="","",IF(L487="",G488,L487+G488))</f>
         <v/>
       </c>
       <c r="M488" s="55" t="n"/>
@@ -57521,7 +57811,7 @@
       <c r="J489" s="47" t="n"/>
       <c r="K489" s="47" t="n"/>
       <c r="L489" s="50">
-        <f>IF(G499="","",IF(L498="",G499,L498+G499))</f>
+        <f>IF(G489="","",IF(L488="",G489,L488+G489))</f>
         <v/>
       </c>
       <c r="M489" s="47" t="n"/>
@@ -57541,7 +57831,7 @@
       <c r="J490" s="55" t="n"/>
       <c r="K490" s="55" t="n"/>
       <c r="L490" s="58">
-        <f>IF(G500="","",IF(L499="",G500,L499+G500))</f>
+        <f>IF(G490="","",IF(L489="",G490,L489+G490))</f>
         <v/>
       </c>
       <c r="M490" s="55" t="n"/>
@@ -57561,7 +57851,7 @@
       <c r="J491" s="47" t="n"/>
       <c r="K491" s="47" t="n"/>
       <c r="L491" s="50">
-        <f>IF(G501="","",IF(L500="",G501,L500+G501))</f>
+        <f>IF(G491="","",IF(L490="",G491,L490+G491))</f>
         <v/>
       </c>
       <c r="M491" s="47" t="n"/>
@@ -57581,7 +57871,7 @@
       <c r="J492" s="55" t="n"/>
       <c r="K492" s="55" t="n"/>
       <c r="L492" s="58">
-        <f>IF(G502="","",IF(L501="",G502,L501+G502))</f>
+        <f>IF(G492="","",IF(L491="",G492,L491+G492))</f>
         <v/>
       </c>
       <c r="M492" s="55" t="n"/>
@@ -57601,7 +57891,7 @@
       <c r="J493" s="47" t="n"/>
       <c r="K493" s="47" t="n"/>
       <c r="L493" s="50">
-        <f>IF(G503="","",IF(L502="",G503,L502+G503))</f>
+        <f>IF(G493="","",IF(L492="",G493,L492+G493))</f>
         <v/>
       </c>
       <c r="M493" s="47" t="n"/>
@@ -57621,7 +57911,7 @@
       <c r="J494" s="55" t="n"/>
       <c r="K494" s="55" t="n"/>
       <c r="L494" s="58">
-        <f>IF(G504="","",IF(L503="",G504,L503+G504))</f>
+        <f>IF(G494="","",IF(L493="",G494,L493+G494))</f>
         <v/>
       </c>
       <c r="M494" s="55" t="n"/>
@@ -57632,6 +57922,10 @@
         <is>
           <t>Y</t>
         </is>
+      </c>
+      <c r="L495">
+        <f>IF(G495="","",IF(L494="",G495,L494+G495))</f>
+        <v/>
       </c>
     </row>
     <row r="496" ht="15.75" customHeight="1" s="99"/>
@@ -57768,16 +58062,16 @@
         </is>
       </c>
       <c r="C5" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A5,'All Transactions'!F:F,B5)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A5,'All Transactions'!F:F,B5,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D5" s="42" t="inlineStr">
         <is>
-          <t>Nos/Trailor</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E5" s="65">
-        <f>IFERROR(F5/C5,"")</f>
+        <f>IFERROR(IF(C5=0,"",F5/C5),"")</f>
         <v/>
       </c>
       <c r="F5" s="66">
@@ -57800,25 +58094,25 @@
     <row r="6" ht="15.75" customHeight="1" s="99">
       <c r="A6" s="44" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B6" s="44" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Tiscon 10mm</t>
         </is>
       </c>
       <c r="C6" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A6,'All Transactions'!F:F,B6)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A6,'All Transactions'!F:F,B6,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D6" s="44" t="inlineStr">
         <is>
-          <t>CFT</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E6" s="70">
-        <f>IFERROR(F6/C6,"")</f>
+        <f>IFERROR(IF(C6=0,"",F6/C6),"")</f>
         <v/>
       </c>
       <c r="F6" s="71">
@@ -57850,16 +58144,16 @@
         </is>
       </c>
       <c r="C7" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A7,'All Transactions'!F:F,B7)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A7,'All Transactions'!F:F,B7,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D7" s="42" t="inlineStr">
         <is>
-          <t>Tonnes/Trailor</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E7" s="65">
-        <f>IFERROR(F7/C7,"")</f>
+        <f>IFERROR(IF(C7=0,"",F7/C7),"")</f>
         <v/>
       </c>
       <c r="F7" s="66">
@@ -57887,20 +58181,20 @@
       </c>
       <c r="B8" s="44" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Super</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="C8" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A8,'All Transactions'!F:F,B8)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A8,'All Transactions'!F:F,B8,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D8" s="44" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E8" s="70">
-        <f>IFERROR(F8/C8,"")</f>
+        <f>IFERROR(IF(C8=0,"",F8/C8),"")</f>
         <v/>
       </c>
       <c r="F8" s="71">
@@ -57928,20 +58222,20 @@
       </c>
       <c r="B9" s="42" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Normal</t>
+          <t>Cement</t>
         </is>
       </c>
       <c r="C9" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A9,'All Transactions'!F:F,B9)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A9,'All Transactions'!F:F,B9,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D9" s="42" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>bags</t>
         </is>
       </c>
       <c r="E9" s="65">
-        <f>IFERROR(F9/C9,"")</f>
+        <f>IFERROR(IF(C9=0,"",F9/C9),"")</f>
         <v/>
       </c>
       <c r="F9" s="66">
@@ -57964,25 +58258,25 @@
     <row r="10" ht="15.75" customHeight="1" s="99">
       <c r="A10" s="44" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B10" s="44" t="inlineStr">
         <is>
-          <t>Cement-Ultratech Prem</t>
+          <t>Tiscon 12mm</t>
         </is>
       </c>
       <c r="C10" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A10,'All Transactions'!F:F,B10)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A10,'All Transactions'!F:F,B10,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D10" s="44" t="inlineStr">
         <is>
-          <t>Bags</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E10" s="70">
-        <f>IFERROR(F10/C10,"")</f>
+        <f>IFERROR(IF(C10=0,"",F10/C10),"")</f>
         <v/>
       </c>
       <c r="F10" s="71">
@@ -58005,25 +58299,25 @@
     <row r="11" ht="15.75" customHeight="1" s="99">
       <c r="A11" s="42" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B11" s="42" t="inlineStr">
         <is>
-          <t>Dr Fixit</t>
+          <t>Tiscon 8mm</t>
         </is>
       </c>
       <c r="C11" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A11,'All Transactions'!F:F,B11)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A11,'All Transactions'!F:F,B11,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D11" s="42" t="inlineStr">
         <is>
-          <t>Litres</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E11" s="65">
-        <f>IFERROR(F11/C11,"")</f>
+        <f>IFERROR(IF(C11=0,"",F11/C11),"")</f>
         <v/>
       </c>
       <c r="F11" s="66">
@@ -58046,25 +58340,25 @@
     <row r="12" ht="15.75" customHeight="1" s="99">
       <c r="A12" s="44" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B12" s="44" t="inlineStr">
         <is>
-          <t>Pipe PVC/GI</t>
+          <t>Tiscon 6mm</t>
         </is>
       </c>
       <c r="C12" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A12,'All Transactions'!F:F,B12)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A12,'All Transactions'!F:F,B12,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D12" s="44" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E12" s="70">
-        <f>IFERROR(F12/C12,"")</f>
+        <f>IFERROR(IF(C12=0,"",F12/C12),"")</f>
         <v/>
       </c>
       <c r="F12" s="71">
@@ -58092,20 +58386,20 @@
       </c>
       <c r="B13" s="42" t="inlineStr">
         <is>
-          <t>Cover Block</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C13" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A13,'All Transactions'!F:F,B13)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A13,'All Transactions'!F:F,B13,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D13" s="42" t="inlineStr">
         <is>
-          <t>Packets</t>
+          <t>cft</t>
         </is>
       </c>
       <c r="E13" s="65">
-        <f>IFERROR(F13/C13,"")</f>
+        <f>IFERROR(IF(C13=0,"",F13/C13),"")</f>
         <v/>
       </c>
       <c r="F13" s="66">
@@ -58128,25 +58422,25 @@
     <row r="14" ht="15.75" customHeight="1" s="99">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>Kala Panni/Tar</t>
+          <t>Fabrication</t>
         </is>
       </c>
       <c r="C14" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A14,'All Transactions'!F:F,B14)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A14,'All Transactions'!F:F,B14,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D14" s="44" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="70">
-        <f>IFERROR(F14/C14,"")</f>
+        <f>IFERROR(IF(C14=0,"",F14/C14),"")</f>
         <v/>
       </c>
       <c r="F14" s="71">
@@ -58169,25 +58463,25 @@
     <row r="15" ht="15.75" customHeight="1" s="99">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="B15" s="42" t="inlineStr">
         <is>
-          <t>Bamboo/Shuttering</t>
+          <t>Electrical Items</t>
         </is>
       </c>
       <c r="C15" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A15,'All Transactions'!F:F,B15)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A15,'All Transactions'!F:F,B15,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>Nos</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E15" s="65">
-        <f>IFERROR(F15/C15,"")</f>
+        <f>IFERROR(IF(C15=0,"",F15/C15),"")</f>
         <v/>
       </c>
       <c r="F15" s="66">
@@ -58215,20 +58509,20 @@
       </c>
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>Nails</t>
+          <t>Dr Fixit</t>
         </is>
       </c>
       <c r="C16" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A16,'All Transactions'!F:F,B16)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A16,'All Transactions'!F:F,B16,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
-          <t>Kg/Bags</t>
+          <t>litres</t>
         </is>
       </c>
       <c r="E16" s="70">
-        <f>IFERROR(F16/C16,"")</f>
+        <f>IFERROR(IF(C16=0,"",F16/C16),"")</f>
         <v/>
       </c>
       <c r="F16" s="71">
@@ -58256,20 +58550,20 @@
       </c>
       <c r="B17" s="42" t="inlineStr">
         <is>
-          <t>Binding Wire</t>
+          <t>Water Tank</t>
         </is>
       </c>
       <c r="C17" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A17,'All Transactions'!F:F,B17)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A17,'All Transactions'!F:F,B17,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E17" s="65">
-        <f>IFERROR(F17/C17,"")</f>
+        <f>IFERROR(IF(C17=0,"",F17/C17),"")</f>
         <v/>
       </c>
       <c r="F17" s="66">
@@ -58292,25 +58586,25 @@
     <row r="18" ht="15.75" customHeight="1" s="99">
       <c r="A18" s="44" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>Blade</t>
+          <t>Tiscon 16mm</t>
         </is>
       </c>
       <c r="C18" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A18,'All Transactions'!F:F,B18)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A18,'All Transactions'!F:F,B18,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E18" s="70">
-        <f>IFERROR(F18/C18,"")</f>
+        <f>IFERROR(IF(C18=0,"",F18/C18),"")</f>
         <v/>
       </c>
       <c r="F18" s="71">
@@ -58333,25 +58627,25 @@
     <row r="19" ht="15.75" customHeight="1" s="99">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>Tiscon 16mm</t>
+          <t>Binding Wire</t>
         </is>
       </c>
       <c r="C19" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A19,'All Transactions'!F:F,B19)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A19,'All Transactions'!F:F,B19,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E19" s="65">
-        <f>IFERROR(F19/C19,"")</f>
+        <f>IFERROR(IF(C19=0,"",F19/C19),"")</f>
         <v/>
       </c>
       <c r="F19" s="66">
@@ -58374,25 +58668,25 @@
     <row r="20" ht="15.75" customHeight="1" s="99">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>Tiscon 12mm</t>
+          <t>Wire</t>
         </is>
       </c>
       <c r="C20" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A20,'All Transactions'!F:F,B20)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A20,'All Transactions'!F:F,B20,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D20" s="44" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E20" s="70">
-        <f>IFERROR(F20/C20,"")</f>
+        <f>IFERROR(IF(C20=0,"",F20/C20),"")</f>
         <v/>
       </c>
       <c r="F20" s="71">
@@ -58415,25 +58709,25 @@
     <row r="21" ht="15.75" customHeight="1" s="99">
       <c r="A21" s="42" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>Tiscon 10mm</t>
+          <t>Rings</t>
         </is>
       </c>
       <c r="C21" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A21,'All Transactions'!F:F,B21)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A21,'All Transactions'!F:F,B21,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D21" s="42" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E21" s="65">
-        <f>IFERROR(F21/C21,"")</f>
+        <f>IFERROR(IF(C21=0,"",F21/C21),"")</f>
         <v/>
       </c>
       <c r="F21" s="66">
@@ -58456,25 +58750,25 @@
     <row r="22" ht="15.75" customHeight="1" s="99">
       <c r="A22" s="44" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B22" s="44" t="inlineStr">
         <is>
-          <t>Tiscon 8mm</t>
+          <t>Cover Block</t>
         </is>
       </c>
       <c r="C22" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A22,'All Transactions'!F:F,B22)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A22,'All Transactions'!F:F,B22,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E22" s="70">
-        <f>IFERROR(F22/C22,"")</f>
+        <f>IFERROR(IF(C22=0,"",F22/C22),"")</f>
         <v/>
       </c>
       <c r="F22" s="71">
@@ -58497,25 +58791,25 @@
     <row r="23" ht="15.75" customHeight="1" s="99">
       <c r="A23" s="42" t="inlineStr">
         <is>
-          <t>Steel/Iron</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>Tiscon 6mm</t>
+          <t>Nails</t>
         </is>
       </c>
       <c r="C23" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A23,'All Transactions'!F:F,B23)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A23,'All Transactions'!F:F,B23,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D23" s="42" t="inlineStr">
         <is>
-          <t>Pcs</t>
+          <t>bags</t>
         </is>
       </c>
       <c r="E23" s="65">
-        <f>IFERROR(F23/C23,"")</f>
+        <f>IFERROR(IF(C23=0,"",F23/C23),"")</f>
         <v/>
       </c>
       <c r="F23" s="66">
@@ -58538,25 +58832,25 @@
     <row r="24" ht="15.75" customHeight="1" s="99">
       <c r="A24" s="44" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>Wire 4mm</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C24" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A24,'All Transactions'!F:F,B24)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A24,'All Transactions'!F:F,B24,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
-          <t>Bundle/Metres</t>
+          <t>litres</t>
         </is>
       </c>
       <c r="E24" s="70">
-        <f>IFERROR(F24/C24,"")</f>
+        <f>IFERROR(IF(C24=0,"",F24/C24),"")</f>
         <v/>
       </c>
       <c r="F24" s="71">
@@ -58579,25 +58873,25 @@
     <row r="25" ht="15.75" customHeight="1" s="99">
       <c r="A25" s="42" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B25" s="42" t="inlineStr">
         <is>
-          <t>Wire 2.5mm</t>
+          <t>Wire</t>
         </is>
       </c>
       <c r="C25" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A25,'All Transactions'!F:F,B25)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A25,'All Transactions'!F:F,B25,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D25" s="42" t="inlineStr">
         <is>
-          <t>Bundle/Metres</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E25" s="65">
-        <f>IFERROR(F25/C25,"")</f>
+        <f>IFERROR(IF(C25=0,"",F25/C25),"")</f>
         <v/>
       </c>
       <c r="F25" s="66">
@@ -58620,25 +58914,25 @@
     <row r="26" ht="15.75" customHeight="1" s="99">
       <c r="A26" s="44" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B26" s="44" t="inlineStr">
         <is>
-          <t>Wire 1.5mm</t>
+          <t>Plywood/Shuttering</t>
         </is>
       </c>
       <c r="C26" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A26,'All Transactions'!F:F,B26)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A26,'All Transactions'!F:F,B26,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D26" s="44" t="inlineStr">
         <is>
-          <t>Bundle/Metres</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E26" s="70">
-        <f>IFERROR(F26/C26,"")</f>
+        <f>IFERROR(IF(C26=0,"",F26/C26),"")</f>
         <v/>
       </c>
       <c r="F26" s="71">
@@ -58661,25 +58955,25 @@
     <row r="27" ht="15.75" customHeight="1" s="99">
       <c r="A27" s="42" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B27" s="42" t="inlineStr">
         <is>
-          <t>Wire 1mm</t>
+          <t>Material Transport</t>
         </is>
       </c>
       <c r="C27" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A27,'All Transactions'!F:F,B27)</f>
+        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A27,'All Transactions'!F:F,B27,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
         <v/>
       </c>
       <c r="D27" s="42" t="inlineStr">
         <is>
-          <t>Bundle/Metres</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="E27" s="65">
-        <f>IFERROR(F27/C27,"")</f>
+        <f>IFERROR(IF(C27=0,"",F27/C27),"")</f>
         <v/>
       </c>
       <c r="F27" s="66">
@@ -58700,291 +58994,81 @@
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="99">
-      <c r="A28" s="44" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B28" s="44" t="inlineStr">
-        <is>
-          <t>Wire 0.75mm</t>
-        </is>
-      </c>
-      <c r="C28" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A28,'All Transactions'!F:F,B28)</f>
-        <v/>
-      </c>
-      <c r="D28" s="44" t="inlineStr">
-        <is>
-          <t>Bundle/Metres</t>
-        </is>
-      </c>
-      <c r="E28" s="70">
-        <f>IFERROR(F28/C28,"")</f>
-        <v/>
-      </c>
-      <c r="F28" s="71">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A28,'All Transactions'!F:F,B28)</f>
-        <v/>
-      </c>
-      <c r="G28" s="72">
-        <f>F28-H28</f>
-        <v/>
-      </c>
-      <c r="H28" s="71">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A28,'All Transactions'!F:F,B28)</f>
-        <v/>
-      </c>
-      <c r="I28" s="73">
-        <f>IFERROR(H28/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A28" s="44" t="n"/>
+      <c r="B28" s="44" t="n"/>
+      <c r="C28" s="69" t="n"/>
+      <c r="D28" s="44" t="n"/>
+      <c r="E28" s="70" t="n"/>
+      <c r="F28" s="71" t="n"/>
+      <c r="G28" s="72" t="n"/>
+      <c r="H28" s="71" t="n"/>
+      <c r="I28" s="73" t="n"/>
     </row>
     <row r="29" ht="15.75" customHeight="1" s="99">
-      <c r="A29" s="42" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B29" s="42" t="inlineStr">
-        <is>
-          <t>Switches/Sockets</t>
-        </is>
-      </c>
-      <c r="C29" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A29,'All Transactions'!F:F,B29)</f>
-        <v/>
-      </c>
-      <c r="D29" s="42" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="E29" s="65">
-        <f>IFERROR(F29/C29,"")</f>
-        <v/>
-      </c>
-      <c r="F29" s="66">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A29,'All Transactions'!F:F,B29)</f>
-        <v/>
-      </c>
-      <c r="G29" s="67">
-        <f>F29-H29</f>
-        <v/>
-      </c>
-      <c r="H29" s="66">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A29,'All Transactions'!F:F,B29)</f>
-        <v/>
-      </c>
-      <c r="I29" s="68">
-        <f>IFERROR(H29/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A29" s="42" t="n"/>
+      <c r="B29" s="42" t="n"/>
+      <c r="C29" s="64" t="n"/>
+      <c r="D29" s="42" t="n"/>
+      <c r="E29" s="65" t="n"/>
+      <c r="F29" s="66" t="n"/>
+      <c r="G29" s="67" t="n"/>
+      <c r="H29" s="66" t="n"/>
+      <c r="I29" s="68" t="n"/>
     </row>
     <row r="30" ht="15.75" customHeight="1" s="99">
-      <c r="A30" s="44" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B30" s="44" t="inlineStr">
-        <is>
-          <t>MCB/Distribution Board</t>
-        </is>
-      </c>
-      <c r="C30" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A30,'All Transactions'!F:F,B30)</f>
-        <v/>
-      </c>
-      <c r="D30" s="44" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="E30" s="70">
-        <f>IFERROR(F30/C30,"")</f>
-        <v/>
-      </c>
-      <c r="F30" s="71">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A30,'All Transactions'!F:F,B30)</f>
-        <v/>
-      </c>
-      <c r="G30" s="72">
-        <f>F30-H30</f>
-        <v/>
-      </c>
-      <c r="H30" s="71">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A30,'All Transactions'!F:F,B30)</f>
-        <v/>
-      </c>
-      <c r="I30" s="73">
-        <f>IFERROR(H30/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A30" s="44" t="n"/>
+      <c r="B30" s="44" t="n"/>
+      <c r="C30" s="69" t="n"/>
+      <c r="D30" s="44" t="n"/>
+      <c r="E30" s="70" t="n"/>
+      <c r="F30" s="71" t="n"/>
+      <c r="G30" s="72" t="n"/>
+      <c r="H30" s="71" t="n"/>
+      <c r="I30" s="73" t="n"/>
     </row>
     <row r="31" ht="15.75" customHeight="1" s="99">
-      <c r="A31" s="42" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B31" s="42" t="inlineStr">
-        <is>
-          <t>Conduit Pipe</t>
-        </is>
-      </c>
-      <c r="C31" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A31,'All Transactions'!F:F,B31)</f>
-        <v/>
-      </c>
-      <c r="D31" s="42" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="E31" s="65">
-        <f>IFERROR(F31/C31,"")</f>
-        <v/>
-      </c>
-      <c r="F31" s="66">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A31,'All Transactions'!F:F,B31)</f>
-        <v/>
-      </c>
-      <c r="G31" s="67">
-        <f>F31-H31</f>
-        <v/>
-      </c>
-      <c r="H31" s="66">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A31,'All Transactions'!F:F,B31)</f>
-        <v/>
-      </c>
-      <c r="I31" s="68">
-        <f>IFERROR(H31/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A31" s="42" t="n"/>
+      <c r="B31" s="42" t="n"/>
+      <c r="C31" s="64" t="n"/>
+      <c r="D31" s="42" t="n"/>
+      <c r="E31" s="65" t="n"/>
+      <c r="F31" s="66" t="n"/>
+      <c r="G31" s="67" t="n"/>
+      <c r="H31" s="66" t="n"/>
+      <c r="I31" s="68" t="n"/>
     </row>
     <row r="32" ht="15.75" customHeight="1" s="99">
-      <c r="A32" s="44" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B32" s="44" t="inlineStr">
-        <is>
-          <t>Fan Hooks/Holders</t>
-        </is>
-      </c>
-      <c r="C32" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A32,'All Transactions'!F:F,B32)</f>
-        <v/>
-      </c>
-      <c r="D32" s="44" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="E32" s="70">
-        <f>IFERROR(F32/C32,"")</f>
-        <v/>
-      </c>
-      <c r="F32" s="71">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A32,'All Transactions'!F:F,B32)</f>
-        <v/>
-      </c>
-      <c r="G32" s="72">
-        <f>F32-H32</f>
-        <v/>
-      </c>
-      <c r="H32" s="71">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A32,'All Transactions'!F:F,B32)</f>
-        <v/>
-      </c>
-      <c r="I32" s="73">
-        <f>IFERROR(H32/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A32" s="44" t="n"/>
+      <c r="B32" s="44" t="n"/>
+      <c r="C32" s="69" t="n"/>
+      <c r="D32" s="44" t="n"/>
+      <c r="E32" s="70" t="n"/>
+      <c r="F32" s="71" t="n"/>
+      <c r="G32" s="72" t="n"/>
+      <c r="H32" s="71" t="n"/>
+      <c r="I32" s="73" t="n"/>
     </row>
     <row r="33" ht="15.75" customHeight="1" s="99">
-      <c r="A33" s="42" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B33" s="42" t="inlineStr">
-        <is>
-          <t>Boards/Plates</t>
-        </is>
-      </c>
-      <c r="C33" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A33,'All Transactions'!F:F,B33)</f>
-        <v/>
-      </c>
-      <c r="D33" s="42" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="E33" s="65">
-        <f>IFERROR(F33/C33,"")</f>
-        <v/>
-      </c>
-      <c r="F33" s="66">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A33,'All Transactions'!F:F,B33)</f>
-        <v/>
-      </c>
-      <c r="G33" s="67">
-        <f>F33-H33</f>
-        <v/>
-      </c>
-      <c r="H33" s="66">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A33,'All Transactions'!F:F,B33)</f>
-        <v/>
-      </c>
-      <c r="I33" s="68">
-        <f>IFERROR(H33/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A33" s="42" t="n"/>
+      <c r="B33" s="42" t="n"/>
+      <c r="C33" s="64" t="n"/>
+      <c r="D33" s="42" t="n"/>
+      <c r="E33" s="65" t="n"/>
+      <c r="F33" s="66" t="n"/>
+      <c r="G33" s="67" t="n"/>
+      <c r="H33" s="66" t="n"/>
+      <c r="I33" s="68" t="n"/>
     </row>
     <row r="34" ht="15.75" customHeight="1" s="99">
-      <c r="A34" s="44" t="inlineStr">
-        <is>
-          <t>Electrical</t>
-        </is>
-      </c>
-      <c r="B34" s="44" t="inlineStr">
-        <is>
-          <t>Junction/Bend/Fitting</t>
-        </is>
-      </c>
-      <c r="C34" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A34,'All Transactions'!F:F,B34)</f>
-        <v/>
-      </c>
-      <c r="D34" s="44" t="inlineStr">
-        <is>
-          <t>Pcs</t>
-        </is>
-      </c>
-      <c r="E34" s="70">
-        <f>IFERROR(F34/C34,"")</f>
-        <v/>
-      </c>
-      <c r="F34" s="71">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A34,'All Transactions'!F:F,B34)</f>
-        <v/>
-      </c>
-      <c r="G34" s="72">
-        <f>F34-H34</f>
-        <v/>
-      </c>
-      <c r="H34" s="71">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A34,'All Transactions'!F:F,B34)</f>
-        <v/>
-      </c>
-      <c r="I34" s="73">
-        <f>IFERROR(H34/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A34" s="44" t="n"/>
+      <c r="B34" s="44" t="n"/>
+      <c r="C34" s="69" t="n"/>
+      <c r="D34" s="44" t="n"/>
+      <c r="E34" s="70" t="n"/>
+      <c r="F34" s="71" t="n"/>
+      <c r="G34" s="72" t="n"/>
+      <c r="H34" s="71" t="n"/>
+      <c r="I34" s="73" t="n"/>
     </row>
     <row r="35" ht="15.75" customHeight="1" s="99">
       <c r="A35" s="60" t="inlineStr">
@@ -59043,7 +59127,7 @@
     <row r="1" ht="17.25" customHeight="1" s="99">
       <c r="A1" s="100" t="inlineStr">
         <is>
-          <t>ENGINEER &amp; LABOUR PAYMENT TRACKER</t>
+          <t>ENGINEER &amp; LABOUR PAYMENT TRACKER  (RETIRED — not maintained since May; use Payment Tracker)</t>
         </is>
       </c>
     </row>
@@ -67739,7 +67823,7 @@
       </c>
       <c r="C4" s="40" t="inlineStr">
         <is>
-          <t>Steel/Iron ₹</t>
+          <t>Steel / Iron ₹</t>
         </is>
       </c>
       <c r="D4" s="40" t="inlineStr">
@@ -67754,34 +67838,26 @@
       </c>
       <c r="F4" s="40" t="inlineStr">
         <is>
-          <t>Transport ₹</t>
+          <t>Professional Fees ₹</t>
         </is>
       </c>
       <c r="G4" s="40" t="inlineStr">
         <is>
-          <t>Food/Provisions ₹</t>
+          <t>Land Development ₹</t>
         </is>
       </c>
       <c r="H4" s="40" t="inlineStr">
         <is>
-          <t>Professional Fees ₹</t>
+          <t>Transport · Food · Misc ₹</t>
         </is>
       </c>
       <c r="I4" s="40" t="inlineStr">
         <is>
-          <t>Land Development ₹</t>
-        </is>
-      </c>
-      <c r="J4" s="40" t="inlineStr">
-        <is>
-          <t>Miscellaneous ₹</t>
-        </is>
-      </c>
-      <c r="K4" s="40" t="inlineStr">
-        <is>
           <t>TOTAL ₹</t>
         </is>
       </c>
+      <c r="J4" s="40" t="n"/>
+      <c r="K4" s="40" t="n"/>
     </row>
     <row r="5" ht="15.75" customHeight="1" s="99">
       <c r="A5" s="74" t="inlineStr">
@@ -67790,45 +67866,39 @@
         </is>
       </c>
       <c r="B5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A5,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J5" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A5,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K5" s="76">
-        <f>SUM(B5:J5)</f>
-        <v/>
-      </c>
+        <f>SUM(B5:H5)</f>
+        <v/>
+      </c>
+      <c r="J5" s="75" t="n"/>
+      <c r="K5" s="76" t="n"/>
     </row>
     <row r="6" ht="15.75" customHeight="1" s="99">
       <c r="A6" s="77" t="inlineStr">
@@ -67837,45 +67907,39 @@
         </is>
       </c>
       <c r="B6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A6,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J6" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A6,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K6" s="79">
-        <f>SUM(B6:J6)</f>
-        <v/>
-      </c>
+        <f>SUM(B6:H6)</f>
+        <v/>
+      </c>
+      <c r="J6" s="78" t="n"/>
+      <c r="K6" s="79" t="n"/>
     </row>
     <row r="7" ht="15.75" customHeight="1" s="99">
       <c r="A7" s="74" t="inlineStr">
@@ -67884,45 +67948,39 @@
         </is>
       </c>
       <c r="B7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A7,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J7" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A7,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K7" s="76">
-        <f>SUM(B7:J7)</f>
-        <v/>
-      </c>
+        <f>SUM(B7:H7)</f>
+        <v/>
+      </c>
+      <c r="J7" s="75" t="n"/>
+      <c r="K7" s="76" t="n"/>
     </row>
     <row r="8" ht="15.75" customHeight="1" s="99">
       <c r="A8" s="77" t="inlineStr">
@@ -67931,45 +67989,39 @@
         </is>
       </c>
       <c r="B8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A8,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J8" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A8,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K8" s="79">
-        <f>SUM(B8:J8)</f>
-        <v/>
-      </c>
+        <f>SUM(B8:H8)</f>
+        <v/>
+      </c>
+      <c r="J8" s="78" t="n"/>
+      <c r="K8" s="79" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" s="99">
       <c r="A9" s="74" t="inlineStr">
@@ -67978,45 +68030,39 @@
         </is>
       </c>
       <c r="B9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A9,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J9" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A9,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K9" s="76">
-        <f>SUM(B9:J9)</f>
-        <v/>
-      </c>
+        <f>SUM(B9:H9)</f>
+        <v/>
+      </c>
+      <c r="J9" s="75" t="n"/>
+      <c r="K9" s="76" t="n"/>
     </row>
     <row r="10" ht="15.75" customHeight="1" s="99">
       <c r="A10" s="77" t="inlineStr">
@@ -68025,45 +68071,39 @@
         </is>
       </c>
       <c r="B10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A10,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J10" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A10,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K10" s="79">
-        <f>SUM(B10:J10)</f>
-        <v/>
-      </c>
+        <f>SUM(B10:H10)</f>
+        <v/>
+      </c>
+      <c r="J10" s="78" t="n"/>
+      <c r="K10" s="79" t="n"/>
     </row>
     <row r="11" ht="15.75" customHeight="1" s="99">
       <c r="A11" s="74" t="inlineStr">
@@ -68072,45 +68112,39 @@
         </is>
       </c>
       <c r="B11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A11,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J11" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A11,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K11" s="76">
-        <f>SUM(B11:J11)</f>
-        <v/>
-      </c>
+        <f>SUM(B11:H11)</f>
+        <v/>
+      </c>
+      <c r="J11" s="75" t="n"/>
+      <c r="K11" s="76" t="n"/>
     </row>
     <row r="12" ht="15.75" customHeight="1" s="99">
       <c r="A12" s="77" t="inlineStr">
@@ -68119,45 +68153,39 @@
         </is>
       </c>
       <c r="B12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A12,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J12" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A12,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K12" s="79">
-        <f>SUM(B12:J12)</f>
-        <v/>
-      </c>
+        <f>SUM(B12:H12)</f>
+        <v/>
+      </c>
+      <c r="J12" s="78" t="n"/>
+      <c r="K12" s="79" t="n"/>
     </row>
     <row r="13" ht="15.75" customHeight="1" s="99">
       <c r="A13" s="74" t="inlineStr">
@@ -68166,45 +68194,39 @@
         </is>
       </c>
       <c r="B13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A13,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J13" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A13,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K13" s="76">
-        <f>SUM(B13:J13)</f>
-        <v/>
-      </c>
+        <f>SUM(B13:H13)</f>
+        <v/>
+      </c>
+      <c r="J13" s="75" t="n"/>
+      <c r="K13" s="76" t="n"/>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="99">
       <c r="A14" s="77" t="inlineStr">
@@ -68213,45 +68235,39 @@
         </is>
       </c>
       <c r="B14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A14,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J14" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A14,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K14" s="79">
-        <f>SUM(B14:J14)</f>
-        <v/>
-      </c>
+        <f>SUM(B14:H14)</f>
+        <v/>
+      </c>
+      <c r="J14" s="78" t="n"/>
+      <c r="K14" s="79" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="99">
       <c r="A15" s="74" t="inlineStr">
@@ -68260,45 +68276,39 @@
         </is>
       </c>
       <c r="B15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A15,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J15" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A15,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K15" s="76">
-        <f>SUM(B15:J15)</f>
-        <v/>
-      </c>
+        <f>SUM(B15:H15)</f>
+        <v/>
+      </c>
+      <c r="J15" s="75" t="n"/>
+      <c r="K15" s="76" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="99">
       <c r="A16" s="77" t="inlineStr">
@@ -68307,45 +68317,39 @@
         </is>
       </c>
       <c r="B16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A16,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J16" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A16,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K16" s="79">
-        <f>SUM(B16:J16)</f>
-        <v/>
-      </c>
+        <f>SUM(B16:H16)</f>
+        <v/>
+      </c>
+      <c r="J16" s="78" t="n"/>
+      <c r="K16" s="79" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="99">
       <c r="A17" s="74" t="inlineStr">
@@ -68354,45 +68358,39 @@
         </is>
       </c>
       <c r="B17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A17,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J17" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A17,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K17" s="76">
-        <f>SUM(B17:J17)</f>
-        <v/>
-      </c>
+        <f>SUM(B17:H17)</f>
+        <v/>
+      </c>
+      <c r="J17" s="75" t="n"/>
+      <c r="K17" s="76" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="99">
       <c r="A18" s="77" t="inlineStr">
@@ -68401,45 +68399,39 @@
         </is>
       </c>
       <c r="B18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A18,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J18" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A18,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K18" s="79">
-        <f>SUM(B18:J18)</f>
-        <v/>
-      </c>
+        <f>SUM(B18:H18)</f>
+        <v/>
+      </c>
+      <c r="J18" s="78" t="n"/>
+      <c r="K18" s="79" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="99">
       <c r="A19" s="74" t="inlineStr">
@@ -68448,45 +68440,39 @@
         </is>
       </c>
       <c r="B19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A19,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J19" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A19,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K19" s="76">
-        <f>SUM(B19:J19)</f>
-        <v/>
-      </c>
+        <f>SUM(B19:H19)</f>
+        <v/>
+      </c>
+      <c r="J19" s="75" t="n"/>
+      <c r="K19" s="76" t="n"/>
     </row>
     <row r="20" ht="15.75" customHeight="1" s="99">
       <c r="A20" s="77" t="inlineStr">
@@ -68495,45 +68481,39 @@
         </is>
       </c>
       <c r="B20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A20,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J20" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A20,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K20" s="79">
-        <f>SUM(B20:J20)</f>
-        <v/>
-      </c>
+        <f>SUM(B20:H20)</f>
+        <v/>
+      </c>
+      <c r="J20" s="78" t="n"/>
+      <c r="K20" s="79" t="n"/>
     </row>
     <row r="21" ht="15.75" customHeight="1" s="99">
       <c r="A21" s="74" t="inlineStr">
@@ -68542,45 +68522,39 @@
         </is>
       </c>
       <c r="B21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A21,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J21" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A21,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K21" s="76">
-        <f>SUM(B21:J21)</f>
-        <v/>
-      </c>
+        <f>SUM(B21:H21)</f>
+        <v/>
+      </c>
+      <c r="J21" s="75" t="n"/>
+      <c r="K21" s="76" t="n"/>
     </row>
     <row r="22" ht="15.75" customHeight="1" s="99">
       <c r="A22" s="77" t="inlineStr">
@@ -68589,45 +68563,39 @@
         </is>
       </c>
       <c r="B22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A22,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J22" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A22,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K22" s="79">
-        <f>SUM(B22:J22)</f>
-        <v/>
-      </c>
+        <f>SUM(B22:H22)</f>
+        <v/>
+      </c>
+      <c r="J22" s="78" t="n"/>
+      <c r="K22" s="79" t="n"/>
     </row>
     <row r="23" ht="15.75" customHeight="1" s="99">
       <c r="A23" s="74" t="inlineStr">
@@ -68636,45 +68604,39 @@
         </is>
       </c>
       <c r="B23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A23,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J23" s="75">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A23,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K23" s="76">
-        <f>SUM(B23:J23)</f>
-        <v/>
-      </c>
+        <f>SUM(B23:H23)</f>
+        <v/>
+      </c>
+      <c r="J23" s="75" t="n"/>
+      <c r="K23" s="76" t="n"/>
     </row>
     <row r="24" ht="15.75" customHeight="1" s="99">
       <c r="A24" s="77" t="inlineStr">
@@ -68683,50 +68645,44 @@
         </is>
       </c>
       <c r="B24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Building Materials")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Building Materials")</f>
         <v/>
       </c>
       <c r="C24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Steel/Iron")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Steel / Iron")</f>
         <v/>
       </c>
       <c r="D24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Electrical")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Electrical")</f>
         <v/>
       </c>
       <c r="E24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Labour")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Labour")</f>
         <v/>
       </c>
       <c r="F24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Transport")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Professional Fees")</f>
         <v/>
       </c>
       <c r="G24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Food/Provisions")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Land Development")</f>
         <v/>
       </c>
       <c r="H24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Professional Fees")</f>
+        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,$A24,'All Transactions'!E:E,"Transport · Food · Misc")</f>
         <v/>
       </c>
       <c r="I24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Land Development")</f>
-        <v/>
-      </c>
-      <c r="J24" s="78">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!C:C,A24,'All Transactions'!E:E,"Miscellaneous")</f>
-        <v/>
-      </c>
-      <c r="K24" s="79">
-        <f>SUM(B24:J24)</f>
-        <v/>
-      </c>
+        <f>SUM(B24:H24)</f>
+        <v/>
+      </c>
+      <c r="J24" s="78" t="n"/>
+      <c r="K24" s="79" t="n"/>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="99">
       <c r="A25" s="80" t="inlineStr">
         <is>
-          <t>GRAND TOTAL</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B25" s="81">
@@ -68761,14 +68717,8 @@
         <f>SUM(I5:I24)</f>
         <v/>
       </c>
-      <c r="J25" s="81">
-        <f>SUM(J5:J24)</f>
-        <v/>
-      </c>
-      <c r="K25" s="81">
-        <f>SUM(K5:K24)</f>
-        <v/>
-      </c>
+      <c r="J25" s="81" t="n"/>
+      <c r="K25" s="81" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1" s="99">
       <c r="A26" s="74" t="n"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -2465,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="99" min="1" max="1"/>
@@ -2907,30 +2907,30 @@
       <c r="I16" s="82" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="99">
-      <c r="A17" s="74" t="inlineStr">
+      <c r="A17" s="77" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B17" s="84">
+      <c r="B17" s="87">
         <f>SUM(B5:B16)</f>
         <v/>
       </c>
-      <c r="C17" s="84">
+      <c r="C17" s="87">
         <f>SUM(C5:C16)</f>
         <v/>
       </c>
-      <c r="D17" s="84">
+      <c r="D17" s="87">
         <f>SUM(D5:D16)</f>
         <v/>
       </c>
-      <c r="E17" s="96">
+      <c r="E17" s="97">
         <f>C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="85" t="n"/>
-      <c r="G17" s="86" t="n"/>
-      <c r="H17" s="74" t="n"/>
+      <c r="F17" s="89" t="n"/>
+      <c r="G17" s="90" t="n"/>
+      <c r="H17" s="77" t="n"/>
       <c r="I17" s="82" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="99">
@@ -3010,6 +3010,21 @@
       <c r="H24" s="82" t="n"/>
       <c r="I24" s="82" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
+    <row r="27"/>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -5115,7 +5130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N48"/>
+  <dimension ref="A1:N59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
@@ -6605,6 +6620,17 @@
         </is>
       </c>
     </row>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -6622,7 +6648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R699"/>
+  <dimension ref="A1:R648"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -27767,7 +27793,7 @@
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Transport · Food · Misc</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
@@ -27827,7 +27853,7 @@
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
@@ -27887,7 +27913,7 @@
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
@@ -27947,7 +27973,7 @@
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
@@ -28007,7 +28033,7 @@
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
@@ -28067,7 +28093,7 @@
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
@@ -28127,7 +28153,7 @@
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
@@ -28187,7 +28213,7 @@
       </c>
       <c r="E566" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F566" t="inlineStr">
@@ -28247,7 +28273,7 @@
       </c>
       <c r="E567" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F567" t="inlineStr">
@@ -28307,7 +28333,7 @@
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
@@ -28367,7 +28393,7 @@
       </c>
       <c r="E569" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F569" t="inlineStr">
@@ -28427,7 +28453,7 @@
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
@@ -28487,7 +28513,7 @@
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
@@ -28547,7 +28573,7 @@
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
@@ -28607,7 +28633,7 @@
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
@@ -28667,7 +28693,7 @@
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
@@ -28727,7 +28753,7 @@
       </c>
       <c r="E575" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F575" t="inlineStr">
@@ -28787,7 +28813,7 @@
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
@@ -28847,7 +28873,7 @@
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
@@ -28907,7 +28933,7 @@
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
@@ -28967,7 +28993,7 @@
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Transport · Food · Misc</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
@@ -29027,7 +29053,7 @@
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
@@ -29087,7 +29113,7 @@
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
@@ -29147,7 +29173,7 @@
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
@@ -29207,7 +29233,7 @@
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
@@ -29267,7 +29293,7 @@
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
@@ -29327,7 +29353,7 @@
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
@@ -29387,7 +29413,7 @@
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
@@ -29447,7 +29473,7 @@
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
@@ -29507,7 +29533,7 @@
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
@@ -29567,7 +29593,7 @@
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
@@ -29627,7 +29653,7 @@
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
@@ -29687,7 +29713,7 @@
       </c>
       <c r="E591" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F591" t="inlineStr">
@@ -29747,7 +29773,7 @@
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
@@ -29807,7 +29833,7 @@
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Transport · Food · Misc</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
@@ -29867,7 +29893,7 @@
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
@@ -29927,7 +29953,7 @@
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
@@ -29987,7 +30013,7 @@
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
@@ -30047,7 +30073,7 @@
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
@@ -30107,7 +30133,7 @@
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
@@ -30167,7 +30193,7 @@
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
@@ -30227,7 +30253,7 @@
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Labour</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
@@ -30407,7 +30433,7 @@
       </c>
       <c r="E603" t="inlineStr">
         <is>
-          <t>Transport · Food · Misc</t>
+          <t>Professional Fees</t>
         </is>
       </c>
       <c r="F603" t="inlineStr">
@@ -33168,57 +33194,6 @@
       <c r="P648" s="60" t="n"/>
       <c r="Q648" s="60" t="n"/>
     </row>
-    <row r="649"/>
-    <row r="650"/>
-    <row r="651"/>
-    <row r="652"/>
-    <row r="653"/>
-    <row r="654"/>
-    <row r="655"/>
-    <row r="656"/>
-    <row r="657"/>
-    <row r="658"/>
-    <row r="659"/>
-    <row r="660"/>
-    <row r="661"/>
-    <row r="662"/>
-    <row r="663"/>
-    <row r="664"/>
-    <row r="665"/>
-    <row r="666"/>
-    <row r="667"/>
-    <row r="668"/>
-    <row r="669"/>
-    <row r="670"/>
-    <row r="671"/>
-    <row r="672"/>
-    <row r="673"/>
-    <row r="674"/>
-    <row r="675"/>
-    <row r="676"/>
-    <row r="677"/>
-    <row r="678"/>
-    <row r="679"/>
-    <row r="680"/>
-    <row r="681"/>
-    <row r="682"/>
-    <row r="683"/>
-    <row r="684"/>
-    <row r="685"/>
-    <row r="686"/>
-    <row r="687"/>
-    <row r="688"/>
-    <row r="689"/>
-    <row r="690"/>
-    <row r="691"/>
-    <row r="692"/>
-    <row r="693"/>
-    <row r="694"/>
-    <row r="695"/>
-    <row r="696"/>
-    <row r="697"/>
-    <row r="698"/>
-    <row r="699"/>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
   <mergeCells count="2">
@@ -58422,12 +58397,12 @@
     <row r="14" ht="15.75" customHeight="1" s="99">
       <c r="A14" s="44" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Electrical</t>
         </is>
       </c>
       <c r="B14" s="44" t="inlineStr">
         <is>
-          <t>Fabrication</t>
+          <t>Electrical Items</t>
         </is>
       </c>
       <c r="C14" s="69">
@@ -58463,12 +58438,12 @@
     <row r="15" ht="15.75" customHeight="1" s="99">
       <c r="A15" s="42" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B15" s="42" t="inlineStr">
         <is>
-          <t>Electrical Items</t>
+          <t>Dr Fixit</t>
         </is>
       </c>
       <c r="C15" s="64">
@@ -58477,7 +58452,7 @@
       </c>
       <c r="D15" s="42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>litres</t>
         </is>
       </c>
       <c r="E15" s="65">
@@ -58504,12 +58479,12 @@
     <row r="16" ht="15.75" customHeight="1" s="99">
       <c r="A16" s="44" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B16" s="44" t="inlineStr">
         <is>
-          <t>Dr Fixit</t>
+          <t>Tiscon 16mm</t>
         </is>
       </c>
       <c r="C16" s="69">
@@ -58518,7 +58493,7 @@
       </c>
       <c r="D16" s="44" t="inlineStr">
         <is>
-          <t>litres</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E16" s="70">
@@ -58550,7 +58525,7 @@
       </c>
       <c r="B17" s="42" t="inlineStr">
         <is>
-          <t>Water Tank</t>
+          <t>Binding Wire</t>
         </is>
       </c>
       <c r="C17" s="64">
@@ -58559,7 +58534,7 @@
       </c>
       <c r="D17" s="42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E17" s="65">
@@ -58591,7 +58566,7 @@
       </c>
       <c r="B18" s="44" t="inlineStr">
         <is>
-          <t>Tiscon 16mm</t>
+          <t>Wire</t>
         </is>
       </c>
       <c r="C18" s="69">
@@ -58600,7 +58575,7 @@
       </c>
       <c r="D18" s="44" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="E18" s="70">
@@ -58627,12 +58602,12 @@
     <row r="19" ht="15.75" customHeight="1" s="99">
       <c r="A19" s="42" t="inlineStr">
         <is>
-          <t>Building Materials</t>
+          <t>Steel / Iron</t>
         </is>
       </c>
       <c r="B19" s="42" t="inlineStr">
         <is>
-          <t>Binding Wire</t>
+          <t>Rings</t>
         </is>
       </c>
       <c r="C19" s="64">
@@ -58641,7 +58616,7 @@
       </c>
       <c r="D19" s="42" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E19" s="65">
@@ -58668,12 +58643,12 @@
     <row r="20" ht="15.75" customHeight="1" s="99">
       <c r="A20" s="44" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B20" s="44" t="inlineStr">
         <is>
-          <t>Wire</t>
+          <t>Cover Block</t>
         </is>
       </c>
       <c r="C20" s="69">
@@ -58682,7 +58657,7 @@
       </c>
       <c r="D20" s="44" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>pcs</t>
         </is>
       </c>
       <c r="E20" s="70">
@@ -58709,12 +58684,12 @@
     <row r="21" ht="15.75" customHeight="1" s="99">
       <c r="A21" s="42" t="inlineStr">
         <is>
-          <t>Steel / Iron</t>
+          <t>Building Materials</t>
         </is>
       </c>
       <c r="B21" s="42" t="inlineStr">
         <is>
-          <t>Rings</t>
+          <t>Nails</t>
         </is>
       </c>
       <c r="C21" s="64">
@@ -58723,7 +58698,7 @@
       </c>
       <c r="D21" s="42" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>bags</t>
         </is>
       </c>
       <c r="E21" s="65">
@@ -58755,7 +58730,7 @@
       </c>
       <c r="B22" s="44" t="inlineStr">
         <is>
-          <t>Cover Block</t>
+          <t>Chemical</t>
         </is>
       </c>
       <c r="C22" s="69">
@@ -58764,7 +58739,7 @@
       </c>
       <c r="D22" s="44" t="inlineStr">
         <is>
-          <t>pcs</t>
+          <t>litres</t>
         </is>
       </c>
       <c r="E22" s="70">
@@ -58796,7 +58771,7 @@
       </c>
       <c r="B23" s="42" t="inlineStr">
         <is>
-          <t>Nails</t>
+          <t>Wire</t>
         </is>
       </c>
       <c r="C23" s="64">
@@ -58805,7 +58780,7 @@
       </c>
       <c r="D23" s="42" t="inlineStr">
         <is>
-          <t>bags</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="E23" s="65">
@@ -58837,7 +58812,7 @@
       </c>
       <c r="B24" s="44" t="inlineStr">
         <is>
-          <t>Chemical</t>
+          <t>Material Transport</t>
         </is>
       </c>
       <c r="C24" s="69">
@@ -58846,7 +58821,7 @@
       </c>
       <c r="D24" s="44" t="inlineStr">
         <is>
-          <t>litres</t>
+          <t>trips</t>
         </is>
       </c>
       <c r="E24" s="70">
@@ -58871,127 +58846,37 @@
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1" s="99">
-      <c r="A25" s="42" t="inlineStr">
-        <is>
-          <t>Building Materials</t>
-        </is>
-      </c>
-      <c r="B25" s="42" t="inlineStr">
-        <is>
-          <t>Wire</t>
-        </is>
-      </c>
-      <c r="C25" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A25,'All Transactions'!F:F,B25,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
-        <v/>
-      </c>
-      <c r="D25" s="42" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="E25" s="65">
-        <f>IFERROR(IF(C25=0,"",F25/C25),"")</f>
-        <v/>
-      </c>
-      <c r="F25" s="66">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A25,'All Transactions'!F:F,B25)</f>
-        <v/>
-      </c>
-      <c r="G25" s="67">
-        <f>F25-H25</f>
-        <v/>
-      </c>
-      <c r="H25" s="66">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A25,'All Transactions'!F:F,B25)</f>
-        <v/>
-      </c>
-      <c r="I25" s="68">
-        <f>IFERROR(H25/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A25" s="42" t="n"/>
+      <c r="B25" s="42" t="n"/>
+      <c r="C25" s="64" t="n"/>
+      <c r="D25" s="42" t="n"/>
+      <c r="E25" s="65" t="n"/>
+      <c r="F25" s="66" t="n"/>
+      <c r="G25" s="67" t="n"/>
+      <c r="H25" s="66" t="n"/>
+      <c r="I25" s="68" t="n"/>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="99">
-      <c r="A26" s="44" t="inlineStr">
-        <is>
-          <t>Building Materials</t>
-        </is>
-      </c>
-      <c r="B26" s="44" t="inlineStr">
-        <is>
-          <t>Plywood/Shuttering</t>
-        </is>
-      </c>
-      <c r="C26" s="69">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A26,'All Transactions'!F:F,B26,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
-        <v/>
-      </c>
-      <c r="D26" s="44" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="70">
-        <f>IFERROR(IF(C26=0,"",F26/C26),"")</f>
-        <v/>
-      </c>
-      <c r="F26" s="71">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A26,'All Transactions'!F:F,B26)</f>
-        <v/>
-      </c>
-      <c r="G26" s="72">
-        <f>F26-H26</f>
-        <v/>
-      </c>
-      <c r="H26" s="71">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A26,'All Transactions'!F:F,B26)</f>
-        <v/>
-      </c>
-      <c r="I26" s="73">
-        <f>IFERROR(H26/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A26" s="44" t="n"/>
+      <c r="B26" s="44" t="n"/>
+      <c r="C26" s="69" t="n"/>
+      <c r="D26" s="44" t="n"/>
+      <c r="E26" s="70" t="n"/>
+      <c r="F26" s="71" t="n"/>
+      <c r="G26" s="72" t="n"/>
+      <c r="H26" s="71" t="n"/>
+      <c r="I26" s="73" t="n"/>
     </row>
     <row r="27" ht="15.75" customHeight="1" s="99">
-      <c r="A27" s="42" t="inlineStr">
-        <is>
-          <t>Building Materials</t>
-        </is>
-      </c>
-      <c r="B27" s="42" t="inlineStr">
-        <is>
-          <t>Material Transport</t>
-        </is>
-      </c>
-      <c r="C27" s="64">
-        <f>SUMIFS('All Transactions'!I:I,'All Transactions'!E:E,A27,'All Transactions'!F:F,B27,'All Transactions'!J:J,"&lt;&gt;Lumpsum",'All Transactions'!J:J,"&lt;&gt;Service",'All Transactions'!J:J,"&lt;&gt;Lot",'All Transactions'!J:J,"&lt;&gt;Advance")</f>
-        <v/>
-      </c>
-      <c r="D27" s="42" t="inlineStr">
-        <is>
-          <t>trips</t>
-        </is>
-      </c>
-      <c r="E27" s="65">
-        <f>IFERROR(IF(C27=0,"",F27/C27),"")</f>
-        <v/>
-      </c>
-      <c r="F27" s="66">
-        <f>SUMIFS('All Transactions'!L:L,'All Transactions'!E:E,A27,'All Transactions'!F:F,B27)</f>
-        <v/>
-      </c>
-      <c r="G27" s="67">
-        <f>F27-H27</f>
-        <v/>
-      </c>
-      <c r="H27" s="66">
-        <f>SUMIFS('All Transactions'!O:O,'All Transactions'!E:E,A27,'All Transactions'!F:F,B27)</f>
-        <v/>
-      </c>
-      <c r="I27" s="68">
-        <f>IFERROR(H27/H$35,"")</f>
-        <v/>
-      </c>
+      <c r="A27" s="42" t="n"/>
+      <c r="B27" s="42" t="n"/>
+      <c r="C27" s="64" t="n"/>
+      <c r="D27" s="42" t="n"/>
+      <c r="E27" s="65" t="n"/>
+      <c r="F27" s="66" t="n"/>
+      <c r="G27" s="67" t="n"/>
+      <c r="H27" s="66" t="n"/>
+      <c r="I27" s="68" t="n"/>
     </row>
     <row r="28" ht="15.75" customHeight="1" s="99">
       <c r="A28" s="44" t="n"/>
@@ -67785,7 +67670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:K59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
@@ -68772,6 +68657,36 @@
       <c r="J29" s="74" t="n"/>
       <c r="K29" s="74" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -2465,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" style="99" min="1" max="1"/>
@@ -3010,21 +3010,6 @@
       <c r="H24" s="82" t="n"/>
       <c r="I24" s="82" t="n"/>
     </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27"/>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
@@ -5130,7 +5115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N59"/>
+  <dimension ref="A1:N48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" style="99" min="1" max="1"/>
@@ -6620,17 +6605,6 @@
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:L2"/>
@@ -6648,7 +6622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R648"/>
+  <dimension ref="A1:R659"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -33166,33 +33140,693 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" s="60" t="inlineStr">
+      <c r="A648" t="n">
+        <v>656</v>
+      </c>
+      <c r="B648" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C648">
+        <f>IF(B648="","",TEXT(B648,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F648" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm</t>
+        </is>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>Tiscon 12mm rod 6 pcs</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I648" t="n">
+        <v>6</v>
+      </c>
+      <c r="J648" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K648" t="n">
+        <v>902</v>
+      </c>
+      <c r="L648">
+        <f>IF(OR(I648="",K648=""),"",I648*K648)</f>
+        <v/>
+      </c>
+      <c r="N648">
+        <f>M648*L648</f>
+        <v/>
+      </c>
+      <c r="O648">
+        <f>IF(L648="","",IF(M648="",L648,L648*(1-M648)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="n">
+        <v>657</v>
+      </c>
+      <c r="B649" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C649">
+        <f>IF(B649="","",TEXT(B649,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I649" t="n">
+        <v>1</v>
+      </c>
+      <c r="J649" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K649" t="n">
+        <v>350</v>
+      </c>
+      <c r="L649">
+        <f>IF(OR(I649="",K649=""),"",I649*K649)</f>
+        <v/>
+      </c>
+      <c r="N649">
+        <f>M649*L649</f>
+        <v/>
+      </c>
+      <c r="O649">
+        <f>IF(L649="","",IF(M649="",L649,L649*(1-M649)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="n">
+        <v>658</v>
+      </c>
+      <c r="B650" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C650">
+        <f>IF(B650="","",TEXT(B650,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F650" t="inlineStr">
+        <is>
+          <t>Binding Wire</t>
+        </is>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>Binding wire 60 kg @ ₹110</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I650" t="n">
+        <v>60</v>
+      </c>
+      <c r="J650" t="inlineStr">
+        <is>
+          <t>Kg</t>
+        </is>
+      </c>
+      <c r="K650" t="n">
+        <v>110</v>
+      </c>
+      <c r="L650">
+        <f>IF(OR(I650="",K650=""),"",I650*K650)</f>
+        <v/>
+      </c>
+      <c r="N650">
+        <f>M650*L650</f>
+        <v/>
+      </c>
+      <c r="O650">
+        <f>IF(L650="","",IF(M650="",L650,L650*(1-M650)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="n">
+        <v>659</v>
+      </c>
+      <c r="B651" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C651">
+        <f>IF(B651="","",TEXT(B651,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F651" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm</t>
+        </is>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm rod 32 pcs</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I651" t="n">
+        <v>32</v>
+      </c>
+      <c r="J651" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K651" t="n">
+        <v>620.5</v>
+      </c>
+      <c r="L651">
+        <f>IF(OR(I651="",K651=""),"",I651*K651)</f>
+        <v/>
+      </c>
+      <c r="N651">
+        <f>M651*L651</f>
+        <v/>
+      </c>
+      <c r="O651">
+        <f>IF(L651="","",IF(M651="",L651,L651*(1-M651)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="n">
+        <v>660</v>
+      </c>
+      <c r="B652" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C652">
+        <f>IF(B652="","",TEXT(B652,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F652" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm</t>
+        </is>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm rod 84 pcs</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I652" t="n">
+        <v>84</v>
+      </c>
+      <c r="J652" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K652" t="n">
+        <v>405.297619047619</v>
+      </c>
+      <c r="L652">
+        <f>IF(OR(I652="",K652=""),"",I652*K652)</f>
+        <v/>
+      </c>
+      <c r="N652">
+        <f>M652*L652</f>
+        <v/>
+      </c>
+      <c r="O652">
+        <f>IF(L652="","",IF(M652="",L652,L652*(1-M652)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="n">
+        <v>661</v>
+      </c>
+      <c r="B653" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C653">
+        <f>IF(B653="","",TEXT(B653,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm</t>
+        </is>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>Tiscon 8mm rod 24 pcs</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I653" t="n">
+        <v>24</v>
+      </c>
+      <c r="J653" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K653" t="n">
+        <v>404.1666666666667</v>
+      </c>
+      <c r="L653">
+        <f>IF(OR(I653="",K653=""),"",I653*K653)</f>
+        <v/>
+      </c>
+      <c r="N653">
+        <f>M653*L653</f>
+        <v/>
+      </c>
+      <c r="O653">
+        <f>IF(L653="","",IF(M653="",L653,L653*(1-M653)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="n">
+        <v>662</v>
+      </c>
+      <c r="B654" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C654">
+        <f>IF(B654="","",TEXT(B654,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F654" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>Nails</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I654" t="n">
+        <v>1</v>
+      </c>
+      <c r="J654" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K654" t="n">
+        <v>150</v>
+      </c>
+      <c r="L654">
+        <f>IF(OR(I654="",K654=""),"",I654*K654)</f>
+        <v/>
+      </c>
+      <c r="N654">
+        <f>M654*L654</f>
+        <v/>
+      </c>
+      <c r="O654">
+        <f>IF(L654="","",IF(M654="",L654,L654*(1-M654)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="n">
+        <v>663</v>
+      </c>
+      <c r="B655" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C655">
+        <f>IF(B655="","",TEXT(B655,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Steel / Iron</t>
+        </is>
+      </c>
+      <c r="F655" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm</t>
+        </is>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>Tiscon 10mm rod 3 pcs</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I655" t="n">
+        <v>3</v>
+      </c>
+      <c r="J655" t="inlineStr">
+        <is>
+          <t>pcs</t>
+        </is>
+      </c>
+      <c r="K655" t="n">
+        <v>610</v>
+      </c>
+      <c r="L655">
+        <f>IF(OR(I655="",K655=""),"",I655*K655)</f>
+        <v/>
+      </c>
+      <c r="N655">
+        <f>M655*L655</f>
+        <v/>
+      </c>
+      <c r="O655">
+        <f>IF(L655="","",IF(M655="",L655,L655*(1-M655)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="n">
+        <v>664</v>
+      </c>
+      <c r="B656" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C656">
+        <f>IF(B656="","",TEXT(B656,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F656" t="inlineStr">
+        <is>
+          <t>Concrete/Gitti</t>
+        </is>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>Gitti 4 trailers @ ₹9,500</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I656" t="n">
+        <v>4</v>
+      </c>
+      <c r="J656" t="inlineStr">
+        <is>
+          <t>Trailer</t>
+        </is>
+      </c>
+      <c r="K656" t="n">
+        <v>9500</v>
+      </c>
+      <c r="L656">
+        <f>IF(OR(I656="",K656=""),"",I656*K656)</f>
+        <v/>
+      </c>
+      <c r="N656">
+        <f>M656*L656</f>
+        <v/>
+      </c>
+      <c r="O656">
+        <f>IF(L656="","",IF(M656="",L656,L656*(1-M656)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="n">
+        <v>665</v>
+      </c>
+      <c r="B657" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C657">
+        <f>IF(B657="","",TEXT(B657,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Building Materials</t>
+        </is>
+      </c>
+      <c r="F657" t="inlineStr">
+        <is>
+          <t>Cement</t>
+        </is>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>Concreto Uno cement 65 bags @ ₹380</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I657" t="n">
+        <v>65</v>
+      </c>
+      <c r="J657" t="inlineStr">
+        <is>
+          <t>Bag</t>
+        </is>
+      </c>
+      <c r="K657" t="n">
+        <v>380</v>
+      </c>
+      <c r="L657">
+        <f>IF(OR(I657="",K657=""),"",I657*K657)</f>
+        <v/>
+      </c>
+      <c r="N657">
+        <f>M657*L657</f>
+        <v/>
+      </c>
+      <c r="O657">
+        <f>IF(L657="","",IF(M657="",L657,L657*(1-M657)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="n">
+        <v>666</v>
+      </c>
+      <c r="B658" s="128" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C658">
+        <f>IF(B658="","",TEXT(B658,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="F658" t="inlineStr">
+        <is>
+          <t>Site Labour</t>
+        </is>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>Labour</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="I658" t="n">
+        <v>1</v>
+      </c>
+      <c r="J658" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K658" t="n">
+        <v>2200</v>
+      </c>
+      <c r="L658">
+        <f>IF(OR(I658="",K658=""),"",I658*K658)</f>
+        <v/>
+      </c>
+      <c r="N658">
+        <f>M658*L658</f>
+        <v/>
+      </c>
+      <c r="O658">
+        <f>IF(L658="","",IF(M658="",L658,L658*(1-M658)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B648" s="60" t="n"/>
-      <c r="C648" s="60" t="n"/>
-      <c r="D648" s="60" t="n"/>
-      <c r="E648" s="60" t="n"/>
-      <c r="F648" s="60" t="n"/>
-      <c r="G648" s="60" t="n"/>
-      <c r="H648" s="60" t="n"/>
-      <c r="I648" s="60" t="n"/>
-      <c r="J648" s="60" t="n"/>
-      <c r="K648" s="60" t="n"/>
-      <c r="L648" s="61">
-        <f>SUM(L5:L647)</f>
-        <v/>
-      </c>
-      <c r="M648" s="60" t="n"/>
-      <c r="N648" s="60" t="n"/>
-      <c r="O648" s="61">
+      <c r="B659" s="60" t="n"/>
+      <c r="C659" s="60" t="n"/>
+      <c r="D659" s="60" t="n"/>
+      <c r="E659" s="60" t="n"/>
+      <c r="F659" s="60" t="n"/>
+      <c r="G659" s="60" t="n"/>
+      <c r="H659" s="60" t="n"/>
+      <c r="I659" s="60" t="n"/>
+      <c r="J659" s="60" t="n"/>
+      <c r="K659" s="60" t="n"/>
+      <c r="L659" s="61">
+        <f>SUM(L5:L658)</f>
+        <v/>
+      </c>
+      <c r="M659" s="60" t="n"/>
+      <c r="N659" s="60" t="n"/>
+      <c r="O659" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P648" s="60" t="n"/>
-      <c r="Q648" s="60" t="n"/>
+      <c r="P659" s="60" t="n"/>
+      <c r="Q659" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -50195,16 +50829,44 @@
       <c r="A110" s="43" t="n">
         <v>116</v>
       </c>
-      <c r="B110" s="53" t="n"/>
-      <c r="C110" s="55" t="n"/>
-      <c r="D110" s="55" t="n"/>
-      <c r="E110" s="55" t="n"/>
-      <c r="F110" s="55" t="n"/>
-      <c r="G110" s="63" t="n"/>
-      <c r="H110" s="55" t="n"/>
+      <c r="B110" s="53" t="n">
+        <v>46308</v>
+      </c>
+      <c r="C110" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D110" s="55" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E110" s="55" t="inlineStr">
+        <is>
+          <t>Steel / Iron + Cement + Building Materials</t>
+        </is>
+      </c>
+      <c r="F110" s="55" t="inlineStr">
+        <is>
+          <t>Full payment — 13-Oct bill (₹1,42,843)</t>
+        </is>
+      </c>
+      <c r="G110" s="63" t="n">
+        <v>142843</v>
+      </c>
+      <c r="H110" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I110" s="55" t="n"/>
       <c r="J110" s="55" t="n"/>
-      <c r="K110" s="55" t="n"/>
+      <c r="K110" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L110" s="58">
         <f>IF(G110="","",IF(L109="",G110,L109+G110))</f>
         <v/>
@@ -67670,7 +68332,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K59"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" style="99" min="1" max="1"/>
@@ -68657,36 +69319,6 @@
       <c r="J29" s="74" t="n"/>
       <c r="K29" s="74" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
-    <row r="37"/>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
-    <row r="43"/>
-    <row r="44"/>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
-    <row r="48"/>
-    <row r="49"/>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
-    <row r="55"/>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:K2"/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -50877,16 +50877,44 @@
       <c r="A111" s="41" t="n">
         <v>117</v>
       </c>
-      <c r="B111" s="45" t="n"/>
-      <c r="C111" s="47" t="n"/>
-      <c r="D111" s="47" t="n"/>
-      <c r="E111" s="47" t="n"/>
-      <c r="F111" s="47" t="n"/>
-      <c r="G111" s="62" t="n"/>
-      <c r="H111" s="47" t="n"/>
+      <c r="B111" s="45" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C111" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D111" s="47" t="inlineStr">
+        <is>
+          <t>Pappu Hardware</t>
+        </is>
+      </c>
+      <c r="E111" s="47" t="inlineStr">
+        <is>
+          <t>Steel / Iron + Cement + Building Materials</t>
+        </is>
+      </c>
+      <c r="F111" s="47" t="inlineStr">
+        <is>
+          <t>Balance settled — Oct bills</t>
+        </is>
+      </c>
+      <c r="G111" s="62" t="n">
+        <v>7353</v>
+      </c>
+      <c r="H111" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I111" s="47" t="n"/>
       <c r="J111" s="47" t="n"/>
-      <c r="K111" s="47" t="n"/>
+      <c r="K111" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L111" s="50">
         <f>IF(G111="","",IF(L110="",G111,L110+G111))</f>
         <v/>

--- a/data/Project_Home_Tracker.xlsx
+++ b/data/Project_Home_Tracker.xlsx
@@ -2759,7 +2759,7 @@
     <row r="12" ht="15.75" customHeight="1" s="99">
       <c r="A12" s="77" t="inlineStr">
         <is>
-          <t>Khutauna Chirai mill</t>
+          <t>Local Purchase</t>
         </is>
       </c>
       <c r="B12" s="87">
@@ -2789,7 +2789,7 @@
     <row r="13" ht="15.75" customHeight="1" s="99">
       <c r="A13" s="77" t="inlineStr">
         <is>
-          <t>Local Purchase</t>
+          <t>Khutauna Chirai mill</t>
         </is>
       </c>
       <c r="B13" s="87">
@@ -2849,7 +2849,7 @@
     <row r="15" ht="15.75" customHeight="1" s="99">
       <c r="A15" s="77" t="inlineStr">
         <is>
-          <t>Naveen Hardware</t>
+          <t>Electrician</t>
         </is>
       </c>
       <c r="B15" s="87">
@@ -2879,7 +2879,7 @@
     <row r="16" ht="15.75" customHeight="1" s="99">
       <c r="A16" s="77" t="inlineStr">
         <is>
-          <t>Sonbhai-Coordinator</t>
+          <t>Naveen Hardware</t>
         </is>
       </c>
       <c r="B16" s="87">
@@ -2909,50 +2909,88 @@
     <row r="17" ht="15.75" customHeight="1" s="99">
       <c r="A17" s="77" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>Subhash</t>
         </is>
       </c>
       <c r="B17" s="87">
-        <f>SUM(B5:B16)</f>
+        <f>COUNTIF('All Transactions'!H:H,A17)</f>
         <v/>
       </c>
       <c r="C17" s="87">
-        <f>SUM(C5:C16)</f>
+        <f>SUMIF('All Transactions'!H:H,A17,'All Transactions'!O:O)</f>
         <v/>
       </c>
       <c r="D17" s="87">
-        <f>SUM(D5:D16)</f>
+        <f>SUMIF('Payment Tracker'!D:D,A17,'Payment Tracker'!G:G)</f>
         <v/>
       </c>
       <c r="E17" s="97">
         <f>C17-D17</f>
         <v/>
       </c>
-      <c r="F17" s="89" t="n"/>
+      <c r="F17" s="89">
+        <f>IF(E17&gt;0,"⚠️ DUE",IF(E17&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
       <c r="G17" s="90" t="n"/>
       <c r="H17" s="77" t="n"/>
       <c r="I17" s="82" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1" s="99">
-      <c r="A18" s="82" t="n"/>
-      <c r="B18" s="82" t="n"/>
-      <c r="C18" s="82" t="n"/>
-      <c r="D18" s="82" t="n"/>
-      <c r="E18" s="82" t="n"/>
-      <c r="F18" s="82" t="n"/>
-      <c r="G18" s="82" t="n"/>
-      <c r="H18" s="82" t="n"/>
+      <c r="A18" s="77" t="inlineStr">
+        <is>
+          <t>Sonbhai-Coordinator</t>
+        </is>
+      </c>
+      <c r="B18" s="87">
+        <f>COUNTIF('All Transactions'!H:H,A18)</f>
+        <v/>
+      </c>
+      <c r="C18" s="87">
+        <f>SUMIF('All Transactions'!H:H,A18,'All Transactions'!O:O)</f>
+        <v/>
+      </c>
+      <c r="D18" s="87">
+        <f>SUMIF('Payment Tracker'!D:D,A18,'Payment Tracker'!G:G)</f>
+        <v/>
+      </c>
+      <c r="E18" s="97">
+        <f>C18-D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="89">
+        <f>IF(E18&gt;0,"⚠️ DUE",IF(E18&lt;0,"🔵 ADV","✅ PAID"))</f>
+        <v/>
+      </c>
+      <c r="G18" s="90" t="n"/>
+      <c r="H18" s="77" t="n"/>
       <c r="I18" s="82" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1" s="99">
-      <c r="A19" s="82" t="n"/>
-      <c r="B19" s="82" t="n"/>
-      <c r="C19" s="82" t="n"/>
-      <c r="D19" s="82" t="n"/>
-      <c r="E19" s="82" t="n"/>
-      <c r="F19" s="82" t="n"/>
-      <c r="G19" s="82" t="n"/>
-      <c r="H19" s="82" t="n"/>
+      <c r="A19" s="77" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B19" s="87">
+        <f>SUM(B5:B18)</f>
+        <v/>
+      </c>
+      <c r="C19" s="87">
+        <f>SUM(C5:C18)</f>
+        <v/>
+      </c>
+      <c r="D19" s="87">
+        <f>SUM(D5:D18)</f>
+        <v/>
+      </c>
+      <c r="E19" s="97">
+        <f>C19-D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="89" t="n"/>
+      <c r="G19" s="90" t="n"/>
+      <c r="H19" s="77" t="n"/>
       <c r="I19" s="82" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1" s="99">
@@ -3234,13 +3272,13 @@
       <c r="F7" s="113" t="n"/>
       <c r="G7" s="6" t="n"/>
       <c r="H7" s="120">
-        <f>-SUMIF('Vendor Summary'!E5:E16,"&lt;0")</f>
+        <f>-SUMIF('Vendor Summary'!E5:E18,"&lt;0")</f>
         <v/>
       </c>
       <c r="I7" s="113" t="n"/>
       <c r="J7" s="6" t="n"/>
       <c r="K7" s="121">
-        <f>SUMIF('Vendor Summary'!E5:E16,"&gt;0")</f>
+        <f>SUMIF('Vendor Summary'!E5:E18,"&gt;0")</f>
         <v/>
       </c>
       <c r="L7" s="113" t="n"/>
@@ -3755,11 +3793,11 @@
         </is>
       </c>
       <c r="I21" s="20">
-        <f>'Vendor Summary'!C17-SUM(I12:I20)</f>
+        <f>'Vendor Summary'!C19-SUM(I12:I20)</f>
         <v/>
       </c>
       <c r="J21" s="20">
-        <f>'Vendor Summary'!D17-SUM(J12:J20)</f>
+        <f>'Vendor Summary'!D19-SUM(J12:J20)</f>
         <v/>
       </c>
       <c r="K21" s="20">
@@ -6622,7 +6660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R659"/>
+  <dimension ref="A1:R665"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" style="99" min="1" max="1"/>
@@ -33800,33 +33838,393 @@
       </c>
     </row>
     <row r="659">
-      <c r="A659" s="60" t="inlineStr">
+      <c r="A659" t="n">
+        <v>667</v>
+      </c>
+      <c r="B659" s="128" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C659">
+        <f>IF(B659="","",TEXT(B659,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F659" t="inlineStr">
+        <is>
+          <t>Shuttering Labour</t>
+        </is>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>Shuttering payment (Papa)</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I659" t="n">
+        <v>1</v>
+      </c>
+      <c r="J659" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K659" t="n">
+        <v>30000</v>
+      </c>
+      <c r="L659">
+        <f>IF(OR(I659="",K659=""),"",I659*K659)</f>
+        <v/>
+      </c>
+      <c r="N659">
+        <f>M659*L659</f>
+        <v/>
+      </c>
+      <c r="O659">
+        <f>IF(L659="","",IF(M659="",L659,L659*(1-M659)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="n">
+        <v>668</v>
+      </c>
+      <c r="B660" s="128" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C660">
+        <f>IF(B660="","",TEXT(B660,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F660" t="inlineStr">
+        <is>
+          <t>Engineering</t>
+        </is>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>Engineer payment</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="I660" t="n">
+        <v>1</v>
+      </c>
+      <c r="J660" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K660" t="n">
+        <v>120000</v>
+      </c>
+      <c r="L660">
+        <f>IF(OR(I660="",K660=""),"",I660*K660)</f>
+        <v/>
+      </c>
+      <c r="N660">
+        <f>M660*L660</f>
+        <v/>
+      </c>
+      <c r="O660">
+        <f>IF(L660="","",IF(M660="",L660,L660*(1-M660)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="n">
+        <v>669</v>
+      </c>
+      <c r="B661" s="128" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C661">
+        <f>IF(B661="","",TEXT(B661,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F661" t="inlineStr">
+        <is>
+          <t>Food/Ration</t>
+        </is>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>Subhash — food</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Subhash</t>
+        </is>
+      </c>
+      <c r="I661" t="n">
+        <v>1</v>
+      </c>
+      <c r="J661" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K661" t="n">
+        <v>3100</v>
+      </c>
+      <c r="L661">
+        <f>IF(OR(I661="",K661=""),"",I661*K661)</f>
+        <v/>
+      </c>
+      <c r="N661">
+        <f>M661*L661</f>
+        <v/>
+      </c>
+      <c r="O661">
+        <f>IF(L661="","",IF(M661="",L661,L661*(1-M661)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="n">
+        <v>670</v>
+      </c>
+      <c r="B662" s="128" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C662">
+        <f>IF(B662="","",TEXT(B662,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr">
+        <is>
+          <t>Electrician Labour</t>
+        </is>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>Electrician payment</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="I662" t="n">
+        <v>1</v>
+      </c>
+      <c r="J662" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K662" t="n">
+        <v>20000</v>
+      </c>
+      <c r="L662">
+        <f>IF(OR(I662="",K662=""),"",I662*K662)</f>
+        <v/>
+      </c>
+      <c r="N662">
+        <f>M662*L662</f>
+        <v/>
+      </c>
+      <c r="O662">
+        <f>IF(L662="","",IF(M662="",L662,L662*(1-M662)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="n">
+        <v>671</v>
+      </c>
+      <c r="B663" s="128" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C663">
+        <f>IF(B663="","",TEXT(B663,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="F663" t="inlineStr">
+        <is>
+          <t>Electrical Items</t>
+        </is>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>Electric pipe and concealed accessories</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
+      <c r="I663" t="n">
+        <v>1</v>
+      </c>
+      <c r="J663" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K663" t="n">
+        <v>6800</v>
+      </c>
+      <c r="L663">
+        <f>IF(OR(I663="",K663=""),"",I663*K663)</f>
+        <v/>
+      </c>
+      <c r="N663">
+        <f>M663*L663</f>
+        <v/>
+      </c>
+      <c r="O663">
+        <f>IF(L663="","",IF(M663="",L663,L663*(1-M663)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="n">
+        <v>672</v>
+      </c>
+      <c r="B664" s="128" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C664">
+        <f>IF(B664="","",TEXT(B664,"MMM-YYYY"))</f>
+        <v/>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Plinth Phase</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F664" t="inlineStr">
+        <is>
+          <t>Food/Ration</t>
+        </is>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
+      <c r="I664" t="n">
+        <v>1</v>
+      </c>
+      <c r="J664" t="inlineStr">
+        <is>
+          <t>Lumpsum</t>
+        </is>
+      </c>
+      <c r="K664" t="n">
+        <v>3000</v>
+      </c>
+      <c r="L664">
+        <f>IF(OR(I664="",K664=""),"",I664*K664)</f>
+        <v/>
+      </c>
+      <c r="N664">
+        <f>M664*L664</f>
+        <v/>
+      </c>
+      <c r="O664">
+        <f>IF(L664="","",IF(M664="",L664,L664*(1-M664)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" s="60" t="inlineStr">
         <is>
           <t>TOTALS</t>
         </is>
       </c>
-      <c r="B659" s="60" t="n"/>
-      <c r="C659" s="60" t="n"/>
-      <c r="D659" s="60" t="n"/>
-      <c r="E659" s="60" t="n"/>
-      <c r="F659" s="60" t="n"/>
-      <c r="G659" s="60" t="n"/>
-      <c r="H659" s="60" t="n"/>
-      <c r="I659" s="60" t="n"/>
-      <c r="J659" s="60" t="n"/>
-      <c r="K659" s="60" t="n"/>
-      <c r="L659" s="61">
-        <f>SUM(L5:L658)</f>
-        <v/>
-      </c>
-      <c r="M659" s="60" t="n"/>
-      <c r="N659" s="60" t="n"/>
-      <c r="O659" s="61">
+      <c r="B665" s="60" t="n"/>
+      <c r="C665" s="60" t="n"/>
+      <c r="D665" s="60" t="n"/>
+      <c r="E665" s="60" t="n"/>
+      <c r="F665" s="60" t="n"/>
+      <c r="G665" s="60" t="n"/>
+      <c r="H665" s="60" t="n"/>
+      <c r="I665" s="60" t="n"/>
+      <c r="J665" s="60" t="n"/>
+      <c r="K665" s="60" t="n"/>
+      <c r="L665" s="61">
+        <f>SUM(L5:L664)</f>
+        <v/>
+      </c>
+      <c r="M665" s="60" t="n"/>
+      <c r="N665" s="60" t="n"/>
+      <c r="O665" s="61">
         <f>SUM(O5:O528)</f>
         <v/>
       </c>
-      <c r="P659" s="60" t="n"/>
-      <c r="Q659" s="60" t="n"/>
+      <c r="P665" s="60" t="n"/>
+      <c r="Q665" s="60" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:Q504"/>
@@ -50925,16 +51323,44 @@
       <c r="A112" s="43" t="n">
         <v>118</v>
       </c>
-      <c r="B112" s="53" t="n"/>
-      <c r="C112" s="55" t="n"/>
-      <c r="D112" s="55" t="n"/>
-      <c r="E112" s="55" t="n"/>
-      <c r="F112" s="55" t="n"/>
-      <c r="G112" s="63" t="n"/>
-      <c r="H112" s="55" t="n"/>
+      <c r="B112" s="53" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C112" s="55" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="D112" s="55" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E112" s="55" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F112" s="55" t="inlineStr">
+        <is>
+          <t>Shuttering payment (Papa)</t>
+        </is>
+      </c>
+      <c r="G112" s="63" t="n">
+        <v>30000</v>
+      </c>
+      <c r="H112" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I112" s="55" t="n"/>
       <c r="J112" s="55" t="n"/>
-      <c r="K112" s="55" t="n"/>
+      <c r="K112" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L112" s="58">
         <f>IF(G112="","",IF(L111="",G112,L111+G112))</f>
         <v/>
@@ -50945,16 +51371,44 @@
       <c r="A113" s="41" t="n">
         <v>119</v>
       </c>
-      <c r="B113" s="45" t="n"/>
-      <c r="C113" s="47" t="n"/>
-      <c r="D113" s="47" t="n"/>
-      <c r="E113" s="47" t="n"/>
-      <c r="F113" s="47" t="n"/>
-      <c r="G113" s="62" t="n"/>
-      <c r="H113" s="47" t="n"/>
+      <c r="B113" s="45" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C113" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D113" s="47" t="inlineStr">
+        <is>
+          <t>Econ Builder</t>
+        </is>
+      </c>
+      <c r="E113" s="47" t="inlineStr">
+        <is>
+          <t>Professional Fees</t>
+        </is>
+      </c>
+      <c r="F113" s="47" t="inlineStr">
+        <is>
+          <t>Engineer payment</t>
+        </is>
+      </c>
+      <c r="G113" s="62" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H113" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I113" s="47" t="n"/>
       <c r="J113" s="47" t="n"/>
-      <c r="K113" s="47" t="n"/>
+      <c r="K113" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L113" s="50">
         <f>IF(G113="","",IF(L112="",G113,L112+G113))</f>
         <v/>
@@ -50965,16 +51419,44 @@
       <c r="A114" s="43" t="n">
         <v>120</v>
       </c>
-      <c r="B114" s="53" t="n"/>
-      <c r="C114" s="55" t="n"/>
-      <c r="D114" s="55" t="n"/>
-      <c r="E114" s="55" t="n"/>
-      <c r="F114" s="55" t="n"/>
-      <c r="G114" s="63" t="n"/>
-      <c r="H114" s="55" t="n"/>
+      <c r="B114" s="53" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C114" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D114" s="55" t="inlineStr">
+        <is>
+          <t>Subhash</t>
+        </is>
+      </c>
+      <c r="E114" s="55" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F114" s="55" t="inlineStr">
+        <is>
+          <t>Subhash — food</t>
+        </is>
+      </c>
+      <c r="G114" s="63" t="n">
+        <v>3100</v>
+      </c>
+      <c r="H114" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I114" s="55" t="n"/>
       <c r="J114" s="55" t="n"/>
-      <c r="K114" s="55" t="n"/>
+      <c r="K114" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L114" s="58">
         <f>IF(G114="","",IF(L113="",G114,L113+G114))</f>
         <v/>
@@ -50985,16 +51467,44 @@
       <c r="A115" s="41" t="n">
         <v>121</v>
       </c>
-      <c r="B115" s="45" t="n"/>
-      <c r="C115" s="47" t="n"/>
-      <c r="D115" s="47" t="n"/>
-      <c r="E115" s="47" t="n"/>
-      <c r="F115" s="47" t="n"/>
-      <c r="G115" s="62" t="n"/>
-      <c r="H115" s="47" t="n"/>
+      <c r="B115" s="45" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C115" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D115" s="47" t="inlineStr">
+        <is>
+          <t>Electrician</t>
+        </is>
+      </c>
+      <c r="E115" s="47" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="F115" s="47" t="inlineStr">
+        <is>
+          <t>Electrician payment</t>
+        </is>
+      </c>
+      <c r="G115" s="62" t="n">
+        <v>20000</v>
+      </c>
+      <c r="H115" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I115" s="47" t="n"/>
       <c r="J115" s="47" t="n"/>
-      <c r="K115" s="47" t="n"/>
+      <c r="K115" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L115" s="50">
         <f>IF(G115="","",IF(L114="",G115,L114+G115))</f>
         <v/>
@@ -51005,16 +51515,44 @@
       <c r="A116" s="43" t="n">
         <v>122</v>
       </c>
-      <c r="B116" s="53" t="n"/>
-      <c r="C116" s="55" t="n"/>
-      <c r="D116" s="55" t="n"/>
-      <c r="E116" s="55" t="n"/>
-      <c r="F116" s="55" t="n"/>
-      <c r="G116" s="63" t="n"/>
-      <c r="H116" s="55" t="n"/>
+      <c r="B116" s="53" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C116" s="55" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D116" s="55" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
+      <c r="E116" s="55" t="inlineStr">
+        <is>
+          <t>Electrical</t>
+        </is>
+      </c>
+      <c r="F116" s="55" t="inlineStr">
+        <is>
+          <t>Electric pipe and concealed accessories</t>
+        </is>
+      </c>
+      <c r="G116" s="63" t="n">
+        <v>6800</v>
+      </c>
+      <c r="H116" s="55" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I116" s="55" t="n"/>
       <c r="J116" s="55" t="n"/>
-      <c r="K116" s="55" t="n"/>
+      <c r="K116" s="55" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L116" s="58">
         <f>IF(G116="","",IF(L115="",G116,L115+G116))</f>
         <v/>
@@ -51025,16 +51563,44 @@
       <c r="A117" s="41" t="n">
         <v>123</v>
       </c>
-      <c r="B117" s="45" t="n"/>
-      <c r="C117" s="47" t="n"/>
-      <c r="D117" s="47" t="n"/>
-      <c r="E117" s="47" t="n"/>
-      <c r="F117" s="47" t="n"/>
-      <c r="G117" s="62" t="n"/>
-      <c r="H117" s="47" t="n"/>
+      <c r="B117" s="45" t="n">
+        <v>46309</v>
+      </c>
+      <c r="C117" s="47" t="inlineStr">
+        <is>
+          <t>Self</t>
+        </is>
+      </c>
+      <c r="D117" s="47" t="inlineStr">
+        <is>
+          <t>Local Purchase</t>
+        </is>
+      </c>
+      <c r="E117" s="47" t="inlineStr">
+        <is>
+          <t>Transport · Food · Misc</t>
+        </is>
+      </c>
+      <c r="F117" s="47" t="inlineStr">
+        <is>
+          <t>Vegetables</t>
+        </is>
+      </c>
+      <c r="G117" s="62" t="n">
+        <v>3000</v>
+      </c>
+      <c r="H117" s="47" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="I117" s="47" t="n"/>
       <c r="J117" s="47" t="n"/>
-      <c r="K117" s="47" t="n"/>
+      <c r="K117" s="47" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="L117" s="50">
         <f>IF(G117="","",IF(L116="",G117,L116+G117))</f>
         <v/>
